--- a/jogos_2026-08-17.xlsx
+++ b/jogos_2026-08-17.xlsx
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G38">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G39">

--- a/jogos_2026-08-17.xlsx
+++ b/jogos_2026-08-17.xlsx
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2636,10 +2636,10 @@
         <v>0</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE14">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -2956,10 +2956,10 @@
         <v>0</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC16">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3113,10 +3113,10 @@
         <v>0</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA17">
         <v>0</v>

--- a/jogos_2026-08-17.xlsx
+++ b/jogos_2026-08-17.xlsx
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>12.8</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>6.46</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Q31">
         <v>0</v>

--- a/jogos_2026-08-17.xlsx
+++ b/jogos_2026-08-17.xlsx
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE18">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q30">
         <v>0</v>

--- a/jogos_2026-08-17.xlsx
+++ b/jogos_2026-08-17.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU42"/>
+  <dimension ref="A1:AU41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -593,7 +593,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G2">
@@ -756,7 +756,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G3">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O3">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -914,27 +914,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G4">
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2026-08-17 12:45:00</t>
+          <t>2026-08-17 12:30:00</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G5">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2026-08-17 13:00:00</t>
+          <t>2026-08-17 12:45:00</t>
         </is>
       </c>
     </row>
@@ -1240,27 +1240,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G6">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2026-08-17 13:00:00</t>
+          <t>2026-08-17 12:45:00</t>
         </is>
       </c>
     </row>
@@ -1408,22 +1408,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O7">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P7">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1566,27 +1566,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G8">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2026-08-17 13:15:00</t>
+          <t>2026-08-17 13:00:00</t>
         </is>
       </c>
     </row>
@@ -1729,12 +1729,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="O9">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="P9">
-        <v>5.89</v>
+        <v>4.1</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2026-08-17 13:30:00</t>
+          <t>2026-08-17 13:00:00</t>
         </is>
       </c>
     </row>
@@ -1897,22 +1897,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G10">
@@ -1935,17 +1935,17 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>5.89</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -2055,27 +2055,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G11">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N11">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-08-17 14:00:00</t>
+          <t>2026-08-17 13:30:00</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G12">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O13">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P13">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2549,22 +2549,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.26</v>
+        <v>1.84</v>
       </c>
       <c r="O14">
-        <v>6.1</v>
+        <v>3.58</v>
       </c>
       <c r="P14">
-        <v>9.050000000000001</v>
+        <v>4.57</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2636,10 +2636,10 @@
         <v>0</v>
       </c>
       <c r="AC14">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD14">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE14">
         <v>0</v>
@@ -2712,22 +2712,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.5</v>
+        <v>1.26</v>
       </c>
       <c r="O15">
-        <v>4.4</v>
+        <v>6.1</v>
       </c>
       <c r="P15">
-        <v>5.76</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2799,10 +2799,10 @@
         <v>0</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE15">
         <v>0</v>
@@ -2870,12 +2870,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>3.47</v>
+        <v>1.5</v>
       </c>
       <c r="O16">
-        <v>3.38</v>
+        <v>4.4</v>
       </c>
       <c r="P16">
-        <v>1.94</v>
+        <v>5.76</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -2956,10 +2956,10 @@
         <v>0</v>
       </c>
       <c r="AA16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB16">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC16">
         <v>0</v>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2026-08-17 15:00:00</t>
+          <t>2026-08-17 14:00:00</t>
         </is>
       </c>
     </row>
@@ -3038,22 +3038,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.63</v>
+        <v>3.47</v>
       </c>
       <c r="O17">
-        <v>2.63</v>
+        <v>3.38</v>
       </c>
       <c r="P17">
-        <v>3.1</v>
+        <v>1.94</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3113,16 +3113,16 @@
         <v>0</v>
       </c>
       <c r="Y17">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z17">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC17">
         <v>0</v>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.02</v>
+        <v>2.63</v>
       </c>
       <c r="O18">
-        <v>3.9</v>
+        <v>2.63</v>
       </c>
       <c r="P18">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3276,10 +3276,10 @@
         <v>0</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA18">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="AC18">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD18">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AE18">
         <v>0</v>
@@ -3364,22 +3364,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G19">
@@ -3409,10 +3409,10 @@
         <v>2.02</v>
       </c>
       <c r="O19">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="P19">
-        <v>3.41</v>
+        <v>3.11</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3451,10 +3451,10 @@
         <v>0</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE19">
         <v>0</v>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G23">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="O24">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P24">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>2026-08-17 15:15:00</t>
+          <t>2026-08-17 15:00:00</t>
         </is>
       </c>
     </row>
@@ -4337,12 +4337,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>2026-08-17 15:30:00</t>
+          <t>2026-08-17 15:15:00</t>
         </is>
       </c>
     </row>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Batman Petrolspor</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G26">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Batman Petrolspor</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="O27">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P27">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -4977,7 +4977,7 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>2026-08-17 16:00:00</t>
+          <t>2026-08-17 15:30:00</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="O29">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P29">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5075,10 +5075,10 @@
         <v>0</v>
       </c>
       <c r="AA29">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB29">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC29">
         <v>0</v>
@@ -5152,27 +5152,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.82</v>
+        <v>2.41</v>
       </c>
       <c r="O30">
-        <v>4.35</v>
+        <v>3.44</v>
       </c>
       <c r="P30">
-        <v>3.4</v>
+        <v>2.73</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5238,10 +5238,10 @@
         <v>0</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC30">
         <v>0</v>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>2026-08-17 16:15:00</t>
+          <t>2026-08-17 16:00:00</t>
         </is>
       </c>
     </row>
@@ -5320,22 +5320,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>12.8</v>
+        <v>1.82</v>
       </c>
       <c r="O31">
-        <v>6.46</v>
+        <v>4.35</v>
       </c>
       <c r="P31">
-        <v>1.25</v>
+        <v>3.4</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5478,12 +5478,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.31</v>
+        <v>12.8</v>
       </c>
       <c r="O32">
-        <v>5.17</v>
+        <v>6.46</v>
       </c>
       <c r="P32">
-        <v>11.4</v>
+        <v>1.25</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5564,10 +5564,10 @@
         <v>0</v>
       </c>
       <c r="AA32">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB32">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC32">
         <v>0</v>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>2026-08-17 16:30:00</t>
+          <t>2026-08-17 16:15:00</t>
         </is>
       </c>
     </row>
@@ -5641,27 +5641,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>5.17</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5727,10 +5727,10 @@
         <v>0</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC33">
         <v>0</v>
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>2026-08-17 19:00:00</t>
+          <t>2026-08-17 16:30:00</t>
         </is>
       </c>
     </row>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G34">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="O35">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="P35">
-        <v>5.61</v>
+        <v>0</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6053,10 +6053,10 @@
         <v>0</v>
       </c>
       <c r="AA35">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB35">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC35">
         <v>0</v>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>2026-08-17 20:00:00</t>
+          <t>2026-08-17 19:00:00</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>5.61</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6216,10 +6216,10 @@
         <v>0</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G37">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G38">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>2026-08-17 21:00:00</t>
+          <t>2026-08-17 20:00:00</t>
         </is>
       </c>
     </row>
@@ -6624,7 +6624,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G39">
@@ -6782,12 +6782,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G40">
@@ -6933,7 +6933,7 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>2026-08-17 21:00:00</t>
+          <t>2026-08-17 21:30:00</t>
         </is>
       </c>
     </row>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G41">
@@ -7095,169 +7095,6 @@
         <v>0</v>
       </c>
       <c r="AU41" t="inlineStr">
-        <is>
-          <t>2026-08-17 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Chile Primera División</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Palestino</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Huachipato</t>
-        </is>
-      </c>
-      <c r="G42">
-        <v>0</v>
-      </c>
-      <c r="H42">
-        <v>0</v>
-      </c>
-      <c r="I42">
-        <v>0</v>
-      </c>
-      <c r="J42">
-        <v>0</v>
-      </c>
-      <c r="K42">
-        <v>0</v>
-      </c>
-      <c r="L42">
-        <v>0</v>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N42">
-        <v>0</v>
-      </c>
-      <c r="O42">
-        <v>0</v>
-      </c>
-      <c r="P42">
-        <v>0</v>
-      </c>
-      <c r="Q42">
-        <v>0</v>
-      </c>
-      <c r="R42">
-        <v>0</v>
-      </c>
-      <c r="S42">
-        <v>0</v>
-      </c>
-      <c r="T42">
-        <v>0</v>
-      </c>
-      <c r="U42">
-        <v>0</v>
-      </c>
-      <c r="V42">
-        <v>0</v>
-      </c>
-      <c r="W42">
-        <v>0</v>
-      </c>
-      <c r="X42">
-        <v>0</v>
-      </c>
-      <c r="Y42">
-        <v>0</v>
-      </c>
-      <c r="Z42">
-        <v>0</v>
-      </c>
-      <c r="AA42">
-        <v>0</v>
-      </c>
-      <c r="AB42">
-        <v>0</v>
-      </c>
-      <c r="AC42">
-        <v>0</v>
-      </c>
-      <c r="AD42">
-        <v>0</v>
-      </c>
-      <c r="AE42">
-        <v>0</v>
-      </c>
-      <c r="AF42">
-        <v>0</v>
-      </c>
-      <c r="AG42">
-        <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ42">
-        <v>0</v>
-      </c>
-      <c r="AK42">
-        <v>0</v>
-      </c>
-      <c r="AL42">
-        <v>0</v>
-      </c>
-      <c r="AM42">
-        <v>-1</v>
-      </c>
-      <c r="AN42">
-        <v>-1</v>
-      </c>
-      <c r="AO42">
-        <v>-1</v>
-      </c>
-      <c r="AP42">
-        <v>-1</v>
-      </c>
-      <c r="AQ42">
-        <v>0</v>
-      </c>
-      <c r="AR42">
-        <v>0</v>
-      </c>
-      <c r="AS42">
-        <v>0</v>
-      </c>
-      <c r="AT42">
-        <v>0</v>
-      </c>
-      <c r="AU42" t="inlineStr">
         <is>
           <t>2026-08-17 21:30:00</t>
         </is>

--- a/jogos_2026-08-17.xlsx
+++ b/jogos_2026-08-17.xlsx
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G5">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G6">

--- a/jogos_2026-08-17.xlsx
+++ b/jogos_2026-08-17.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU41"/>
+  <dimension ref="A1:AU42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -588,27 +588,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G2">
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -674,10 +674,10 @@
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC2">
         <v>0</v>
@@ -739,7 +739,7 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2026-08-17 12:30:00</t>
+          <t>2026-08-17 12:00:00</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G3">
@@ -919,7 +919,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O4">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1077,27 +1077,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2026-08-17 12:45:00</t>
+          <t>2026-08-17 12:30:00</t>
         </is>
       </c>
     </row>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1785,55 +1785,55 @@
         <v>4.1</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1948,55 +1948,55 @@
         <v>5.89</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2274,55 +2274,55 @@
         <v>0</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2600,55 +2600,55 @@
         <v>4.57</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2763,40 +2763,40 @@
         <v>9.050000000000001</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AC15">
         <v>1.95</v>
@@ -2805,13 +2805,13 @@
         <v>1.85</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2926,55 +2926,55 @@
         <v>5.76</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3089,34 +3089,34 @@
         <v>1.94</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA17">
         <v>2</v>
@@ -3125,19 +3125,19 @@
         <v>1.8</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3252,28 +3252,28 @@
         <v>3.1</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y18">
         <v>1.83</v>
@@ -3282,25 +3282,25 @@
         <v>1.98</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3415,40 +3415,40 @@
         <v>3.11</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>6.24</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AC19">
         <v>1.78</v>
@@ -3457,13 +3457,13 @@
         <v>1.89</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3578,55 +3578,55 @@
         <v>3.41</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3771,10 +3771,10 @@
         <v>0</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>5.02</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4393,55 +4393,55 @@
         <v>5.75</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4882,55 +4882,55 @@
         <v>4.56</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G29">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
       <c r="O30">
-        <v>3.44</v>
+        <v>3.1</v>
       </c>
       <c r="P30">
-        <v>2.73</v>
+        <v>2.98</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AA30">
-        <v>1.73</v>
+        <v>2.42</v>
       </c>
       <c r="AB30">
-        <v>1.95</v>
+        <v>1.66</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5315,27 +5315,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.82</v>
+        <v>2.41</v>
       </c>
       <c r="O31">
-        <v>4.35</v>
+        <v>3.44</v>
       </c>
       <c r="P31">
-        <v>3.4</v>
+        <v>2.73</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>2026-08-17 16:15:00</t>
+          <t>2026-08-17 16:00:00</t>
         </is>
       </c>
     </row>
@@ -5483,22 +5483,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>12.8</v>
+        <v>1.82</v>
       </c>
       <c r="O32">
-        <v>6.46</v>
+        <v>4.35</v>
       </c>
       <c r="P32">
+        <v>3.4</v>
+      </c>
+      <c r="Q32">
+        <v>2.25</v>
+      </c>
+      <c r="R32">
+        <v>2.8</v>
+      </c>
+      <c r="S32">
+        <v>1.13</v>
+      </c>
+      <c r="T32">
+        <v>4.75</v>
+      </c>
+      <c r="U32">
+        <v>1.74</v>
+      </c>
+      <c r="V32">
+        <v>1.95</v>
+      </c>
+      <c r="W32">
+        <v>1.3</v>
+      </c>
+      <c r="X32">
+        <v>1.01</v>
+      </c>
+      <c r="Y32">
+        <v>1.02</v>
+      </c>
+      <c r="Z32">
+        <v>7.7</v>
+      </c>
+      <c r="AA32">
+        <v>1.18</v>
+      </c>
+      <c r="AB32">
+        <v>3.9</v>
+      </c>
+      <c r="AC32">
+        <v>1.63</v>
+      </c>
+      <c r="AD32">
+        <v>2.21</v>
+      </c>
+      <c r="AE32">
+        <v>1.5</v>
+      </c>
+      <c r="AF32">
         <v>1.25</v>
       </c>
-      <c r="Q32">
-        <v>0</v>
-      </c>
-      <c r="R32">
-        <v>0</v>
-      </c>
-      <c r="S32">
-        <v>0</v>
-      </c>
-      <c r="T32">
-        <v>0</v>
-      </c>
-      <c r="U32">
-        <v>0</v>
-      </c>
-      <c r="V32">
-        <v>0</v>
-      </c>
-      <c r="W32">
-        <v>0</v>
-      </c>
-      <c r="X32">
-        <v>0</v>
-      </c>
-      <c r="Y32">
-        <v>0</v>
-      </c>
-      <c r="Z32">
-        <v>0</v>
-      </c>
-      <c r="AA32">
-        <v>0</v>
-      </c>
-      <c r="AB32">
-        <v>0</v>
-      </c>
-      <c r="AC32">
-        <v>0</v>
-      </c>
-      <c r="AD32">
-        <v>0</v>
-      </c>
-      <c r="AE32">
-        <v>0</v>
-      </c>
-      <c r="AF32">
-        <v>0</v>
-      </c>
       <c r="AG32">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.31</v>
+        <v>12.8</v>
       </c>
       <c r="O33">
-        <v>5.17</v>
+        <v>6.46</v>
       </c>
       <c r="P33">
-        <v>11.4</v>
+        <v>1.25</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA33">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="AB33">
-        <v>1.96</v>
+        <v>2.31</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>2026-08-17 16:30:00</t>
+          <t>2026-08-17 16:15:00</t>
         </is>
       </c>
     </row>
@@ -5804,27 +5804,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>5.17</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>2026-08-17 19:00:00</t>
+          <t>2026-08-17 16:30:00</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G35">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="O36">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="P36">
-        <v>5.61</v>
+        <v>0</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6216,10 +6216,10 @@
         <v>0</v>
       </c>
       <c r="AA36">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB36">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC36">
         <v>0</v>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>2026-08-17 20:00:00</t>
+          <t>2026-08-17 19:00:00</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>5.61</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6619,12 +6619,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>2026-08-17 21:00:00</t>
+          <t>2026-08-17 20:00:00</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G40">
@@ -6838,55 +6838,55 @@
         <v>0</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6933,7 +6933,7 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>2026-08-17 21:30:00</t>
+          <t>2026-08-17 21:00:00</t>
         </is>
       </c>
     </row>
@@ -6950,151 +6950,314 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Deportes Temuco</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Recoleta</t>
+        </is>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>0</v>
+      </c>
+      <c r="Q41">
+        <v>0</v>
+      </c>
+      <c r="R41">
+        <v>0</v>
+      </c>
+      <c r="S41">
+        <v>0</v>
+      </c>
+      <c r="T41">
+        <v>0</v>
+      </c>
+      <c r="U41">
+        <v>0</v>
+      </c>
+      <c r="V41">
+        <v>0</v>
+      </c>
+      <c r="W41">
+        <v>0</v>
+      </c>
+      <c r="X41">
+        <v>0</v>
+      </c>
+      <c r="Y41">
+        <v>0</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+      <c r="AA41">
+        <v>0</v>
+      </c>
+      <c r="AB41">
+        <v>0</v>
+      </c>
+      <c r="AC41">
+        <v>0</v>
+      </c>
+      <c r="AD41">
+        <v>0</v>
+      </c>
+      <c r="AE41">
+        <v>0</v>
+      </c>
+      <c r="AF41">
+        <v>0</v>
+      </c>
+      <c r="AG41">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ41">
+        <v>0</v>
+      </c>
+      <c r="AK41">
+        <v>0</v>
+      </c>
+      <c r="AL41">
+        <v>0</v>
+      </c>
+      <c r="AM41">
+        <v>-1</v>
+      </c>
+      <c r="AN41">
+        <v>-1</v>
+      </c>
+      <c r="AO41">
+        <v>-1</v>
+      </c>
+      <c r="AP41">
+        <v>-1</v>
+      </c>
+      <c r="AQ41">
+        <v>0</v>
+      </c>
+      <c r="AR41">
+        <v>0</v>
+      </c>
+      <c r="AS41">
+        <v>0</v>
+      </c>
+      <c r="AT41">
+        <v>0</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>2026-08-17 21:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
           <t>Chile Primera División</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>Palestino</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>Huachipato</t>
         </is>
       </c>
-      <c r="G41">
-        <v>0</v>
-      </c>
-      <c r="H41">
-        <v>0</v>
-      </c>
-      <c r="I41">
-        <v>0</v>
-      </c>
-      <c r="J41">
-        <v>0</v>
-      </c>
-      <c r="K41">
-        <v>0</v>
-      </c>
-      <c r="L41">
-        <v>0</v>
-      </c>
-      <c r="M41" t="inlineStr">
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N41">
-        <v>0</v>
-      </c>
-      <c r="O41">
-        <v>0</v>
-      </c>
-      <c r="P41">
-        <v>0</v>
-      </c>
-      <c r="Q41">
-        <v>0</v>
-      </c>
-      <c r="R41">
-        <v>0</v>
-      </c>
-      <c r="S41">
-        <v>0</v>
-      </c>
-      <c r="T41">
-        <v>0</v>
-      </c>
-      <c r="U41">
-        <v>0</v>
-      </c>
-      <c r="V41">
-        <v>0</v>
-      </c>
-      <c r="W41">
-        <v>0</v>
-      </c>
-      <c r="X41">
-        <v>0</v>
-      </c>
-      <c r="Y41">
-        <v>0</v>
-      </c>
-      <c r="Z41">
-        <v>0</v>
-      </c>
-      <c r="AA41">
-        <v>0</v>
-      </c>
-      <c r="AB41">
-        <v>0</v>
-      </c>
-      <c r="AC41">
-        <v>0</v>
-      </c>
-      <c r="AD41">
-        <v>0</v>
-      </c>
-      <c r="AE41">
-        <v>0</v>
-      </c>
-      <c r="AF41">
-        <v>0</v>
-      </c>
-      <c r="AG41">
-        <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ41">
-        <v>0</v>
-      </c>
-      <c r="AK41">
-        <v>0</v>
-      </c>
-      <c r="AL41">
-        <v>0</v>
-      </c>
-      <c r="AM41">
-        <v>-1</v>
-      </c>
-      <c r="AN41">
-        <v>-1</v>
-      </c>
-      <c r="AO41">
-        <v>-1</v>
-      </c>
-      <c r="AP41">
-        <v>-1</v>
-      </c>
-      <c r="AQ41">
-        <v>0</v>
-      </c>
-      <c r="AR41">
-        <v>0</v>
-      </c>
-      <c r="AS41">
-        <v>0</v>
-      </c>
-      <c r="AT41">
-        <v>0</v>
-      </c>
-      <c r="AU41" t="inlineStr">
+      <c r="N42">
+        <v>1.77</v>
+      </c>
+      <c r="O42">
+        <v>3.65</v>
+      </c>
+      <c r="P42">
+        <v>4.15</v>
+      </c>
+      <c r="Q42">
+        <v>2.3</v>
+      </c>
+      <c r="R42">
+        <v>2.3</v>
+      </c>
+      <c r="S42">
+        <v>1.3</v>
+      </c>
+      <c r="T42">
+        <v>3.05</v>
+      </c>
+      <c r="U42">
+        <v>2.58</v>
+      </c>
+      <c r="V42">
+        <v>1.5</v>
+      </c>
+      <c r="W42">
+        <v>1.11</v>
+      </c>
+      <c r="X42">
+        <v>1.01</v>
+      </c>
+      <c r="Y42">
+        <v>1.18</v>
+      </c>
+      <c r="Z42">
+        <v>3.92</v>
+      </c>
+      <c r="AA42">
+        <v>1.74</v>
+      </c>
+      <c r="AB42">
+        <v>2.1</v>
+      </c>
+      <c r="AC42">
+        <v>2.69</v>
+      </c>
+      <c r="AD42">
+        <v>1.38</v>
+      </c>
+      <c r="AE42">
+        <v>1.13</v>
+      </c>
+      <c r="AF42">
+        <v>1.65</v>
+      </c>
+      <c r="AG42">
+        <v>2.1</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ42">
+        <v>1.15</v>
+      </c>
+      <c r="AK42">
+        <v>1.9</v>
+      </c>
+      <c r="AL42">
+        <v>0</v>
+      </c>
+      <c r="AM42">
+        <v>-1</v>
+      </c>
+      <c r="AN42">
+        <v>-1</v>
+      </c>
+      <c r="AO42">
+        <v>-1</v>
+      </c>
+      <c r="AP42">
+        <v>-1</v>
+      </c>
+      <c r="AQ42">
+        <v>0</v>
+      </c>
+      <c r="AR42">
+        <v>0</v>
+      </c>
+      <c r="AS42">
+        <v>0</v>
+      </c>
+      <c r="AT42">
+        <v>0</v>
+      </c>
+      <c r="AU42" t="inlineStr">
         <is>
           <t>2026-08-17 21:30:00</t>
         </is>

--- a/jogos_2026-08-17.xlsx
+++ b/jogos_2026-08-17.xlsx
@@ -2591,19 +2591,19 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="O14">
-        <v>3.58</v>
+        <v>3.2</v>
       </c>
       <c r="P14">
-        <v>4.57</v>
+        <v>4.62</v>
       </c>
       <c r="Q14">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R14">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="S14">
         <v>1.4</v>
@@ -2612,7 +2612,7 @@
         <v>2.75</v>
       </c>
       <c r="U14">
-        <v>3.04</v>
+        <v>2.91</v>
       </c>
       <c r="V14">
         <v>1.35</v>
@@ -2621,7 +2621,7 @@
         <v>1.06</v>
       </c>
       <c r="X14">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y14">
         <v>1.4</v>
@@ -2639,16 +2639,16 @@
         <v>4.1</v>
       </c>
       <c r="AD14">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE14">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF14">
         <v>1.95</v>
       </c>
       <c r="AG14">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK14">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -4873,22 +4873,22 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="O28">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="P28">
-        <v>4.56</v>
+        <v>5.4</v>
       </c>
       <c r="Q28">
         <v>2</v>
       </c>
       <c r="R28">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="S28">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T28">
         <v>3.6</v>
@@ -4897,37 +4897,37 @@
         <v>2.33</v>
       </c>
       <c r="V28">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="W28">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X28">
         <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z28">
-        <v>3.98</v>
+        <v>4.33</v>
       </c>
       <c r="AA28">
         <v>1.66</v>
       </c>
       <c r="AB28">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="AC28">
-        <v>2.49</v>
+        <v>2.63</v>
       </c>
       <c r="AD28">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AE28">
         <v>1.17</v>
       </c>
       <c r="AF28">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG28">
         <v>2.1</v>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK28">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="O34">
-        <v>5.17</v>
+        <v>4.8</v>
       </c>
       <c r="P34">
-        <v>11.4</v>
+        <v>7.8</v>
       </c>
       <c r="Q34">
         <v>1.71</v>
@@ -5866,10 +5866,10 @@
         <v>2.55</v>
       </c>
       <c r="S34">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T34">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="U34">
         <v>2.5</v>
@@ -5878,28 +5878,28 @@
         <v>1.51</v>
       </c>
       <c r="W34">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X34">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="Z34">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="AA34">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="AB34">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="AC34">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AD34">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AE34">
         <v>1.16</v>
@@ -5908,7 +5908,7 @@
         <v>2</v>
       </c>
       <c r="AG34">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>1.04</v>
       </c>
       <c r="AK34">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q36">
         <v>0</v>

--- a/jogos_2026-08-17.xlsx
+++ b/jogos_2026-08-17.xlsx
@@ -638,10 +638,10 @@
         <v>2.5</v>
       </c>
       <c r="O2">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P2">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -970,55 +970,55 @@
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="R4">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="S4">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T4">
-        <v>3.4</v>
+        <v>2.91</v>
       </c>
       <c r="U4">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="V4">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="W4">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X4">
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z4">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AA4">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AB4">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AC4">
-        <v>2.28</v>
+        <v>2.55</v>
       </c>
       <c r="AD4">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AE4">
         <v>1.19</v>
       </c>
       <c r="AF4">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AG4">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK4">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="O6">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="P6">
-        <v>2.18</v>
+        <v>2.07</v>
       </c>
       <c r="Q6">
-        <v>3.86</v>
+        <v>4.04</v>
       </c>
       <c r="R6">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="S6">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="T6">
-        <v>2.67</v>
+        <v>2.53</v>
       </c>
       <c r="U6">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="V6">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W6">
         <v>1.05</v>
       </c>
       <c r="X6">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="Z6">
-        <v>3.05</v>
+        <v>2.86</v>
       </c>
       <c r="AA6">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="AB6">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="AC6">
-        <v>3.58</v>
+        <v>3.86</v>
       </c>
       <c r="AD6">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AE6">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF6">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="AG6">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK6">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1622,55 +1622,55 @@
         <v>1.87</v>
       </c>
       <c r="Q8">
-        <v>3.24</v>
+        <v>3.6</v>
       </c>
       <c r="R8">
-        <v>2.17</v>
+        <v>2.33</v>
       </c>
       <c r="S8">
         <v>1.3</v>
       </c>
       <c r="T8">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="U8">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="V8">
         <v>1.5</v>
       </c>
       <c r="W8">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X8">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y8">
         <v>1.18</v>
       </c>
       <c r="Z8">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="AA8">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB8">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AC8">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="AD8">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AE8">
         <v>1.12</v>
       </c>
       <c r="AF8">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="AG8">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK8">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1785,55 +1785,55 @@
         <v>4.1</v>
       </c>
       <c r="Q9">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R9">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="S9">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T9">
-        <v>2.66</v>
+        <v>2.59</v>
       </c>
       <c r="U9">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="V9">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W9">
         <v>1.03</v>
       </c>
       <c r="X9">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z9">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AA9">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AB9">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AC9">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="AD9">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AE9">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF9">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG9">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>1.22</v>
       </c>
       <c r="AK9">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="O10">
-        <v>3.56</v>
+        <v>3.62</v>
       </c>
       <c r="P10">
-        <v>5.89</v>
+        <v>5.25</v>
       </c>
       <c r="Q10">
         <v>2.26</v>
@@ -1954,16 +1954,16 @@
         <v>2.03</v>
       </c>
       <c r="S10">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="T10">
         <v>2.69</v>
       </c>
       <c r="U10">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="V10">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W10">
         <v>1.03</v>
@@ -1975,16 +1975,16 @@
         <v>1.34</v>
       </c>
       <c r="Z10">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="AA10">
         <v>2.16</v>
       </c>
       <c r="AB10">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AC10">
-        <v>3.95</v>
+        <v>3.74</v>
       </c>
       <c r="AD10">
         <v>1.19</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.09</v>
+        <v>1.29</v>
       </c>
       <c r="AK10">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2280,13 +2280,13 @@
         <v>2.18</v>
       </c>
       <c r="S12">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T12">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="U12">
-        <v>2.43</v>
+        <v>2.56</v>
       </c>
       <c r="V12">
         <v>1.42</v>
@@ -2322,7 +2322,7 @@
         <v>1.67</v>
       </c>
       <c r="AG12">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>1.22</v>
       </c>
       <c r="AK12">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.89</v>
+        <v>2.35</v>
       </c>
       <c r="O13">
-        <v>3.18</v>
+        <v>3.05</v>
       </c>
       <c r="P13">
-        <v>2.42</v>
+        <v>2.95</v>
       </c>
       <c r="Q13">
         <v>2.92</v>
@@ -2443,49 +2443,49 @@
         <v>2</v>
       </c>
       <c r="S13">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T13">
-        <v>2.65</v>
+        <v>2.84</v>
       </c>
       <c r="U13">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="V13">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W13">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X13">
         <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z13">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="AA13">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="AB13">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AC13">
-        <v>3.65</v>
+        <v>3.42</v>
       </c>
       <c r="AD13">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE13">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF13">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG13">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AK13">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2754,19 +2754,19 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="O15">
-        <v>6.1</v>
+        <v>5</v>
       </c>
       <c r="P15">
-        <v>9.050000000000001</v>
+        <v>7</v>
       </c>
       <c r="Q15">
         <v>1.67</v>
       </c>
       <c r="R15">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="S15">
         <v>1.18</v>
@@ -2787,7 +2787,7 @@
         <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z15">
         <v>6.05</v>
@@ -2796,13 +2796,13 @@
         <v>1.4</v>
       </c>
       <c r="AB15">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AC15">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AD15">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AE15">
         <v>1.27</v>
@@ -2811,7 +2811,7 @@
         <v>1.73</v>
       </c>
       <c r="AG15">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2917,31 +2917,31 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="O16">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="P16">
-        <v>5.76</v>
+        <v>5.3</v>
       </c>
       <c r="Q16">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="R16">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="S16">
         <v>1.25</v>
       </c>
       <c r="T16">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="U16">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="V16">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W16">
         <v>1.15</v>
@@ -2950,22 +2950,22 @@
         <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z16">
         <v>5</v>
       </c>
       <c r="AA16">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AB16">
         <v>2.35</v>
       </c>
       <c r="AC16">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AD16">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AE16">
         <v>1.18</v>
@@ -2974,7 +2974,7 @@
         <v>1.7</v>
       </c>
       <c r="AG16">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>1.17</v>
       </c>
       <c r="AK16">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.47</v>
+        <v>3.2</v>
       </c>
       <c r="O17">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="P17">
         <v>1.94</v>
       </c>
       <c r="Q17">
-        <v>4.26</v>
+        <v>3.9</v>
       </c>
       <c r="R17">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="S17">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T17">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="U17">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="V17">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W17">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X17">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y17">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="Z17">
-        <v>3.34</v>
+        <v>3.58</v>
       </c>
       <c r="AA17">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AB17">
-        <v>1.8</v>
+        <v>1.99</v>
       </c>
       <c r="AC17">
-        <v>3.45</v>
+        <v>2.7</v>
       </c>
       <c r="AD17">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AE17">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF17">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG17">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.23</v>
+        <v>1.69</v>
       </c>
       <c r="AK17">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="O18">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="P18">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="Q18">
         <v>3.08</v>
@@ -3261,37 +3261,37 @@
         <v>1.69</v>
       </c>
       <c r="T18">
-        <v>2.23</v>
+        <v>2.04</v>
       </c>
       <c r="U18">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="V18">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="W18">
         <v>1.03</v>
       </c>
       <c r="X18">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y18">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="Z18">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="AA18">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AB18">
         <v>1.31</v>
       </c>
       <c r="AC18">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="AD18">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AE18">
         <v>1.02</v>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AK18">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,22 +3406,22 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="O19">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P19">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="Q19">
+        <v>2.49</v>
+      </c>
+      <c r="R19">
         <v>2.48</v>
       </c>
-      <c r="R19">
-        <v>2.49</v>
-      </c>
       <c r="S19">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T19">
         <v>4.5</v>
@@ -3430,7 +3430,7 @@
         <v>1.91</v>
       </c>
       <c r="V19">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="W19">
         <v>1.22</v>
@@ -3451,19 +3451,19 @@
         <v>3.16</v>
       </c>
       <c r="AC19">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AD19">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AE19">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AF19">
         <v>1.31</v>
       </c>
       <c r="AG19">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>1.25</v>
       </c>
       <c r="AK19">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,46 +3569,46 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="O20">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P20">
-        <v>3.41</v>
+        <v>3.2</v>
       </c>
       <c r="Q20">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="R20">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S20">
         <v>1.3</v>
       </c>
       <c r="T20">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="U20">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="V20">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W20">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X20">
         <v>1</v>
       </c>
       <c r="Y20">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z20">
         <v>3.78</v>
       </c>
       <c r="AA20">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB20">
         <v>2.03</v>
@@ -3620,13 +3620,13 @@
         <v>1.37</v>
       </c>
       <c r="AE20">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF20">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG20">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK20">
         <v>1.75</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="O21">
-        <v>3.1</v>
+        <v>2.65</v>
       </c>
       <c r="P21">
-        <v>3.72</v>
+        <v>3.8</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3895,34 +3895,34 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="O22">
-        <v>4.1</v>
+        <v>4.55</v>
       </c>
       <c r="P22">
-        <v>3.61</v>
+        <v>3.35</v>
       </c>
       <c r="Q22">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="R22">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="S22">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="T22">
-        <v>5.2</v>
+        <v>4.75</v>
       </c>
       <c r="U22">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="V22">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="W22">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X22">
         <v>1.01</v>
@@ -3931,28 +3931,28 @@
         <v>1.03</v>
       </c>
       <c r="Z22">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="AA22">
         <v>1.3</v>
       </c>
       <c r="AB22">
-        <v>3.15</v>
+        <v>3.33</v>
       </c>
       <c r="AC22">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AD22">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AE22">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AF22">
         <v>1.33</v>
       </c>
       <c r="AG22">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>1.29</v>
       </c>
       <c r="AK22">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,43 +4058,43 @@
         </is>
       </c>
       <c r="N23">
-        <v>3.44</v>
+        <v>2.95</v>
       </c>
       <c r="O23">
-        <v>3.82</v>
+        <v>3.68</v>
       </c>
       <c r="P23">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="Q23">
-        <v>3.76</v>
+        <v>3.14</v>
       </c>
       <c r="R23">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="S23">
         <v>1.23</v>
       </c>
       <c r="T23">
-        <v>3.8</v>
+        <v>3.52</v>
       </c>
       <c r="U23">
         <v>2.23</v>
       </c>
       <c r="V23">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W23">
+        <v>1.12</v>
+      </c>
+      <c r="X23">
+        <v>1.03</v>
+      </c>
+      <c r="Y23">
         <v>1.14</v>
       </c>
-      <c r="X23">
-        <v>1.02</v>
-      </c>
-      <c r="Y23">
-        <v>1.15</v>
-      </c>
       <c r="Z23">
-        <v>5.02</v>
+        <v>5</v>
       </c>
       <c r="AA23">
         <v>1.5</v>
@@ -4106,16 +4106,16 @@
         <v>2.29</v>
       </c>
       <c r="AD23">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AE23">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF23">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AG23">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.78</v>
+        <v>1.29</v>
       </c>
       <c r="AK23">
         <v>1.27</v>
@@ -4221,58 +4221,58 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="O24">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P24">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="Q24">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="R24">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S24">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T24">
-        <v>3.68</v>
+        <v>3.9</v>
       </c>
       <c r="U24">
         <v>2.1</v>
       </c>
       <c r="V24">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="W24">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="X24">
         <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z24">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AA24">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AB24">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="AC24">
         <v>2.15</v>
       </c>
       <c r="AD24">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AE24">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AF24">
         <v>1.39</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK24">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="O25">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="P25">
-        <v>5.75</v>
+        <v>4.96</v>
       </c>
       <c r="Q25">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="R25">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="S25">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T25">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="U25">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="V25">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W25">
         <v>1.08</v>
       </c>
       <c r="X25">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y25">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z25">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AA25">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="AB25">
+        <v>1.81</v>
+      </c>
+      <c r="AC25">
+        <v>3.46</v>
+      </c>
+      <c r="AD25">
+        <v>1.28</v>
+      </c>
+      <c r="AE25">
+        <v>1.08</v>
+      </c>
+      <c r="AF25">
         <v>1.83</v>
       </c>
-      <c r="AC25">
-        <v>3.14</v>
-      </c>
-      <c r="AD25">
-        <v>1.3</v>
-      </c>
-      <c r="AE25">
-        <v>1.1</v>
-      </c>
-      <c r="AF25">
-        <v>1.84</v>
-      </c>
       <c r="AG25">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>1.22</v>
       </c>
       <c r="AK25">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4550,10 +4550,10 @@
         <v>2.13</v>
       </c>
       <c r="O26">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="P26">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="Q26">
         <v>2.72</v>
@@ -4580,7 +4580,7 @@
         <v>1.06</v>
       </c>
       <c r="Y26">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z26">
         <v>3.1</v>
@@ -4589,22 +4589,22 @@
         <v>2.1</v>
       </c>
       <c r="AB26">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AC26">
         <v>3.63</v>
       </c>
       <c r="AD26">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE26">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF26">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG26">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -5199,58 +5199,58 @@
         </is>
       </c>
       <c r="N30">
+        <v>2.33</v>
+      </c>
+      <c r="O30">
+        <v>2.88</v>
+      </c>
+      <c r="P30">
+        <v>2.95</v>
+      </c>
+      <c r="Q30">
+        <v>3.16</v>
+      </c>
+      <c r="R30">
+        <v>1.95</v>
+      </c>
+      <c r="S30">
+        <v>1.45</v>
+      </c>
+      <c r="T30">
         <v>2.36</v>
-      </c>
-      <c r="O30">
-        <v>3.1</v>
-      </c>
-      <c r="P30">
-        <v>2.98</v>
-      </c>
-      <c r="Q30">
-        <v>3.18</v>
-      </c>
-      <c r="R30">
-        <v>2.05</v>
-      </c>
-      <c r="S30">
-        <v>1.55</v>
-      </c>
-      <c r="T30">
-        <v>2.62</v>
       </c>
       <c r="U30">
         <v>3.3</v>
       </c>
       <c r="V30">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W30">
         <v>1.03</v>
       </c>
       <c r="X30">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y30">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Z30">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="AA30">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="AB30">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AC30">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="AD30">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AE30">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF30">
         <v>1.91</v>
@@ -5362,37 +5362,37 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="O31">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="P31">
-        <v>2.73</v>
+        <v>2.87</v>
       </c>
       <c r="Q31">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="R31">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="S31">
         <v>1.3</v>
       </c>
       <c r="T31">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U31">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="V31">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W31">
         <v>1.08</v>
       </c>
       <c r="X31">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y31">
         <v>1.21</v>
@@ -5401,19 +5401,19 @@
         <v>4.17</v>
       </c>
       <c r="AA31">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AB31">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="AC31">
         <v>2.8</v>
       </c>
       <c r="AD31">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE31">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF31">
         <v>1.57</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="O32">
-        <v>4.35</v>
+        <v>4.15</v>
       </c>
       <c r="P32">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="Q32">
         <v>2.25</v>
@@ -5543,13 +5543,13 @@
         <v>1.13</v>
       </c>
       <c r="T32">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="U32">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="V32">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="W32">
         <v>1.3</v>
@@ -5561,22 +5561,22 @@
         <v>1.02</v>
       </c>
       <c r="Z32">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="AA32">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AB32">
-        <v>3.9</v>
+        <v>3.58</v>
       </c>
       <c r="AC32">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AD32">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="AE32">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AF32">
         <v>1.25</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK32">
         <v>1.85</v>
@@ -5688,16 +5688,16 @@
         </is>
       </c>
       <c r="N33">
-        <v>12.8</v>
+        <v>9.4</v>
       </c>
       <c r="O33">
-        <v>6.46</v>
+        <v>5.3</v>
       </c>
       <c r="P33">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Q33">
-        <v>9.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="R33">
         <v>2.87</v>
@@ -5706,7 +5706,7 @@
         <v>1.27</v>
       </c>
       <c r="T33">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="U33">
         <v>2.38</v>
@@ -5715,19 +5715,19 @@
         <v>1.55</v>
       </c>
       <c r="W33">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X33">
         <v>1.02</v>
       </c>
       <c r="Y33">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z33">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="AA33">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB33">
         <v>2.31</v>
@@ -5742,10 +5742,10 @@
         <v>1.2</v>
       </c>
       <c r="AF33">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG33">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>4.7</v>
+        <v>1.08</v>
       </c>
       <c r="AK33">
         <v>1.02</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.1</v>
+        <v>2.49</v>
       </c>
       <c r="O35">
-        <v>3.24</v>
+        <v>3.32</v>
       </c>
       <c r="P35">
-        <v>3.18</v>
+        <v>2.45</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.49</v>
+        <v>2.1</v>
       </c>
       <c r="O36">
-        <v>3.32</v>
+        <v>3.24</v>
       </c>
       <c r="P36">
-        <v>2.45</v>
+        <v>3.18</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6355,10 +6355,10 @@
         <v>2.24</v>
       </c>
       <c r="S37">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T37">
-        <v>3.21</v>
+        <v>2.9</v>
       </c>
       <c r="U37">
         <v>2.6</v>
@@ -6370,19 +6370,19 @@
         <v>1.06</v>
       </c>
       <c r="X37">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z37">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AA37">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AB37">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AC37">
         <v>3</v>
@@ -6391,7 +6391,7 @@
         <v>1.33</v>
       </c>
       <c r="AE37">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF37">
         <v>1.85</v>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK37">
         <v>2.38</v>
@@ -6503,31 +6503,31 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.13</v>
+        <v>1.67</v>
       </c>
       <c r="O38">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="P38">
-        <v>3.29</v>
+        <v>3.9</v>
       </c>
       <c r="Q38">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="R38">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="S38">
         <v>1.37</v>
       </c>
       <c r="T38">
-        <v>2.66</v>
+        <v>2.71</v>
       </c>
       <c r="U38">
-        <v>2.66</v>
+        <v>2.71</v>
       </c>
       <c r="V38">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W38">
         <v>1.08</v>
@@ -6536,31 +6536,31 @@
         <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z38">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AA38">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AB38">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AC38">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="AD38">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE38">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF38">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="AG38">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AK38">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,25 +6666,25 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="O39">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P39">
-        <v>3.06</v>
+        <v>3.3</v>
       </c>
       <c r="Q39">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="R39">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="S39">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="T39">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="U39">
         <v>3.08</v>
@@ -6717,13 +6717,13 @@
         <v>1.22</v>
       </c>
       <c r="AE39">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF39">
         <v>1.82</v>
       </c>
       <c r="AG39">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AK39">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,37 +6829,37 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q40">
-        <v>3.64</v>
+        <v>3.3</v>
       </c>
       <c r="R40">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="S40">
         <v>1.43</v>
       </c>
       <c r="T40">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="U40">
-        <v>3.08</v>
+        <v>2.8</v>
       </c>
       <c r="V40">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W40">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X40">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y40">
         <v>1.33</v>
@@ -6871,13 +6871,13 @@
         <v>2.16</v>
       </c>
       <c r="AB40">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AC40">
         <v>3.5</v>
       </c>
       <c r="AD40">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE40">
         <v>1.03</v>
@@ -6886,7 +6886,7 @@
         <v>1.76</v>
       </c>
       <c r="AG40">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="O42">
         <v>3.65</v>
@@ -7173,7 +7173,7 @@
         <v>1.3</v>
       </c>
       <c r="T42">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="U42">
         <v>2.58</v>
@@ -7188,10 +7188,10 @@
         <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z42">
-        <v>3.92</v>
+        <v>3.95</v>
       </c>
       <c r="AA42">
         <v>1.74</v>
@@ -7206,7 +7206,7 @@
         <v>1.38</v>
       </c>
       <c r="AE42">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF42">
         <v>1.65</v>

--- a/jogos_2026-08-17.xlsx
+++ b/jogos_2026-08-17.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU42"/>
+  <dimension ref="A1:AU41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.8</v>
+        <v>2.95</v>
       </c>
       <c r="O22">
-        <v>4.55</v>
+        <v>3.68</v>
       </c>
       <c r="P22">
-        <v>3.35</v>
+        <v>1.93</v>
       </c>
       <c r="Q22">
-        <v>2.25</v>
+        <v>3.14</v>
       </c>
       <c r="R22">
-        <v>2.75</v>
+        <v>2.34</v>
       </c>
       <c r="S22">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="T22">
-        <v>4.75</v>
+        <v>3.52</v>
       </c>
       <c r="U22">
-        <v>1.84</v>
+        <v>2.23</v>
       </c>
       <c r="V22">
-        <v>1.98</v>
+        <v>1.62</v>
       </c>
       <c r="W22">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="X22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y22">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="Z22">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="AA22">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AB22">
-        <v>3.33</v>
+        <v>2.4</v>
       </c>
       <c r="AC22">
-        <v>1.78</v>
+        <v>2.29</v>
       </c>
       <c r="AD22">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="AE22">
-        <v>1.42</v>
+        <v>1.2</v>
       </c>
       <c r="AF22">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AG22">
-        <v>3.08</v>
+        <v>2.48</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>1.29</v>
       </c>
       <c r="AK22">
-        <v>1.95</v>
+        <v>1.27</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="O23">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="P23">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="Q23">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="R23">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="S23">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="T23">
-        <v>3.52</v>
+        <v>3.9</v>
       </c>
       <c r="U23">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="V23">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="W23">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="X23">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z23">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AA23">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AB23">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="AC23">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="AD23">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AE23">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AF23">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AG23">
-        <v>2.48</v>
+        <v>2.65</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AK23">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="O24">
-        <v>3.5</v>
+        <v>4.55</v>
       </c>
       <c r="P24">
-        <v>2.2</v>
+        <v>3.35</v>
       </c>
       <c r="Q24">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="R24">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="S24">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="T24">
-        <v>3.9</v>
+        <v>4.75</v>
       </c>
       <c r="U24">
-        <v>2.1</v>
+        <v>1.84</v>
       </c>
       <c r="V24">
-        <v>1.65</v>
+        <v>1.98</v>
       </c>
       <c r="W24">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="X24">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="Z24">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA24">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="AB24">
-        <v>2.63</v>
+        <v>3.33</v>
       </c>
       <c r="AC24">
-        <v>2.15</v>
+        <v>1.78</v>
       </c>
       <c r="AD24">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AE24">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AF24">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AG24">
-        <v>2.65</v>
+        <v>3.08</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AK24">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="O30">
+        <v>3.45</v>
+      </c>
+      <c r="P30">
+        <v>2.87</v>
+      </c>
+      <c r="Q30">
         <v>2.88</v>
       </c>
-      <c r="P30">
-        <v>2.95</v>
-      </c>
-      <c r="Q30">
-        <v>3.16</v>
-      </c>
       <c r="R30">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="S30">
+        <v>1.3</v>
+      </c>
+      <c r="T30">
+        <v>3.1</v>
+      </c>
+      <c r="U30">
+        <v>2.55</v>
+      </c>
+      <c r="V30">
         <v>1.45</v>
       </c>
-      <c r="T30">
-        <v>2.36</v>
-      </c>
-      <c r="U30">
-        <v>3.3</v>
-      </c>
-      <c r="V30">
-        <v>1.3</v>
-      </c>
       <c r="W30">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X30">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y30">
-        <v>1.39</v>
+        <v>1.21</v>
       </c>
       <c r="Z30">
-        <v>2.72</v>
+        <v>4.17</v>
       </c>
       <c r="AA30">
-        <v>2.41</v>
+        <v>1.76</v>
       </c>
       <c r="AB30">
-        <v>1.61</v>
+        <v>2.09</v>
       </c>
       <c r="AC30">
-        <v>4.15</v>
+        <v>2.8</v>
       </c>
       <c r="AD30">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="AE30">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AF30">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AG30">
-        <v>1.81</v>
+        <v>2.25</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK30">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5315,27 +5315,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.3</v>
+        <v>1.84</v>
       </c>
       <c r="O31">
-        <v>3.45</v>
+        <v>4.15</v>
       </c>
       <c r="P31">
-        <v>2.87</v>
+        <v>3.25</v>
       </c>
       <c r="Q31">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="R31">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="S31">
+        <v>1.13</v>
+      </c>
+      <c r="T31">
+        <v>5.5</v>
+      </c>
+      <c r="U31">
+        <v>1.73</v>
+      </c>
+      <c r="V31">
+        <v>2.03</v>
+      </c>
+      <c r="W31">
         <v>1.3</v>
       </c>
-      <c r="T31">
-        <v>3.1</v>
-      </c>
-      <c r="U31">
-        <v>2.55</v>
-      </c>
-      <c r="V31">
-        <v>1.45</v>
-      </c>
-      <c r="W31">
-        <v>1.08</v>
-      </c>
       <c r="X31">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
+        <v>1.02</v>
+      </c>
+      <c r="Z31">
+        <v>7.8</v>
+      </c>
+      <c r="AA31">
         <v>1.21</v>
       </c>
-      <c r="Z31">
-        <v>4.17</v>
-      </c>
-      <c r="AA31">
-        <v>1.76</v>
-      </c>
       <c r="AB31">
-        <v>2.09</v>
+        <v>3.58</v>
       </c>
       <c r="AC31">
-        <v>2.8</v>
+        <v>1.62</v>
       </c>
       <c r="AD31">
-        <v>1.4</v>
+        <v>2.24</v>
       </c>
       <c r="AE31">
-        <v>1.12</v>
+        <v>1.51</v>
       </c>
       <c r="AF31">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AG31">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AK31">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>2026-08-17 16:00:00</t>
+          <t>2026-08-17 16:15:00</t>
         </is>
       </c>
     </row>
@@ -5483,22 +5483,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,80 +5525,80 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.84</v>
+        <v>9.4</v>
       </c>
       <c r="O32">
-        <v>4.15</v>
+        <v>5.3</v>
       </c>
       <c r="P32">
-        <v>3.25</v>
+        <v>1.21</v>
       </c>
       <c r="Q32">
-        <v>2.25</v>
+        <v>9.9</v>
       </c>
       <c r="R32">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="S32">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="T32">
-        <v>5.5</v>
+        <v>3.4</v>
       </c>
       <c r="U32">
-        <v>1.73</v>
+        <v>2.38</v>
       </c>
       <c r="V32">
-        <v>2.03</v>
+        <v>1.55</v>
       </c>
       <c r="W32">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="X32">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
+        <v>1.17</v>
+      </c>
+      <c r="Z32">
+        <v>4.6</v>
+      </c>
+      <c r="AA32">
+        <v>1.53</v>
+      </c>
+      <c r="AB32">
+        <v>2.31</v>
+      </c>
+      <c r="AC32">
+        <v>2.38</v>
+      </c>
+      <c r="AD32">
+        <v>1.47</v>
+      </c>
+      <c r="AE32">
+        <v>1.2</v>
+      </c>
+      <c r="AF32">
+        <v>2.1</v>
+      </c>
+      <c r="AG32">
+        <v>1.67</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ32">
+        <v>1.08</v>
+      </c>
+      <c r="AK32">
         <v>1.02</v>
-      </c>
-      <c r="Z32">
-        <v>7.8</v>
-      </c>
-      <c r="AA32">
-        <v>1.21</v>
-      </c>
-      <c r="AB32">
-        <v>3.58</v>
-      </c>
-      <c r="AC32">
-        <v>1.62</v>
-      </c>
-      <c r="AD32">
-        <v>2.24</v>
-      </c>
-      <c r="AE32">
-        <v>1.51</v>
-      </c>
-      <c r="AF32">
-        <v>1.25</v>
-      </c>
-      <c r="AG32">
-        <v>3.4</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ32">
-        <v>1.22</v>
-      </c>
-      <c r="AK32">
-        <v>1.85</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>9.4</v>
+        <v>1.3</v>
       </c>
       <c r="O33">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="P33">
-        <v>1.21</v>
+        <v>7.8</v>
       </c>
       <c r="Q33">
-        <v>9.9</v>
+        <v>1.71</v>
       </c>
       <c r="R33">
-        <v>2.87</v>
+        <v>2.55</v>
       </c>
       <c r="S33">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="T33">
-        <v>3.4</v>
+        <v>3.26</v>
       </c>
       <c r="U33">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="V33">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="W33">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X33">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z33">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AA33">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AB33">
-        <v>2.31</v>
+        <v>2.12</v>
       </c>
       <c r="AC33">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="AD33">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AE33">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AF33">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AG33">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AK33">
-        <v>1.02</v>
+        <v>3.2</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>2026-08-17 16:15:00</t>
+          <t>2026-08-17 16:30:00</t>
         </is>
       </c>
     </row>
@@ -5804,27 +5804,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.3</v>
+        <v>2.49</v>
       </c>
       <c r="O34">
-        <v>4.8</v>
+        <v>3.32</v>
       </c>
       <c r="P34">
-        <v>7.8</v>
+        <v>2.45</v>
       </c>
       <c r="Q34">
-        <v>1.71</v>
+        <v>3.16</v>
       </c>
       <c r="R34">
-        <v>2.55</v>
+        <v>2.12</v>
       </c>
       <c r="S34">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T34">
-        <v>3.26</v>
+        <v>2.88</v>
       </c>
       <c r="U34">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="V34">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="W34">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X34">
         <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="Z34">
-        <v>4.5</v>
+        <v>3.34</v>
       </c>
       <c r="AA34">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AB34">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="AC34">
-        <v>2.7</v>
+        <v>3.08</v>
       </c>
       <c r="AD34">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="AE34">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="AF34">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AG34">
-        <v>1.7</v>
+        <v>2.06</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.04</v>
+        <v>1.24</v>
       </c>
       <c r="AK34">
-        <v>3.2</v>
+        <v>1.42</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>2026-08-17 16:30:00</t>
+          <t>2026-08-17 19:00:00</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,80 +6014,80 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.49</v>
+        <v>2.1</v>
       </c>
       <c r="O35">
-        <v>3.32</v>
+        <v>3.24</v>
       </c>
       <c r="P35">
-        <v>2.45</v>
+        <v>3.18</v>
       </c>
       <c r="Q35">
-        <v>3.16</v>
+        <v>2.7</v>
       </c>
       <c r="R35">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="S35">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T35">
         <v>2.88</v>
       </c>
       <c r="U35">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="V35">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W35">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X35">
         <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Z35">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="AA35">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AB35">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AC35">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AD35">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE35">
         <v>1.07</v>
       </c>
       <c r="AF35">
+        <v>1.72</v>
+      </c>
+      <c r="AG35">
+        <v>1.98</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ35">
+        <v>1.25</v>
+      </c>
+      <c r="AK35">
         <v>1.67</v>
-      </c>
-      <c r="AG35">
-        <v>2.06</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ35">
-        <v>1.24</v>
-      </c>
-      <c r="AK35">
-        <v>1.42</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6130,12 +6130,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.1</v>
+        <v>1.64</v>
       </c>
       <c r="O36">
-        <v>3.24</v>
+        <v>3.96</v>
       </c>
       <c r="P36">
-        <v>3.18</v>
+        <v>5.61</v>
       </c>
       <c r="Q36">
-        <v>2.7</v>
+        <v>2.08</v>
       </c>
       <c r="R36">
-        <v>2.07</v>
+        <v>2.24</v>
       </c>
       <c r="S36">
         <v>1.36</v>
       </c>
       <c r="T36">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="U36">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="V36">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="W36">
         <v>1.06</v>
       </c>
       <c r="X36">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z36">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="AA36">
+        <v>1.83</v>
+      </c>
+      <c r="AB36">
         <v>1.89</v>
       </c>
-      <c r="AB36">
-        <v>1.81</v>
-      </c>
       <c r="AC36">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="AD36">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AE36">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF36">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AG36">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK36">
-        <v>1.67</v>
+        <v>2.38</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>2026-08-17 19:00:00</t>
+          <t>2026-08-17 20:00:00</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="O37">
-        <v>3.96</v>
+        <v>3.45</v>
       </c>
       <c r="P37">
-        <v>5.61</v>
+        <v>3.9</v>
       </c>
       <c r="Q37">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="R37">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="S37">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T37">
-        <v>2.9</v>
+        <v>2.71</v>
       </c>
       <c r="U37">
-        <v>2.6</v>
+        <v>2.71</v>
       </c>
       <c r="V37">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W37">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X37">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z37">
-        <v>3.65</v>
+        <v>3.42</v>
       </c>
       <c r="AA37">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="AB37">
+        <v>1.7</v>
+      </c>
+      <c r="AC37">
+        <v>3.04</v>
+      </c>
+      <c r="AD37">
+        <v>1.29</v>
+      </c>
+      <c r="AE37">
+        <v>1.07</v>
+      </c>
+      <c r="AF37">
         <v>1.89</v>
       </c>
-      <c r="AC37">
-        <v>3</v>
-      </c>
-      <c r="AD37">
-        <v>1.33</v>
-      </c>
-      <c r="AE37">
-        <v>1.13</v>
-      </c>
-      <c r="AF37">
-        <v>1.85</v>
-      </c>
       <c r="AG37">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK37">
-        <v>2.38</v>
+        <v>1.93</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="O38">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="P38">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="Q38">
-        <v>2.3</v>
+        <v>2.95</v>
       </c>
       <c r="R38">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="S38">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="T38">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="U38">
-        <v>2.71</v>
+        <v>3.08</v>
       </c>
       <c r="V38">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="W38">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X38">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="Z38">
-        <v>3.42</v>
+        <v>2.85</v>
       </c>
       <c r="AA38">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AB38">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AC38">
-        <v>3.04</v>
+        <v>3.7</v>
       </c>
       <c r="AD38">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AE38">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AF38">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AG38">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AK38">
-        <v>1.93</v>
+        <v>1.53</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6619,12 +6619,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,52 +6666,52 @@
         </is>
       </c>
       <c r="N39">
+        <v>2.7</v>
+      </c>
+      <c r="O39">
+        <v>3.1</v>
+      </c>
+      <c r="P39">
+        <v>2.35</v>
+      </c>
+      <c r="Q39">
+        <v>3.3</v>
+      </c>
+      <c r="R39">
         <v>2</v>
       </c>
-      <c r="O39">
-        <v>3.2</v>
-      </c>
-      <c r="P39">
-        <v>3.3</v>
-      </c>
-      <c r="Q39">
-        <v>2.95</v>
-      </c>
-      <c r="R39">
-        <v>1.88</v>
-      </c>
       <c r="S39">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T39">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="U39">
-        <v>3.08</v>
+        <v>2.8</v>
       </c>
       <c r="V39">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W39">
         <v>1.04</v>
       </c>
       <c r="X39">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y39">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z39">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="AA39">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AB39">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AC39">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AD39">
         <v>1.22</v>
@@ -6720,10 +6720,10 @@
         <v>1.03</v>
       </c>
       <c r="AF39">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="AG39">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AK39">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>2026-08-17 20:00:00</t>
+          <t>2026-08-17 21:00:00</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O40">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P40">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q40">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R40">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S40">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T40">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U40">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="V40">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W40">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X40">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y40">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z40">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AA40">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AB40">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC40">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD40">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE40">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF40">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG40">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK40">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6933,7 +6933,7 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>2026-08-17 21:00:00</t>
+          <t>2026-08-17 21:30:00</t>
         </is>
       </c>
     </row>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7095,169 +7095,6 @@
         <v>0</v>
       </c>
       <c r="AU41" t="inlineStr">
-        <is>
-          <t>2026-08-17 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Chile Primera División</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Palestino</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Huachipato</t>
-        </is>
-      </c>
-      <c r="G42">
-        <v>0</v>
-      </c>
-      <c r="H42">
-        <v>0</v>
-      </c>
-      <c r="I42">
-        <v>0</v>
-      </c>
-      <c r="J42">
-        <v>0</v>
-      </c>
-      <c r="K42">
-        <v>0</v>
-      </c>
-      <c r="L42">
-        <v>0</v>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N42">
-        <v>1.72</v>
-      </c>
-      <c r="O42">
-        <v>3.65</v>
-      </c>
-      <c r="P42">
-        <v>4.15</v>
-      </c>
-      <c r="Q42">
-        <v>2.3</v>
-      </c>
-      <c r="R42">
-        <v>2.3</v>
-      </c>
-      <c r="S42">
-        <v>1.3</v>
-      </c>
-      <c r="T42">
-        <v>3.2</v>
-      </c>
-      <c r="U42">
-        <v>2.58</v>
-      </c>
-      <c r="V42">
-        <v>1.5</v>
-      </c>
-      <c r="W42">
-        <v>1.11</v>
-      </c>
-      <c r="X42">
-        <v>1.01</v>
-      </c>
-      <c r="Y42">
-        <v>1.22</v>
-      </c>
-      <c r="Z42">
-        <v>3.95</v>
-      </c>
-      <c r="AA42">
-        <v>1.74</v>
-      </c>
-      <c r="AB42">
-        <v>2.1</v>
-      </c>
-      <c r="AC42">
-        <v>2.69</v>
-      </c>
-      <c r="AD42">
-        <v>1.38</v>
-      </c>
-      <c r="AE42">
-        <v>1.12</v>
-      </c>
-      <c r="AF42">
-        <v>1.65</v>
-      </c>
-      <c r="AG42">
-        <v>2.1</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ42">
-        <v>1.15</v>
-      </c>
-      <c r="AK42">
-        <v>1.9</v>
-      </c>
-      <c r="AL42">
-        <v>0</v>
-      </c>
-      <c r="AM42">
-        <v>-1</v>
-      </c>
-      <c r="AN42">
-        <v>-1</v>
-      </c>
-      <c r="AO42">
-        <v>-1</v>
-      </c>
-      <c r="AP42">
-        <v>-1</v>
-      </c>
-      <c r="AQ42">
-        <v>0</v>
-      </c>
-      <c r="AR42">
-        <v>0</v>
-      </c>
-      <c r="AS42">
-        <v>0</v>
-      </c>
-      <c r="AT42">
-        <v>0</v>
-      </c>
-      <c r="AU42" t="inlineStr">
         <is>
           <t>2026-08-17 21:30:00</t>
         </is>

--- a/jogos_2026-08-17.xlsx
+++ b/jogos_2026-08-17.xlsx
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="O8">
         <v>3.5</v>
@@ -1622,16 +1622,16 @@
         <v>1.87</v>
       </c>
       <c r="Q8">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="R8">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="S8">
         <v>1.3</v>
       </c>
       <c r="T8">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="U8">
         <v>2.45</v>
@@ -1640,13 +1640,13 @@
         <v>1.5</v>
       </c>
       <c r="W8">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X8">
         <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z8">
         <v>4</v>
@@ -1661,10 +1661,10 @@
         <v>2.7</v>
       </c>
       <c r="AD8">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE8">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF8">
         <v>1.58</v>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK8">
         <v>1.27</v>
@@ -1788,19 +1788,19 @@
         <v>2.5</v>
       </c>
       <c r="R9">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="S9">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T9">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="U9">
         <v>2.9</v>
       </c>
       <c r="V9">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W9">
         <v>1.03</v>
@@ -1809,32 +1809,32 @@
         <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Z9">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AA9">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AB9">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AC9">
-        <v>3.67</v>
+        <v>3.8</v>
       </c>
       <c r="AD9">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AE9">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF9">
+        <v>1.9</v>
+      </c>
+      <c r="AG9">
         <v>1.85</v>
       </c>
-      <c r="AG9">
-        <v>1.82</v>
-      </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK9">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="Q12">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="R12">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="S12">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T12">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="U12">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="V12">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W12">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X12">
         <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="Z12">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="AA12">
-        <v>1.79</v>
+        <v>1.96</v>
       </c>
       <c r="AB12">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AC12">
-        <v>2.88</v>
+        <v>3.28</v>
       </c>
       <c r="AD12">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AE12">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF12">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AG12">
-        <v>2.06</v>
+        <v>1.83</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK12">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2597,10 +2597,10 @@
         <v>3.2</v>
       </c>
       <c r="P14">
-        <v>4.62</v>
+        <v>4.2</v>
       </c>
       <c r="Q14">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R14">
         <v>1.95</v>
@@ -2609,10 +2609,10 @@
         <v>1.4</v>
       </c>
       <c r="T14">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="U14">
-        <v>2.91</v>
+        <v>3.28</v>
       </c>
       <c r="V14">
         <v>1.35</v>
@@ -2621,7 +2621,7 @@
         <v>1.06</v>
       </c>
       <c r="X14">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y14">
         <v>1.4</v>
@@ -2633,22 +2633,22 @@
         <v>2.2</v>
       </c>
       <c r="AB14">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC14">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AD14">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE14">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF14">
         <v>1.95</v>
       </c>
       <c r="AG14">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK14">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2917,19 +2917,19 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="O16">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="P16">
-        <v>5.3</v>
+        <v>6.5</v>
       </c>
       <c r="Q16">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="R16">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="S16">
         <v>1.25</v>
@@ -2938,13 +2938,13 @@
         <v>3.5</v>
       </c>
       <c r="U16">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="V16">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="W16">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X16">
         <v>1.03</v>
@@ -2965,7 +2965,7 @@
         <v>2.38</v>
       </c>
       <c r="AD16">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AE16">
         <v>1.18</v>
@@ -2974,7 +2974,7 @@
         <v>1.7</v>
       </c>
       <c r="AG16">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="O21">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="P21">
-        <v>3.8</v>
+        <v>4.46</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3895,34 +3895,34 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.95</v>
+        <v>3.35</v>
       </c>
       <c r="O22">
-        <v>3.68</v>
+        <v>3.74</v>
       </c>
       <c r="P22">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="Q22">
-        <v>3.14</v>
+        <v>3.6</v>
       </c>
       <c r="R22">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="S22">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T22">
-        <v>3.52</v>
+        <v>3.8</v>
       </c>
       <c r="U22">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="V22">
         <v>1.62</v>
       </c>
       <c r="W22">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X22">
         <v>1.03</v>
@@ -3931,28 +3931,28 @@
         <v>1.14</v>
       </c>
       <c r="Z22">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AA22">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AB22">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AC22">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="AD22">
         <v>1.57</v>
       </c>
       <c r="AE22">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF22">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AG22">
-        <v>2.48</v>
+        <v>2.53</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>1.29</v>
       </c>
       <c r="AK22">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,25 +4058,25 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="O23">
         <v>3.5</v>
       </c>
       <c r="P23">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q23">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="R23">
         <v>2.4</v>
       </c>
       <c r="S23">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T23">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U23">
         <v>2.1</v>
@@ -4085,31 +4085,31 @@
         <v>1.65</v>
       </c>
       <c r="W23">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X23">
         <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z23">
-        <v>5.5</v>
+        <v>5.45</v>
       </c>
       <c r="AA23">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AB23">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="AC23">
         <v>2.15</v>
       </c>
       <c r="AD23">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AE23">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AF23">
         <v>1.39</v>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK23">
         <v>1.4</v>
@@ -4221,34 +4221,34 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="O24">
-        <v>4.55</v>
+        <v>4.1</v>
       </c>
       <c r="P24">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="Q24">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="R24">
         <v>2.75</v>
       </c>
       <c r="S24">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="T24">
         <v>4.75</v>
       </c>
       <c r="U24">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="V24">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="W24">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X24">
         <v>1.01</v>
@@ -4257,28 +4257,28 @@
         <v>1.03</v>
       </c>
       <c r="Z24">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="AA24">
         <v>1.3</v>
       </c>
       <c r="AB24">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="AC24">
         <v>1.78</v>
       </c>
       <c r="AD24">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AE24">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AF24">
         <v>1.33</v>
       </c>
       <c r="AG24">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AK24">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="O25">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P25">
-        <v>4.96</v>
+        <v>3.81</v>
       </c>
       <c r="Q25">
         <v>2.38</v>
@@ -4423,19 +4423,19 @@
         <v>3.08</v>
       </c>
       <c r="AA25">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AB25">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AC25">
-        <v>3.46</v>
+        <v>3.4</v>
       </c>
       <c r="AD25">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE25">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF25">
         <v>1.83</v>
@@ -4547,16 +4547,16 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="O26">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P26">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="Q26">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="R26">
         <v>2.18</v>
@@ -4568,19 +4568,19 @@
         <v>2.65</v>
       </c>
       <c r="U26">
-        <v>2.94</v>
+        <v>2.75</v>
       </c>
       <c r="V26">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W26">
         <v>1.03</v>
       </c>
       <c r="X26">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z26">
         <v>3.1</v>
@@ -4589,13 +4589,13 @@
         <v>2.1</v>
       </c>
       <c r="AB26">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AC26">
-        <v>3.63</v>
+        <v>3.64</v>
       </c>
       <c r="AD26">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AE26">
         <v>1.04</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="O33">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="P33">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="Q33">
         <v>1.71</v>
@@ -5703,16 +5703,16 @@
         <v>2.55</v>
       </c>
       <c r="S33">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T33">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="U33">
         <v>2.5</v>
       </c>
       <c r="V33">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W33">
         <v>1.11</v>
@@ -5727,10 +5727,10 @@
         <v>4.5</v>
       </c>
       <c r="AA33">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AB33">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AC33">
         <v>2.7</v>
@@ -5745,7 +5745,7 @@
         <v>2</v>
       </c>
       <c r="AG33">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AK33">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AL33">
         <v>0</v>

--- a/jogos_2026-08-17.xlsx
+++ b/jogos_2026-08-17.xlsx
@@ -970,55 +970,55 @@
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R4">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W4">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y4">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z4">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AA4">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AC4">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD4">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE4">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK4">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1945,10 +1945,10 @@
         <v>3.62</v>
       </c>
       <c r="P10">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
       <c r="Q10">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="R10">
         <v>2.03</v>
@@ -1957,10 +1957,10 @@
         <v>1.44</v>
       </c>
       <c r="T10">
-        <v>2.69</v>
+        <v>2.56</v>
       </c>
       <c r="U10">
-        <v>3.24</v>
+        <v>3.05</v>
       </c>
       <c r="V10">
         <v>1.32</v>
@@ -1972,31 +1972,31 @@
         <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z10">
-        <v>2.78</v>
+        <v>2.83</v>
       </c>
       <c r="AA10">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AB10">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AC10">
-        <v>3.74</v>
+        <v>3.68</v>
       </c>
       <c r="AD10">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE10">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF10">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AG10">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK10">
-        <v>2.03</v>
+        <v>2.22</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2428,31 +2428,31 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.35</v>
+        <v>2.21</v>
       </c>
       <c r="O13">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="P13">
         <v>2.95</v>
       </c>
       <c r="Q13">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="R13">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S13">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T13">
-        <v>2.84</v>
+        <v>2.59</v>
       </c>
       <c r="U13">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="V13">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W13">
         <v>1.07</v>
@@ -2461,22 +2461,22 @@
         <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z13">
         <v>3.28</v>
       </c>
       <c r="AA13">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="AB13">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AC13">
         <v>3.42</v>
       </c>
       <c r="AD13">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE13">
         <v>1.04</v>
@@ -2501,7 +2501,7 @@
         <v>1.36</v>
       </c>
       <c r="AK13">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.2</v>
+        <v>3.44</v>
       </c>
       <c r="O17">
         <v>3.4</v>
@@ -3089,52 +3089,52 @@
         <v>1.94</v>
       </c>
       <c r="Q17">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="R17">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S17">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T17">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="U17">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="V17">
         <v>1.44</v>
       </c>
       <c r="W17">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X17">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z17">
-        <v>3.58</v>
+        <v>3.78</v>
       </c>
       <c r="AA17">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AB17">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AC17">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AD17">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE17">
         <v>1.13</v>
       </c>
       <c r="AF17">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG17">
         <v>2.1</v>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.69</v>
+        <v>1.3</v>
       </c>
       <c r="AK17">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3569,7 +3569,7 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="O20">
         <v>3.45</v>
@@ -3578,28 +3578,28 @@
         <v>3.2</v>
       </c>
       <c r="Q20">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="R20">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="S20">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T20">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="U20">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="V20">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W20">
         <v>1.08</v>
       </c>
       <c r="X20">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y20">
         <v>1.19</v>
@@ -3614,19 +3614,19 @@
         <v>2.03</v>
       </c>
       <c r="AC20">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AD20">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AE20">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF20">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG20">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>1.3</v>
       </c>
       <c r="AK20">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="O28">
         <v>4</v>
       </c>
       <c r="P28">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="Q28">
         <v>2</v>
       </c>
       <c r="R28">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S28">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="T28">
         <v>3.6</v>
       </c>
       <c r="U28">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="V28">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="W28">
         <v>1.11</v>
       </c>
       <c r="X28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z28">
-        <v>4.33</v>
+        <v>4.31</v>
       </c>
       <c r="AA28">
         <v>1.66</v>
       </c>
       <c r="AB28">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AC28">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AD28">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AE28">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF28">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG28">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK28">
         <v>2.38</v>
@@ -5045,49 +5045,49 @@
         <v>2.95</v>
       </c>
       <c r="Q29">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="R29">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="S29">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T29">
-        <v>2.36</v>
+        <v>2.7</v>
       </c>
       <c r="U29">
         <v>3.3</v>
       </c>
       <c r="V29">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W29">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X29">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y29">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="Z29">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="AA29">
         <v>2.41</v>
       </c>
       <c r="AB29">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AC29">
-        <v>4.15</v>
+        <v>4.5</v>
       </c>
       <c r="AD29">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE29">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF29">
         <v>1.91</v>
@@ -5109,7 +5109,7 @@
         <v>1.3</v>
       </c>
       <c r="AK29">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5202,10 +5202,10 @@
         <v>2.3</v>
       </c>
       <c r="O30">
-        <v>3.45</v>
+        <v>3.41</v>
       </c>
       <c r="P30">
-        <v>2.87</v>
+        <v>2.61</v>
       </c>
       <c r="Q30">
         <v>2.88</v>
@@ -5214,10 +5214,10 @@
         <v>2.25</v>
       </c>
       <c r="S30">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T30">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="U30">
         <v>2.55</v>
@@ -5229,10 +5229,10 @@
         <v>1.08</v>
       </c>
       <c r="X30">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="Z30">
         <v>4.17</v>
@@ -5253,10 +5253,10 @@
         <v>1.12</v>
       </c>
       <c r="AF30">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG30">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AK30">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5525,61 +5525,61 @@
         </is>
       </c>
       <c r="N32">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="O32">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="P32">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Q32">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="R32">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="S32">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T32">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U32">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="V32">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W32">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X32">
         <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z32">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="AA32">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AB32">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="AC32">
         <v>2.38</v>
       </c>
       <c r="AD32">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="AE32">
         <v>1.2</v>
       </c>
       <c r="AF32">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="AG32">
         <v>1.67</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.08</v>
+        <v>4.74</v>
       </c>
       <c r="AK32">
         <v>1.02</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,80 +5851,80 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.49</v>
+        <v>2.1</v>
       </c>
       <c r="O34">
-        <v>3.32</v>
+        <v>3.24</v>
       </c>
       <c r="P34">
-        <v>2.45</v>
+        <v>3.18</v>
       </c>
       <c r="Q34">
-        <v>3.16</v>
+        <v>2.7</v>
       </c>
       <c r="R34">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="S34">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T34">
         <v>2.88</v>
       </c>
       <c r="U34">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="V34">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W34">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X34">
         <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Z34">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="AA34">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AB34">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AC34">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AD34">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE34">
         <v>1.07</v>
       </c>
       <c r="AF34">
+        <v>1.72</v>
+      </c>
+      <c r="AG34">
+        <v>1.98</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ34">
+        <v>1.25</v>
+      </c>
+      <c r="AK34">
         <v>1.67</v>
-      </c>
-      <c r="AG34">
-        <v>2.06</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ34">
-        <v>1.24</v>
-      </c>
-      <c r="AK34">
-        <v>1.42</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.1</v>
+        <v>2.49</v>
       </c>
       <c r="O35">
-        <v>3.24</v>
+        <v>3.32</v>
       </c>
       <c r="P35">
-        <v>3.18</v>
+        <v>2.45</v>
       </c>
       <c r="Q35">
-        <v>2.7</v>
+        <v>3.16</v>
       </c>
       <c r="R35">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="S35">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T35">
         <v>2.88</v>
       </c>
       <c r="U35">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="V35">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W35">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X35">
         <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Z35">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="AA35">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AB35">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AC35">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AD35">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE35">
         <v>1.07</v>
       </c>
       <c r="AF35">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AG35">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK35">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6349,28 +6349,28 @@
         <v>3.9</v>
       </c>
       <c r="Q37">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R37">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="S37">
         <v>1.37</v>
       </c>
       <c r="T37">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="U37">
-        <v>2.71</v>
+        <v>2.59</v>
       </c>
       <c r="V37">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W37">
         <v>1.08</v>
       </c>
       <c r="X37">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y37">
         <v>1.23</v>
@@ -6379,22 +6379,22 @@
         <v>3.42</v>
       </c>
       <c r="AA37">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AB37">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AC37">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="AD37">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE37">
         <v>1.07</v>
       </c>
       <c r="AF37">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="AG37">
         <v>1.9</v>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK37">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6512,10 +6512,10 @@
         <v>3.3</v>
       </c>
       <c r="Q38">
-        <v>2.95</v>
+        <v>2.81</v>
       </c>
       <c r="R38">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="S38">
         <v>1.42</v>
@@ -6530,7 +6530,7 @@
         <v>1.29</v>
       </c>
       <c r="W38">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X38">
         <v>1.02</v>
@@ -6542,10 +6542,10 @@
         <v>2.85</v>
       </c>
       <c r="AA38">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB38">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AC38">
         <v>3.7</v>
@@ -6554,13 +6554,13 @@
         <v>1.22</v>
       </c>
       <c r="AE38">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF38">
         <v>1.82</v>
       </c>
       <c r="AG38">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>

--- a/jogos_2026-08-17.xlsx
+++ b/jogos_2026-08-17.xlsx
@@ -2274,71 +2274,71 @@
         <v>4.45</v>
       </c>
       <c r="Q12">
-        <v>2.38</v>
+        <v>2.21</v>
       </c>
       <c r="R12">
-        <v>2.11</v>
+        <v>2.36</v>
       </c>
       <c r="S12">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T12">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="U12">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="V12">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="W12">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y12">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z12">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="AA12">
-        <v>1.96</v>
+        <v>1.77</v>
       </c>
       <c r="AB12">
+        <v>2.02</v>
+      </c>
+      <c r="AC12">
+        <v>3</v>
+      </c>
+      <c r="AD12">
+        <v>1.34</v>
+      </c>
+      <c r="AE12">
+        <v>1.1</v>
+      </c>
+      <c r="AF12">
         <v>1.75</v>
       </c>
-      <c r="AC12">
-        <v>3.28</v>
-      </c>
-      <c r="AD12">
+      <c r="AG12">
+        <v>1.95</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12">
         <v>1.25</v>
       </c>
-      <c r="AE12">
-        <v>1.06</v>
-      </c>
-      <c r="AF12">
-        <v>1.83</v>
-      </c>
-      <c r="AG12">
-        <v>1.83</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12">
-        <v>1.17</v>
-      </c>
       <c r="AK12">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2757,16 +2757,16 @@
         <v>1.3</v>
       </c>
       <c r="O15">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="P15">
-        <v>7</v>
+        <v>7.9</v>
       </c>
       <c r="Q15">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R15">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="S15">
         <v>1.18</v>
@@ -2775,10 +2775,10 @@
         <v>4.05</v>
       </c>
       <c r="U15">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="V15">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W15">
         <v>1.16</v>
@@ -2787,31 +2787,31 @@
         <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z15">
-        <v>6.05</v>
+        <v>6.13</v>
       </c>
       <c r="AA15">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AB15">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="AC15">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="AD15">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AE15">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AF15">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG15">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -3246,49 +3246,49 @@
         <v>2.15</v>
       </c>
       <c r="O18">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="P18">
-        <v>3.08</v>
+        <v>3.6</v>
       </c>
       <c r="Q18">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="R18">
         <v>1.8</v>
       </c>
       <c r="S18">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="T18">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="U18">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="V18">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="W18">
         <v>1.03</v>
       </c>
       <c r="X18">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Y18">
-        <v>1.71</v>
+        <v>1.56</v>
       </c>
       <c r="Z18">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AA18">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AB18">
         <v>1.31</v>
       </c>
       <c r="AC18">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="AD18">
         <v>1.08</v>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="AK18">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,22 +3406,22 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="O19">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P19">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="Q19">
-        <v>2.49</v>
+        <v>2.28</v>
       </c>
       <c r="R19">
-        <v>2.48</v>
+        <v>2.63</v>
       </c>
       <c r="S19">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T19">
         <v>4.5</v>
@@ -3430,7 +3430,7 @@
         <v>1.91</v>
       </c>
       <c r="V19">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="W19">
         <v>1.22</v>
@@ -3439,7 +3439,7 @@
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Z19">
         <v>6.24</v>
@@ -3460,10 +3460,10 @@
         <v>1.4</v>
       </c>
       <c r="AF19">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AG19">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK19">
         <v>1.73</v>
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="O28">
         <v>4</v>
@@ -4885,19 +4885,19 @@
         <v>2</v>
       </c>
       <c r="R28">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="S28">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T28">
         <v>3.6</v>
       </c>
       <c r="U28">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="V28">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W28">
         <v>1.11</v>
@@ -4912,10 +4912,10 @@
         <v>4.31</v>
       </c>
       <c r="AA28">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB28">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="AC28">
         <v>2.6</v>
@@ -4930,7 +4930,7 @@
         <v>1.67</v>
       </c>
       <c r="AG28">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>1.08</v>
       </c>
       <c r="X30">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y30">
         <v>1.24</v>
@@ -5272,7 +5272,7 @@
         <v>1.4</v>
       </c>
       <c r="AK30">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="O31">
-        <v>4.15</v>
+        <v>3.85</v>
       </c>
       <c r="P31">
-        <v>3.25</v>
+        <v>2.93</v>
       </c>
       <c r="Q31">
         <v>2.25</v>
@@ -5377,16 +5377,16 @@
         <v>2.8</v>
       </c>
       <c r="S31">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="T31">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="U31">
         <v>1.73</v>
       </c>
       <c r="V31">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="W31">
         <v>1.3</v>
@@ -5395,22 +5395,22 @@
         <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Z31">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AA31">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AB31">
-        <v>3.58</v>
+        <v>3.82</v>
       </c>
       <c r="AC31">
         <v>1.62</v>
       </c>
       <c r="AD31">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="AE31">
         <v>1.51</v>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK31">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5528,7 +5528,7 @@
         <v>11</v>
       </c>
       <c r="O32">
-        <v>6.4</v>
+        <v>5.95</v>
       </c>
       <c r="P32">
         <v>1.25</v>
@@ -5582,7 +5582,7 @@
         <v>2.22</v>
       </c>
       <c r="AG32">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5851,19 +5851,19 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.1</v>
+        <v>1.84</v>
       </c>
       <c r="O34">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="P34">
-        <v>3.18</v>
+        <v>3.65</v>
       </c>
       <c r="Q34">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="R34">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="S34">
         <v>1.36</v>
@@ -5872,43 +5872,43 @@
         <v>2.88</v>
       </c>
       <c r="U34">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="V34">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W34">
         <v>1.06</v>
       </c>
       <c r="X34">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z34">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AA34">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="AB34">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AC34">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="AD34">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE34">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF34">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AG34">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK34">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,25 +6014,25 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.49</v>
+        <v>2.09</v>
       </c>
       <c r="O35">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="P35">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="Q35">
-        <v>3.16</v>
+        <v>2.86</v>
       </c>
       <c r="R35">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="S35">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T35">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="U35">
         <v>2.7</v>
@@ -6044,25 +6044,25 @@
         <v>1.07</v>
       </c>
       <c r="X35">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y35">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z35">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="AA35">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB35">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC35">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AD35">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE35">
         <v>1.07</v>
@@ -6071,7 +6071,7 @@
         <v>1.67</v>
       </c>
       <c r="AG35">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AK35">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6192,10 +6192,10 @@
         <v>2.24</v>
       </c>
       <c r="S36">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T36">
-        <v>2.9</v>
+        <v>3.21</v>
       </c>
       <c r="U36">
         <v>2.6</v>
@@ -6204,16 +6204,16 @@
         <v>1.44</v>
       </c>
       <c r="W36">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X36">
         <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z36">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AA36">
         <v>1.83</v>
@@ -6228,7 +6228,7 @@
         <v>1.33</v>
       </c>
       <c r="AE36">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF36">
         <v>1.85</v>
@@ -6675,19 +6675,19 @@
         <v>2.35</v>
       </c>
       <c r="Q39">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R39">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S39">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="T39">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="U39">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="V39">
         <v>1.33</v>
@@ -6696,10 +6696,10 @@
         <v>1.04</v>
       </c>
       <c r="X39">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z39">
         <v>2.88</v>
@@ -6714,16 +6714,16 @@
         <v>3.5</v>
       </c>
       <c r="AD39">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE39">
         <v>1.03</v>
       </c>
       <c r="AF39">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AG39">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="O41">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="P41">
-        <v>4.15</v>
+        <v>4.22</v>
       </c>
       <c r="Q41">
         <v>2.3</v>
@@ -7028,7 +7028,7 @@
         <v>1.22</v>
       </c>
       <c r="Z41">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="AA41">
         <v>1.74</v>
@@ -7037,7 +7037,7 @@
         <v>2.1</v>
       </c>
       <c r="AC41">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="AD41">
         <v>1.38</v>

--- a/jogos_2026-08-17.xlsx
+++ b/jogos_2026-08-17.xlsx
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1827,7 +1827,7 @@
         <v>1.24</v>
       </c>
       <c r="AE9">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF9">
         <v>1.9</v>
@@ -2760,7 +2760,7 @@
         <v>4.8</v>
       </c>
       <c r="P15">
-        <v>7.9</v>
+        <v>7.75</v>
       </c>
       <c r="Q15">
         <v>1.68</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.65</v>
+        <v>1.77</v>
       </c>
       <c r="O23">
+        <v>4.1</v>
+      </c>
+      <c r="P23">
         <v>3.5</v>
       </c>
-      <c r="P23">
+      <c r="Q23">
         <v>2.15</v>
       </c>
-      <c r="Q23">
-        <v>3.22</v>
-      </c>
       <c r="R23">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="S23">
+        <v>1.13</v>
+      </c>
+      <c r="T23">
+        <v>4.75</v>
+      </c>
+      <c r="U23">
+        <v>1.8</v>
+      </c>
+      <c r="V23">
+        <v>1.91</v>
+      </c>
+      <c r="W23">
         <v>1.22</v>
       </c>
-      <c r="T23">
-        <v>4</v>
-      </c>
-      <c r="U23">
-        <v>2.1</v>
-      </c>
-      <c r="V23">
-        <v>1.65</v>
-      </c>
-      <c r="W23">
-        <v>1.14</v>
-      </c>
       <c r="X23">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="Z23">
-        <v>5.45</v>
+        <v>7</v>
       </c>
       <c r="AA23">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="AB23">
-        <v>2.62</v>
+        <v>3.25</v>
       </c>
       <c r="AC23">
-        <v>2.15</v>
+        <v>1.78</v>
       </c>
       <c r="AD23">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="AE23">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AF23">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AG23">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK23">
-        <v>1.4</v>
+        <v>1.87</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,80 +4221,80 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.77</v>
+        <v>2.55</v>
       </c>
       <c r="O24">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="P24">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="Q24">
+        <v>3.22</v>
+      </c>
+      <c r="R24">
+        <v>2.4</v>
+      </c>
+      <c r="S24">
+        <v>1.22</v>
+      </c>
+      <c r="T24">
+        <v>4</v>
+      </c>
+      <c r="U24">
+        <v>2.1</v>
+      </c>
+      <c r="V24">
+        <v>1.65</v>
+      </c>
+      <c r="W24">
+        <v>1.14</v>
+      </c>
+      <c r="X24">
+        <v>1.02</v>
+      </c>
+      <c r="Y24">
+        <v>1.14</v>
+      </c>
+      <c r="Z24">
+        <v>5.45</v>
+      </c>
+      <c r="AA24">
+        <v>1.48</v>
+      </c>
+      <c r="AB24">
+        <v>2.62</v>
+      </c>
+      <c r="AC24">
         <v>2.15</v>
       </c>
-      <c r="R24">
-        <v>2.75</v>
-      </c>
-      <c r="S24">
-        <v>1.13</v>
-      </c>
-      <c r="T24">
-        <v>4.75</v>
-      </c>
-      <c r="U24">
-        <v>1.8</v>
-      </c>
-      <c r="V24">
-        <v>1.91</v>
-      </c>
-      <c r="W24">
-        <v>1.22</v>
-      </c>
-      <c r="X24">
-        <v>1.01</v>
-      </c>
-      <c r="Y24">
-        <v>1.03</v>
-      </c>
-      <c r="Z24">
-        <v>7</v>
-      </c>
-      <c r="AA24">
-        <v>1.3</v>
-      </c>
-      <c r="AB24">
-        <v>3.25</v>
-      </c>
-      <c r="AC24">
-        <v>1.78</v>
-      </c>
       <c r="AD24">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="AE24">
+        <v>1.28</v>
+      </c>
+      <c r="AF24">
+        <v>1.39</v>
+      </c>
+      <c r="AG24">
+        <v>2.65</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24">
+        <v>1.24</v>
+      </c>
+      <c r="AK24">
         <v>1.4</v>
-      </c>
-      <c r="AF24">
-        <v>1.33</v>
-      </c>
-      <c r="AG24">
-        <v>3.1</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ24">
-        <v>1.17</v>
-      </c>
-      <c r="AK24">
-        <v>1.87</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4387,10 +4387,10 @@
         <v>1.73</v>
       </c>
       <c r="O25">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="P25">
-        <v>3.81</v>
+        <v>4.96</v>
       </c>
       <c r="Q25">
         <v>2.38</v>
@@ -4420,10 +4420,10 @@
         <v>1.28</v>
       </c>
       <c r="Z25">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="AA25">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AB25">
         <v>1.75</v>
@@ -5851,31 +5851,31 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="O34">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P34">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="Q34">
         <v>2.4</v>
       </c>
       <c r="R34">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="S34">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T34">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U34">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="V34">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W34">
         <v>1.06</v>
@@ -5884,31 +5884,31 @@
         <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z34">
-        <v>3.08</v>
+        <v>2.97</v>
       </c>
       <c r="AA34">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="AB34">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC34">
         <v>3.1</v>
       </c>
       <c r="AD34">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE34">
         <v>1.08</v>
       </c>
       <c r="AF34">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AG34">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="O40">
         <v>3.45</v>
       </c>
       <c r="P40">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="Q40">
         <v>2.5</v>
@@ -6862,7 +6862,7 @@
         <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z40">
         <v>3.82</v>
@@ -6874,7 +6874,7 @@
         <v>1.95</v>
       </c>
       <c r="AC40">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="AD40">
         <v>1.38</v>

--- a/jogos_2026-08-17.xlsx
+++ b/jogos_2026-08-17.xlsx
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="N4">
-        <v>6.3</v>
+        <v>4.8</v>
       </c>
       <c r="O4">
         <v>3.65</v>
@@ -988,10 +988,10 @@
         <v>1.55</v>
       </c>
       <c r="W4">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X4">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y4">
         <v>1.19</v>
@@ -1616,10 +1616,10 @@
         <v>3.05</v>
       </c>
       <c r="O8">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P8">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="Q8">
         <v>3.64</v>
@@ -1628,10 +1628,10 @@
         <v>2.3</v>
       </c>
       <c r="S8">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T8">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="U8">
         <v>2.45</v>
@@ -1667,7 +1667,7 @@
         <v>1.15</v>
       </c>
       <c r="AF8">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG8">
         <v>2.25</v>
@@ -1794,7 +1794,7 @@
         <v>1.44</v>
       </c>
       <c r="T9">
-        <v>2.56</v>
+        <v>2.76</v>
       </c>
       <c r="U9">
         <v>2.9</v>
@@ -1849,7 +1849,7 @@
         <v>1.2</v>
       </c>
       <c r="AK9">
-        <v>1.73</v>
+        <v>1.96</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="O10">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="P10">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="Q10">
         <v>2.15</v>
@@ -1960,7 +1960,7 @@
         <v>2.56</v>
       </c>
       <c r="U10">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="V10">
         <v>1.32</v>
@@ -1981,10 +1981,10 @@
         <v>2.15</v>
       </c>
       <c r="AB10">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AC10">
-        <v>3.68</v>
+        <v>3.87</v>
       </c>
       <c r="AD10">
         <v>1.2</v>
@@ -2265,43 +2265,43 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="O12">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P12">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="Q12">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="R12">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="S12">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T12">
-        <v>2.91</v>
+        <v>3.2</v>
       </c>
       <c r="U12">
         <v>2.5</v>
       </c>
       <c r="V12">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W12">
         <v>1.11</v>
       </c>
       <c r="X12">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z12">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA12">
         <v>1.77</v>
@@ -2310,19 +2310,19 @@
         <v>2.02</v>
       </c>
       <c r="AC12">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="AD12">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AE12">
         <v>1.1</v>
       </c>
       <c r="AF12">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AG12">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="O13">
         <v>3.2</v>
       </c>
       <c r="P13">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -2443,31 +2443,31 @@
         <v>2.1</v>
       </c>
       <c r="S13">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T13">
         <v>2.59</v>
       </c>
       <c r="U13">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="V13">
         <v>1.36</v>
       </c>
       <c r="W13">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X13">
         <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z13">
         <v>3.28</v>
       </c>
       <c r="AA13">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="AB13">
         <v>1.72</v>
@@ -2501,7 +2501,7 @@
         <v>1.36</v>
       </c>
       <c r="AK13">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,19 +2591,19 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="O14">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="P14">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Q14">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="R14">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="S14">
         <v>1.4</v>
@@ -2624,7 +2624,7 @@
         <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z14">
         <v>2.85</v>
@@ -2633,13 +2633,13 @@
         <v>2.2</v>
       </c>
       <c r="AB14">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC14">
-        <v>4.2</v>
+        <v>3.54</v>
       </c>
       <c r="AD14">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AE14">
         <v>1.07</v>
@@ -2648,7 +2648,7 @@
         <v>1.95</v>
       </c>
       <c r="AG14">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>1.2</v>
       </c>
       <c r="AK14">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="O16">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="P16">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="Q16">
         <v>1.93</v>
       </c>
       <c r="R16">
-        <v>2.47</v>
+        <v>2.32</v>
       </c>
       <c r="S16">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T16">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="U16">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="V16">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="W16">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X16">
         <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="Z16">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AA16">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB16">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AC16">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AD16">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AE16">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF16">
         <v>1.7</v>
       </c>
       <c r="AG16">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>1.17</v>
       </c>
       <c r="AK16">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,61 +3080,61 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.44</v>
+        <v>3.2</v>
       </c>
       <c r="O17">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P17">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="Q17">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="R17">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S17">
         <v>1.31</v>
       </c>
       <c r="T17">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="U17">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="V17">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W17">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y17">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z17">
-        <v>3.78</v>
+        <v>3.95</v>
       </c>
       <c r="AA17">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AB17">
         <v>2</v>
       </c>
       <c r="AC17">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AD17">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE17">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF17">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG17">
         <v>2.1</v>
@@ -3153,7 +3153,7 @@
         <v>1.3</v>
       </c>
       <c r="AK17">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,10 +3243,10 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.15</v>
+        <v>2.61</v>
       </c>
       <c r="O18">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="P18">
         <v>3.6</v>
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="O20">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P20">
         <v>3.2</v>
@@ -3581,25 +3581,25 @@
         <v>2.5</v>
       </c>
       <c r="R20">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="S20">
         <v>1.31</v>
       </c>
       <c r="T20">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U20">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="V20">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W20">
         <v>1.08</v>
       </c>
       <c r="X20">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
         <v>1.19</v>
@@ -3614,7 +3614,7 @@
         <v>2.03</v>
       </c>
       <c r="AC20">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="AD20">
         <v>1.38</v>
@@ -3626,7 +3626,7 @@
         <v>1.62</v>
       </c>
       <c r="AG20">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="O21">
         <v>2.8</v>
       </c>
       <c r="P21">
-        <v>4.46</v>
+        <v>4.52</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3771,10 +3771,10 @@
         <v>0</v>
       </c>
       <c r="AA21">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AB21">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AC21">
         <v>0</v>
@@ -3907,10 +3907,10 @@
         <v>3.6</v>
       </c>
       <c r="R22">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S22">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T22">
         <v>3.8</v>
@@ -3928,16 +3928,16 @@
         <v>1.03</v>
       </c>
       <c r="Y22">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z22">
-        <v>4.75</v>
+        <v>4.95</v>
       </c>
       <c r="AA22">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AB22">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AC22">
         <v>2.31</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.29</v>
+        <v>1.77</v>
       </c>
       <c r="AK22">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="O23">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P23">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q23">
         <v>2.15</v>
@@ -4076,16 +4076,16 @@
         <v>1.13</v>
       </c>
       <c r="T23">
-        <v>4.75</v>
+        <v>5.2</v>
       </c>
       <c r="U23">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="V23">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="W23">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X23">
         <v>1.01</v>
@@ -4094,22 +4094,22 @@
         <v>1.03</v>
       </c>
       <c r="Z23">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="AA23">
         <v>1.3</v>
       </c>
       <c r="AB23">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="AC23">
         <v>1.78</v>
       </c>
       <c r="AD23">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="AE23">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AF23">
         <v>1.33</v>
@@ -4230,7 +4230,7 @@
         <v>2.2</v>
       </c>
       <c r="Q24">
-        <v>3.22</v>
+        <v>3.37</v>
       </c>
       <c r="R24">
         <v>2.4</v>
@@ -4239,40 +4239,40 @@
         <v>1.22</v>
       </c>
       <c r="T24">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U24">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="V24">
         <v>1.65</v>
       </c>
       <c r="W24">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X24">
         <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z24">
         <v>5.45</v>
       </c>
       <c r="AA24">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AB24">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AC24">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AD24">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AE24">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AF24">
         <v>1.39</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK24">
         <v>1.4</v>
@@ -4384,31 +4384,31 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="O25">
-        <v>3.33</v>
+        <v>3.72</v>
       </c>
       <c r="P25">
-        <v>4.96</v>
+        <v>4.1</v>
       </c>
       <c r="Q25">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="R25">
-        <v>2.09</v>
+        <v>2.22</v>
       </c>
       <c r="S25">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="T25">
         <v>2.89</v>
       </c>
       <c r="U25">
-        <v>2.99</v>
+        <v>2.8</v>
       </c>
       <c r="V25">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W25">
         <v>1.08</v>
@@ -4432,7 +4432,7 @@
         <v>3.4</v>
       </c>
       <c r="AD25">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE25">
         <v>1.06</v>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK25">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4876,31 +4876,31 @@
         <v>1.53</v>
       </c>
       <c r="O28">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="P28">
-        <v>4.8</v>
+        <v>4.67</v>
       </c>
       <c r="Q28">
         <v>2</v>
       </c>
       <c r="R28">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="S28">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T28">
         <v>3.6</v>
       </c>
       <c r="U28">
-        <v>2.39</v>
+        <v>2.33</v>
       </c>
       <c r="V28">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W28">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X28">
         <v>1.01</v>
@@ -4915,10 +4915,10 @@
         <v>1.65</v>
       </c>
       <c r="AB28">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="AC28">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AD28">
         <v>1.47</v>
@@ -4927,10 +4927,10 @@
         <v>1.14</v>
       </c>
       <c r="AF28">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG28">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -5036,16 +5036,16 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="O29">
         <v>2.88</v>
       </c>
       <c r="P29">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="Q29">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="R29">
         <v>1.9</v>
@@ -5060,40 +5060,40 @@
         <v>3.3</v>
       </c>
       <c r="V29">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W29">
         <v>1.07</v>
       </c>
       <c r="X29">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y29">
         <v>1.42</v>
       </c>
       <c r="Z29">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="AA29">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="AB29">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AC29">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="AD29">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AE29">
         <v>1.02</v>
       </c>
       <c r="AF29">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AG29">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5229,10 +5229,10 @@
         <v>1.08</v>
       </c>
       <c r="X30">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y30">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="Z30">
         <v>4.17</v>
@@ -5247,7 +5247,7 @@
         <v>2.8</v>
       </c>
       <c r="AD30">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE30">
         <v>1.12</v>
@@ -5528,34 +5528,34 @@
         <v>11</v>
       </c>
       <c r="O32">
-        <v>5.95</v>
+        <v>5.85</v>
       </c>
       <c r="P32">
         <v>1.25</v>
       </c>
       <c r="Q32">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="R32">
-        <v>2.89</v>
+        <v>2.62</v>
       </c>
       <c r="S32">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T32">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="U32">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="V32">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W32">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X32">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
         <v>1.19</v>
@@ -5564,7 +5564,7 @@
         <v>4</v>
       </c>
       <c r="AA32">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AB32">
         <v>2.35</v>
@@ -5573,16 +5573,16 @@
         <v>2.38</v>
       </c>
       <c r="AD32">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AE32">
         <v>1.2</v>
       </c>
       <c r="AF32">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="AG32">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>4.74</v>
+        <v>4.46</v>
       </c>
       <c r="AK32">
         <v>1.02</v>
@@ -5688,31 +5688,31 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="O33">
         <v>4.6</v>
       </c>
       <c r="P33">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="Q33">
         <v>1.71</v>
       </c>
       <c r="R33">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="S33">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T33">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="U33">
         <v>2.5</v>
       </c>
       <c r="V33">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="W33">
         <v>1.11</v>
@@ -5730,13 +5730,13 @@
         <v>1.65</v>
       </c>
       <c r="AB33">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AC33">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AD33">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AE33">
         <v>1.16</v>
@@ -5761,7 +5761,7 @@
         <v>1.06</v>
       </c>
       <c r="AK33">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5881,7 +5881,7 @@
         <v>1.06</v>
       </c>
       <c r="X34">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y34">
         <v>1.3</v>
@@ -5893,13 +5893,13 @@
         <v>2.06</v>
       </c>
       <c r="AB34">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AC34">
         <v>3.1</v>
       </c>
       <c r="AD34">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AE34">
         <v>1.08</v>
@@ -6014,19 +6014,19 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
       <c r="O35">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="P35">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Q35">
         <v>2.86</v>
       </c>
       <c r="R35">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S35">
         <v>1.35</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AK35">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6340,19 +6340,19 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="O37">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P37">
-        <v>3.9</v>
+        <v>4.15</v>
       </c>
       <c r="Q37">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R37">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="S37">
         <v>1.37</v>
@@ -6379,13 +6379,13 @@
         <v>3.42</v>
       </c>
       <c r="AA37">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB37">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC37">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="AD37">
         <v>1.3</v>
@@ -6397,7 +6397,7 @@
         <v>1.77</v>
       </c>
       <c r="AG37">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK37">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6530,25 +6530,25 @@
         <v>1.29</v>
       </c>
       <c r="W38">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X38">
         <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="Z38">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="AA38">
         <v>2.15</v>
       </c>
       <c r="AB38">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AC38">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="AD38">
         <v>1.22</v>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK38">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,16 +6666,16 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="O39">
         <v>3.1</v>
       </c>
       <c r="P39">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="Q39">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R39">
         <v>2.05</v>
@@ -6702,7 +6702,7 @@
         <v>1.3</v>
       </c>
       <c r="Z39">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AA39">
         <v>2.16</v>
@@ -6717,7 +6717,7 @@
         <v>1.25</v>
       </c>
       <c r="AE39">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF39">
         <v>1.83</v>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="O40">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="P40">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="Q40">
         <v>2.5</v>
@@ -6868,10 +6868,10 @@
         <v>3.82</v>
       </c>
       <c r="AA40">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AB40">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC40">
         <v>2.85</v>
@@ -7013,10 +7013,10 @@
         <v>3.2</v>
       </c>
       <c r="U41">
-        <v>2.58</v>
+        <v>2.53</v>
       </c>
       <c r="V41">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W41">
         <v>1.11</v>
@@ -7040,7 +7040,7 @@
         <v>2.66</v>
       </c>
       <c r="AD41">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AE41">
         <v>1.12</v>

--- a/jogos_2026-08-17.xlsx
+++ b/jogos_2026-08-17.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="O2">
         <v>3.5</v>
       </c>
       <c r="P2">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -674,10 +674,10 @@
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AB2">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AC2">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O6">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P6">
-        <v>2.07</v>
+        <v>1.97</v>
       </c>
       <c r="Q6">
         <v>4.04</v>
@@ -1305,10 +1305,10 @@
         <v>1.44</v>
       </c>
       <c r="T6">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="U6">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="V6">
         <v>1.3</v>
@@ -1323,16 +1323,16 @@
         <v>1.39</v>
       </c>
       <c r="Z6">
-        <v>2.86</v>
+        <v>3.05</v>
       </c>
       <c r="AA6">
         <v>2.15</v>
       </c>
       <c r="AB6">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AC6">
-        <v>3.86</v>
+        <v>3.25</v>
       </c>
       <c r="AD6">
         <v>1.26</v>
@@ -1344,7 +1344,7 @@
         <v>1.88</v>
       </c>
       <c r="AG6">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AK6">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -2754,16 +2754,16 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="O15">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="P15">
-        <v>7.75</v>
+        <v>7.3</v>
       </c>
       <c r="Q15">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R15">
         <v>2.7</v>
@@ -2775,10 +2775,10 @@
         <v>4.05</v>
       </c>
       <c r="U15">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="V15">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="W15">
         <v>1.16</v>
@@ -2790,19 +2790,19 @@
         <v>1.14</v>
       </c>
       <c r="Z15">
-        <v>6.13</v>
+        <v>5.7</v>
       </c>
       <c r="AA15">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AB15">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="AC15">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AD15">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AE15">
         <v>1.3</v>
@@ -3261,7 +3261,7 @@
         <v>1.68</v>
       </c>
       <c r="T18">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="U18">
         <v>4.45</v>
@@ -3273,7 +3273,7 @@
         <v>1.03</v>
       </c>
       <c r="X18">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="Y18">
         <v>1.56</v>
@@ -3457,13 +3457,13 @@
         <v>1.93</v>
       </c>
       <c r="AE19">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AF19">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AG19">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -4547,25 +4547,25 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="O26">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P26">
         <v>2.9</v>
       </c>
       <c r="Q26">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="R26">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="S26">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T26">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="U26">
         <v>2.75</v>
@@ -4577,7 +4577,7 @@
         <v>1.03</v>
       </c>
       <c r="X26">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y26">
         <v>1.3</v>
@@ -4592,19 +4592,19 @@
         <v>1.73</v>
       </c>
       <c r="AC26">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="AD26">
         <v>1.27</v>
       </c>
       <c r="AE26">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF26">
         <v>1.8</v>
       </c>
       <c r="AG26">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="O31">
         <v>3.85</v>
       </c>
       <c r="P31">
-        <v>2.93</v>
+        <v>3.25</v>
       </c>
       <c r="Q31">
         <v>2.25</v>
@@ -5377,7 +5377,7 @@
         <v>2.8</v>
       </c>
       <c r="S31">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="T31">
         <v>5</v>
@@ -5386,10 +5386,10 @@
         <v>1.73</v>
       </c>
       <c r="V31">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="W31">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="X31">
         <v>1.01</v>
@@ -5851,19 +5851,19 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="O34">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P34">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="Q34">
         <v>2.4</v>
       </c>
       <c r="R34">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="S34">
         <v>1.4</v>
@@ -5893,13 +5893,13 @@
         <v>2.06</v>
       </c>
       <c r="AB34">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AC34">
         <v>3.1</v>
       </c>
       <c r="AD34">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AE34">
         <v>1.08</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK34">
-        <v>1.8</v>
+        <v>1.56</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,16 +6014,16 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="O35">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P35">
-        <v>2.9</v>
+        <v>2.99</v>
       </c>
       <c r="Q35">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="R35">
         <v>2.1</v>
@@ -6032,59 +6032,59 @@
         <v>1.35</v>
       </c>
       <c r="T35">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="U35">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="V35">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W35">
         <v>1.07</v>
       </c>
       <c r="X35">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z35">
+        <v>3.2</v>
+      </c>
+      <c r="AA35">
+        <v>1.91</v>
+      </c>
+      <c r="AB35">
+        <v>1.75</v>
+      </c>
+      <c r="AC35">
         <v>3.3</v>
       </c>
-      <c r="AA35">
-        <v>1.83</v>
-      </c>
-      <c r="AB35">
-        <v>1.8</v>
-      </c>
-      <c r="AC35">
-        <v>3.2</v>
-      </c>
       <c r="AD35">
+        <v>1.29</v>
+      </c>
+      <c r="AE35">
+        <v>1.06</v>
+      </c>
+      <c r="AF35">
+        <v>1.7</v>
+      </c>
+      <c r="AG35">
+        <v>2.01</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ35">
         <v>1.3</v>
-      </c>
-      <c r="AE35">
-        <v>1.07</v>
-      </c>
-      <c r="AF35">
-        <v>1.67</v>
-      </c>
-      <c r="AG35">
-        <v>2.05</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ35">
-        <v>1.31</v>
       </c>
       <c r="AK35">
         <v>1.53</v>
@@ -6186,28 +6186,28 @@
         <v>5.61</v>
       </c>
       <c r="Q36">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="R36">
         <v>2.24</v>
       </c>
       <c r="S36">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T36">
-        <v>3.21</v>
+        <v>2.82</v>
       </c>
       <c r="U36">
         <v>2.6</v>
       </c>
       <c r="V36">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W36">
         <v>1.07</v>
       </c>
       <c r="X36">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
         <v>1.22</v>
@@ -6228,7 +6228,7 @@
         <v>1.33</v>
       </c>
       <c r="AE36">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF36">
         <v>1.85</v>
@@ -6693,37 +6693,37 @@
         <v>1.33</v>
       </c>
       <c r="W39">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X39">
         <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z39">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="AA39">
         <v>2.16</v>
       </c>
       <c r="AB39">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AC39">
         <v>3.5</v>
       </c>
       <c r="AD39">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AE39">
         <v>1.06</v>
       </c>
       <c r="AF39">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AG39">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6829,10 +6829,10 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="O40">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P40">
         <v>3.05</v>
@@ -6847,16 +6847,16 @@
         <v>1.3</v>
       </c>
       <c r="T40">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U40">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V40">
         <v>1.44</v>
       </c>
       <c r="W40">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X40">
         <v>1.01</v>
@@ -6899,7 +6899,7 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK40">
         <v>1.73</v>
@@ -7013,22 +7013,22 @@
         <v>3.2</v>
       </c>
       <c r="U41">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="V41">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W41">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X41">
         <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z41">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AA41">
         <v>1.74</v>
@@ -7043,7 +7043,7 @@
         <v>1.37</v>
       </c>
       <c r="AE41">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF41">
         <v>1.65</v>

--- a/jogos_2026-08-17.xlsx
+++ b/jogos_2026-08-17.xlsx
@@ -1948,19 +1948,19 @@
         <v>5.7</v>
       </c>
       <c r="Q10">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="R10">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="S10">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="T10">
         <v>2.56</v>
       </c>
       <c r="U10">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="V10">
         <v>1.32</v>
@@ -1972,10 +1972,10 @@
         <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="Z10">
-        <v>2.83</v>
+        <v>2.96</v>
       </c>
       <c r="AA10">
         <v>2.15</v>
@@ -3086,10 +3086,10 @@
         <v>3.45</v>
       </c>
       <c r="P17">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="Q17">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="R17">
         <v>2.3</v>
@@ -3104,19 +3104,19 @@
         <v>2.38</v>
       </c>
       <c r="V17">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W17">
         <v>1.07</v>
       </c>
       <c r="X17">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y17">
         <v>1.17</v>
       </c>
       <c r="Z17">
-        <v>3.95</v>
+        <v>3.94</v>
       </c>
       <c r="AA17">
         <v>1.75</v>
@@ -3125,7 +3125,7 @@
         <v>2</v>
       </c>
       <c r="AC17">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="AD17">
         <v>1.4</v>
@@ -3137,7 +3137,7 @@
         <v>1.62</v>
       </c>
       <c r="AG17">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>1.3</v>
       </c>
       <c r="AK17">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AL17">
         <v>0</v>

--- a/jogos_2026-08-17.xlsx
+++ b/jogos_2026-08-17.xlsx
@@ -1939,25 +1939,25 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="O10">
-        <v>3.6</v>
+        <v>3.38</v>
       </c>
       <c r="P10">
-        <v>5.7</v>
+        <v>4.5</v>
       </c>
       <c r="Q10">
         <v>2.17</v>
       </c>
       <c r="R10">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="S10">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T10">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="U10">
         <v>3.05</v>
@@ -1972,19 +1972,19 @@
         <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z10">
-        <v>2.96</v>
+        <v>2.7</v>
       </c>
       <c r="AA10">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AB10">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AC10">
-        <v>3.87</v>
+        <v>3.68</v>
       </c>
       <c r="AD10">
         <v>1.2</v>
@@ -1993,7 +1993,7 @@
         <v>1.04</v>
       </c>
       <c r="AF10">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AG10">
         <v>1.67</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AK10">
         <v>2.22</v>
@@ -5202,10 +5202,10 @@
         <v>2.3</v>
       </c>
       <c r="O30">
-        <v>3.41</v>
+        <v>3.45</v>
       </c>
       <c r="P30">
-        <v>2.61</v>
+        <v>2.87</v>
       </c>
       <c r="Q30">
         <v>2.88</v>
@@ -5214,7 +5214,7 @@
         <v>2.25</v>
       </c>
       <c r="S30">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T30">
         <v>2.91</v>
@@ -5223,16 +5223,16 @@
         <v>2.55</v>
       </c>
       <c r="V30">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W30">
         <v>1.08</v>
       </c>
       <c r="X30">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="Z30">
         <v>4.17</v>
@@ -5247,10 +5247,10 @@
         <v>2.8</v>
       </c>
       <c r="AD30">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE30">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF30">
         <v>1.56</v>

--- a/jogos_2026-08-17.xlsx
+++ b/jogos_2026-08-17.xlsx
@@ -961,46 +961,46 @@
         </is>
       </c>
       <c r="N4">
-        <v>4.8</v>
+        <v>6.3</v>
       </c>
       <c r="O4">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="P4">
         <v>1.55</v>
       </c>
       <c r="Q4">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="R4">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S4">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T4">
-        <v>3.4</v>
+        <v>3.02</v>
       </c>
       <c r="U4">
         <v>2.31</v>
       </c>
       <c r="V4">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="W4">
         <v>1.1</v>
       </c>
       <c r="X4">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y4">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z4">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AA4">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AB4">
         <v>2.08</v>
@@ -1009,10 +1009,10 @@
         <v>2.6</v>
       </c>
       <c r="AD4">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="AE4">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF4">
         <v>1.67</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="AK4">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="O8">
         <v>3.8</v>
@@ -1628,10 +1628,10 @@
         <v>2.3</v>
       </c>
       <c r="S8">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T8">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="U8">
         <v>2.45</v>
@@ -1794,16 +1794,16 @@
         <v>1.44</v>
       </c>
       <c r="T9">
-        <v>2.76</v>
+        <v>2.52</v>
       </c>
       <c r="U9">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="V9">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="W9">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X9">
         <v>1.02</v>
@@ -1812,25 +1812,25 @@
         <v>1.32</v>
       </c>
       <c r="Z9">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AA9">
         <v>2.15</v>
       </c>
       <c r="AB9">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AC9">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="AD9">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AE9">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF9">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AG9">
         <v>1.85</v>
@@ -1849,7 +1849,7 @@
         <v>1.2</v>
       </c>
       <c r="AK9">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1948,34 +1948,34 @@
         <v>4.5</v>
       </c>
       <c r="Q10">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="R10">
         <v>2.03</v>
       </c>
       <c r="S10">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T10">
         <v>2.63</v>
       </c>
       <c r="U10">
-        <v>3.05</v>
+        <v>3.16</v>
       </c>
       <c r="V10">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W10">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X10">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y10">
         <v>1.4</v>
       </c>
       <c r="Z10">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="AA10">
         <v>2.25</v>
@@ -1984,19 +1984,19 @@
         <v>1.62</v>
       </c>
       <c r="AC10">
-        <v>3.68</v>
+        <v>3.88</v>
       </c>
       <c r="AD10">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE10">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF10">
         <v>2.14</v>
       </c>
       <c r="AG10">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>1.2</v>
       </c>
       <c r="AK10">
-        <v>2.22</v>
+        <v>2.03</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2274,7 +2274,7 @@
         <v>4.4</v>
       </c>
       <c r="Q12">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R12">
         <v>2.3</v>
@@ -2286,7 +2286,7 @@
         <v>3.2</v>
       </c>
       <c r="U12">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="V12">
         <v>1.44</v>
@@ -2295,7 +2295,7 @@
         <v>1.11</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y12">
         <v>1.22</v>
@@ -2304,22 +2304,22 @@
         <v>3.8</v>
       </c>
       <c r="AA12">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AB12">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AC12">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="AD12">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE12">
         <v>1.1</v>
       </c>
       <c r="AF12">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AG12">
         <v>2</v>
@@ -2428,19 +2428,19 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="O13">
         <v>3.2</v>
       </c>
       <c r="P13">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="Q13">
         <v>3</v>
       </c>
       <c r="R13">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="S13">
         <v>1.42</v>
@@ -2458,22 +2458,22 @@
         <v>1.02</v>
       </c>
       <c r="X13">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y13">
         <v>1.28</v>
       </c>
       <c r="Z13">
-        <v>3.28</v>
+        <v>3.08</v>
       </c>
       <c r="AA13">
         <v>1.98</v>
       </c>
       <c r="AB13">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AC13">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="AD13">
         <v>1.25</v>
@@ -2482,10 +2482,10 @@
         <v>1.04</v>
       </c>
       <c r="AF13">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AG13">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK13">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2594,28 +2594,28 @@
         <v>1.77</v>
       </c>
       <c r="O14">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="P14">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Q14">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="R14">
         <v>2.04</v>
       </c>
       <c r="S14">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T14">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="U14">
-        <v>3.28</v>
+        <v>2.91</v>
       </c>
       <c r="V14">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="W14">
         <v>1.06</v>
@@ -2636,10 +2636,10 @@
         <v>1.65</v>
       </c>
       <c r="AC14">
-        <v>3.54</v>
+        <v>4.1</v>
       </c>
       <c r="AD14">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AE14">
         <v>1.07</v>
@@ -2648,7 +2648,7 @@
         <v>1.95</v>
       </c>
       <c r="AG14">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>1.2</v>
       </c>
       <c r="AK14">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,25 +2754,25 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="O15">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="P15">
         <v>7.3</v>
       </c>
       <c r="Q15">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="R15">
         <v>2.7</v>
       </c>
       <c r="S15">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="T15">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="U15">
         <v>2.07</v>
@@ -2790,13 +2790,13 @@
         <v>1.14</v>
       </c>
       <c r="Z15">
-        <v>5.7</v>
+        <v>5.75</v>
       </c>
       <c r="AA15">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AB15">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="AC15">
         <v>2.05</v>
@@ -2805,10 +2805,10 @@
         <v>1.69</v>
       </c>
       <c r="AE15">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AF15">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AG15">
         <v>2.05</v>
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="O16">
-        <v>4.55</v>
+        <v>4.2</v>
       </c>
       <c r="P16">
         <v>5.75</v>
@@ -2929,22 +2929,22 @@
         <v>1.93</v>
       </c>
       <c r="R16">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="S16">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T16">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="U16">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="V16">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W16">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X16">
         <v>1.03</v>
@@ -2965,16 +2965,16 @@
         <v>2.5</v>
       </c>
       <c r="AD16">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AE16">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF16">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG16">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="O17">
         <v>3.45</v>
@@ -3095,7 +3095,7 @@
         <v>2.3</v>
       </c>
       <c r="S17">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T17">
         <v>3</v>
@@ -3104,25 +3104,25 @@
         <v>2.38</v>
       </c>
       <c r="V17">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W17">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X17">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y17">
         <v>1.17</v>
       </c>
       <c r="Z17">
-        <v>3.94</v>
+        <v>3.9</v>
       </c>
       <c r="AA17">
         <v>1.75</v>
       </c>
       <c r="AB17">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AC17">
         <v>2.56</v>
@@ -3131,7 +3131,7 @@
         <v>1.4</v>
       </c>
       <c r="AE17">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF17">
         <v>1.62</v>
@@ -3153,7 +3153,7 @@
         <v>1.3</v>
       </c>
       <c r="AK17">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3581,13 +3581,13 @@
         <v>2.5</v>
       </c>
       <c r="R20">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="S20">
         <v>1.31</v>
       </c>
       <c r="T20">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U20">
         <v>2.44</v>
@@ -3599,10 +3599,10 @@
         <v>1.08</v>
       </c>
       <c r="X20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y20">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z20">
         <v>3.78</v>
@@ -3611,10 +3611,10 @@
         <v>1.7</v>
       </c>
       <c r="AB20">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AC20">
-        <v>2.76</v>
+        <v>2.62</v>
       </c>
       <c r="AD20">
         <v>1.38</v>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK20">
         <v>1.68</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="O21">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="P21">
-        <v>4.52</v>
+        <v>4.3</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3910,7 +3910,7 @@
         <v>2.3</v>
       </c>
       <c r="S22">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T22">
         <v>3.8</v>
@@ -3919,7 +3919,7 @@
         <v>2.2</v>
       </c>
       <c r="V22">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="W22">
         <v>1.17</v>
@@ -3928,16 +3928,16 @@
         <v>1.03</v>
       </c>
       <c r="Y22">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Z22">
         <v>4.95</v>
       </c>
       <c r="AA22">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AB22">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AC22">
         <v>2.31</v>
@@ -3949,10 +3949,10 @@
         <v>1.18</v>
       </c>
       <c r="AF22">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AG22">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.77</v>
+        <v>1.19</v>
       </c>
       <c r="AK22">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,19 +4058,19 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="O23">
-        <v>4</v>
+        <v>4.55</v>
       </c>
       <c r="P23">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="Q23">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="R23">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="S23">
         <v>1.13</v>
@@ -4079,13 +4079,13 @@
         <v>5.2</v>
       </c>
       <c r="U23">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V23">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="W23">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X23">
         <v>1.01</v>
@@ -4097,25 +4097,25 @@
         <v>6.25</v>
       </c>
       <c r="AA23">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AB23">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AC23">
         <v>1.78</v>
       </c>
       <c r="AD23">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AE23">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AF23">
         <v>1.33</v>
       </c>
       <c r="AG23">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>1.17</v>
       </c>
       <c r="AK23">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="O24">
         <v>3.65</v>
@@ -4233,7 +4233,7 @@
         <v>3.37</v>
       </c>
       <c r="R24">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="S24">
         <v>1.22</v>
@@ -4242,10 +4242,10 @@
         <v>3.9</v>
       </c>
       <c r="U24">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="V24">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W24">
         <v>1.13</v>
@@ -4260,19 +4260,19 @@
         <v>5.45</v>
       </c>
       <c r="AA24">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB24">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AC24">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AD24">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AE24">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF24">
         <v>1.39</v>
@@ -4384,22 +4384,22 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="O25">
-        <v>3.72</v>
+        <v>3.33</v>
       </c>
       <c r="P25">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Q25">
-        <v>2.48</v>
+        <v>2.32</v>
       </c>
       <c r="R25">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="S25">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="T25">
         <v>2.89</v>
@@ -4408,25 +4408,25 @@
         <v>2.8</v>
       </c>
       <c r="V25">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W25">
         <v>1.08</v>
       </c>
       <c r="X25">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z25">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="AA25">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB25">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AC25">
         <v>3.4</v>
@@ -4435,13 +4435,13 @@
         <v>1.28</v>
       </c>
       <c r="AE25">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF25">
         <v>1.83</v>
       </c>
       <c r="AG25">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK25">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,10 +4547,10 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="O26">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P26">
         <v>2.9</v>
@@ -4559,7 +4559,7 @@
         <v>2.8</v>
       </c>
       <c r="R26">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="S26">
         <v>1.43</v>
@@ -4568,43 +4568,43 @@
         <v>2.62</v>
       </c>
       <c r="U26">
-        <v>2.75</v>
+        <v>2.94</v>
       </c>
       <c r="V26">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W26">
         <v>1.03</v>
       </c>
       <c r="X26">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y26">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z26">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AA26">
         <v>2.1</v>
       </c>
       <c r="AB26">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AC26">
-        <v>3.65</v>
+        <v>3.59</v>
       </c>
       <c r="AD26">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE26">
         <v>1.05</v>
       </c>
       <c r="AF26">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AG26">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4873,34 +4873,34 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="O28">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="P28">
-        <v>4.67</v>
+        <v>5</v>
       </c>
       <c r="Q28">
         <v>2</v>
       </c>
       <c r="R28">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S28">
         <v>1.31</v>
       </c>
       <c r="T28">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="U28">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="V28">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W28">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X28">
         <v>1.01</v>
@@ -4930,7 +4930,7 @@
         <v>1.73</v>
       </c>
       <c r="AG28">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK28">
         <v>2.38</v>
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="O29">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="P29">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="Q29">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="R29">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="S29">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="T29">
-        <v>2.7</v>
+        <v>2.44</v>
       </c>
       <c r="U29">
         <v>3.3</v>
       </c>
       <c r="V29">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W29">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X29">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y29">
         <v>1.42</v>
       </c>
       <c r="Z29">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AA29">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AB29">
         <v>1.59</v>
       </c>
       <c r="AC29">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AD29">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE29">
         <v>1.02</v>
       </c>
       <c r="AF29">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AG29">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK29">
         <v>1.58</v>
@@ -5202,7 +5202,7 @@
         <v>2.3</v>
       </c>
       <c r="O30">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P30">
         <v>2.87</v>
@@ -5220,7 +5220,7 @@
         <v>2.91</v>
       </c>
       <c r="U30">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="V30">
         <v>1.46</v>
@@ -5232,10 +5232,10 @@
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z30">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="AA30">
         <v>1.76</v>
@@ -5244,13 +5244,13 @@
         <v>2.09</v>
       </c>
       <c r="AC30">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="AD30">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE30">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF30">
         <v>1.56</v>
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK30">
         <v>1.53</v>
@@ -5528,10 +5528,10 @@
         <v>11</v>
       </c>
       <c r="O32">
-        <v>5.85</v>
+        <v>6.5</v>
       </c>
       <c r="P32">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Q32">
         <v>11</v>
@@ -5540,7 +5540,7 @@
         <v>2.62</v>
       </c>
       <c r="S32">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T32">
         <v>3.45</v>
@@ -5549,25 +5549,25 @@
         <v>2.25</v>
       </c>
       <c r="V32">
+        <v>1.52</v>
+      </c>
+      <c r="W32">
+        <v>1.14</v>
+      </c>
+      <c r="X32">
+        <v>1.04</v>
+      </c>
+      <c r="Y32">
+        <v>1.14</v>
+      </c>
+      <c r="Z32">
+        <v>4.42</v>
+      </c>
+      <c r="AA32">
         <v>1.57</v>
       </c>
-      <c r="W32">
-        <v>1.11</v>
-      </c>
-      <c r="X32">
-        <v>1.03</v>
-      </c>
-      <c r="Y32">
-        <v>1.19</v>
-      </c>
-      <c r="Z32">
-        <v>4</v>
-      </c>
-      <c r="AA32">
-        <v>1.61</v>
-      </c>
       <c r="AB32">
-        <v>2.35</v>
+        <v>2.12</v>
       </c>
       <c r="AC32">
         <v>2.38</v>
@@ -5576,10 +5576,10 @@
         <v>1.5</v>
       </c>
       <c r="AE32">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AF32">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AG32">
         <v>1.6</v>
@@ -5688,25 +5688,25 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="O33">
         <v>4.6</v>
       </c>
       <c r="P33">
-        <v>7.5</v>
+        <v>8.25</v>
       </c>
       <c r="Q33">
         <v>1.71</v>
       </c>
       <c r="R33">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="S33">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T33">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="U33">
         <v>2.5</v>
@@ -5727,16 +5727,16 @@
         <v>4.5</v>
       </c>
       <c r="AA33">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB33">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="AC33">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="AD33">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AE33">
         <v>1.16</v>
@@ -5745,7 +5745,7 @@
         <v>2</v>
       </c>
       <c r="AG33">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="O37">
         <v>3.3</v>
@@ -6352,19 +6352,19 @@
         <v>2.3</v>
       </c>
       <c r="R37">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="S37">
         <v>1.37</v>
       </c>
       <c r="T37">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="U37">
-        <v>2.59</v>
+        <v>2.71</v>
       </c>
       <c r="V37">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="W37">
         <v>1.08</v>
@@ -6379,13 +6379,13 @@
         <v>3.42</v>
       </c>
       <c r="AA37">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB37">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC37">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="AD37">
         <v>1.3</v>
@@ -6397,7 +6397,7 @@
         <v>1.77</v>
       </c>
       <c r="AG37">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK37">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="O38">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="P38">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q38">
         <v>2.81</v>
@@ -6521,13 +6521,13 @@
         <v>1.42</v>
       </c>
       <c r="T38">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="U38">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="V38">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W38">
         <v>1.04</v>
@@ -6560,7 +6560,7 @@
         <v>1.82</v>
       </c>
       <c r="AG38">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK38">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AL38">
         <v>0</v>

--- a/jogos_2026-08-17.xlsx
+++ b/jogos_2026-08-17.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="O2">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P2">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -1296,19 +1296,19 @@
         <v>1.97</v>
       </c>
       <c r="Q6">
-        <v>4.04</v>
+        <v>4.16</v>
       </c>
       <c r="R6">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="S6">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T6">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="U6">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="V6">
         <v>1.3</v>
@@ -1320,16 +1320,16 @@
         <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="Z6">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="AA6">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AB6">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AC6">
         <v>3.25</v>
@@ -1341,10 +1341,10 @@
         <v>1.03</v>
       </c>
       <c r="AF6">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AG6">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>1.44</v>
       </c>
       <c r="T9">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="U9">
         <v>2.75</v>
@@ -1803,7 +1803,7 @@
         <v>1.38</v>
       </c>
       <c r="W9">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X9">
         <v>1.02</v>
@@ -2754,7 +2754,7 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="O15">
         <v>5.6</v>
@@ -2790,22 +2790,22 @@
         <v>1.14</v>
       </c>
       <c r="Z15">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="AA15">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AB15">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AC15">
         <v>2.05</v>
       </c>
       <c r="AD15">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="AE15">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AF15">
         <v>1.73</v>
@@ -3243,25 +3243,25 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.61</v>
+        <v>2.15</v>
       </c>
       <c r="O18">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="P18">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q18">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="R18">
         <v>1.8</v>
       </c>
       <c r="S18">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="T18">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="U18">
         <v>4.45</v>
@@ -3273,19 +3273,19 @@
         <v>1.03</v>
       </c>
       <c r="X18">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="Y18">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Z18">
-        <v>2.03</v>
+        <v>2.25</v>
       </c>
       <c r="AA18">
         <v>3.14</v>
       </c>
       <c r="AB18">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AC18">
         <v>7.1</v>
@@ -3300,7 +3300,7 @@
         <v>2.51</v>
       </c>
       <c r="AG18">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3415,25 +3415,25 @@
         <v>2.6</v>
       </c>
       <c r="Q19">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="R19">
-        <v>2.63</v>
+        <v>2.49</v>
       </c>
       <c r="S19">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="T19">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="U19">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V19">
         <v>1.85</v>
       </c>
       <c r="W19">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="X19">
         <v>1.01</v>
@@ -3460,10 +3460,10 @@
         <v>1.36</v>
       </c>
       <c r="AF19">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AG19">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AK19">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="O21">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="P21">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -4085,7 +4085,7 @@
         <v>1.85</v>
       </c>
       <c r="W23">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="X23">
         <v>1.01</v>
@@ -4393,13 +4393,13 @@
         <v>4</v>
       </c>
       <c r="Q25">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="R25">
         <v>2.15</v>
       </c>
       <c r="S25">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T25">
         <v>2.89</v>
@@ -4411,16 +4411,16 @@
         <v>1.4</v>
       </c>
       <c r="W25">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X25">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y25">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z25">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AA25">
         <v>2</v>
@@ -4441,7 +4441,7 @@
         <v>1.83</v>
       </c>
       <c r="AG25">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK25">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -5045,7 +5045,7 @@
         <v>2.96</v>
       </c>
       <c r="Q29">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="R29">
         <v>1.95</v>
@@ -5217,7 +5217,7 @@
         <v>1.34</v>
       </c>
       <c r="T30">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="U30">
         <v>2.58</v>
@@ -5232,10 +5232,10 @@
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z30">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AA30">
         <v>1.76</v>
@@ -5247,7 +5247,7 @@
         <v>2.68</v>
       </c>
       <c r="AD30">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE30">
         <v>1.14</v>
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AK30">
         <v>1.53</v>
@@ -5365,28 +5365,28 @@
         <v>1.84</v>
       </c>
       <c r="O31">
-        <v>3.85</v>
+        <v>4.15</v>
       </c>
       <c r="P31">
         <v>3.25</v>
       </c>
       <c r="Q31">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="R31">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="S31">
         <v>1.13</v>
       </c>
       <c r="T31">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="U31">
         <v>1.73</v>
       </c>
       <c r="V31">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="W31">
         <v>1.28</v>
@@ -5395,10 +5395,10 @@
         <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Z31">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AA31">
         <v>1.24</v>
@@ -5410,7 +5410,7 @@
         <v>1.62</v>
       </c>
       <c r="AD31">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="AE31">
         <v>1.51</v>
@@ -5435,7 +5435,7 @@
         <v>1.19</v>
       </c>
       <c r="AK31">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="N32">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O32">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="P32">
         <v>1.18</v>
@@ -5552,10 +5552,10 @@
         <v>1.52</v>
       </c>
       <c r="W32">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X32">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
         <v>1.14</v>
@@ -5579,10 +5579,10 @@
         <v>1.16</v>
       </c>
       <c r="AF32">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AG32">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5854,22 +5854,22 @@
         <v>1.92</v>
       </c>
       <c r="O34">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P34">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="Q34">
         <v>2.4</v>
       </c>
       <c r="R34">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="S34">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T34">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="U34">
         <v>2.9</v>
@@ -5884,31 +5884,31 @@
         <v>1.02</v>
       </c>
       <c r="Y34">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z34">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="AA34">
         <v>2.06</v>
       </c>
       <c r="AB34">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AC34">
         <v>3.1</v>
       </c>
       <c r="AD34">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AE34">
         <v>1.08</v>
       </c>
       <c r="AF34">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AG34">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AK34">
-        <v>1.56</v>
+        <v>1.8</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6023,34 +6023,34 @@
         <v>2.99</v>
       </c>
       <c r="Q35">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="R35">
         <v>2.1</v>
       </c>
       <c r="S35">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T35">
         <v>3</v>
       </c>
       <c r="U35">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="V35">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W35">
         <v>1.07</v>
       </c>
       <c r="X35">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y35">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z35">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AA35">
         <v>1.91</v>
@@ -6062,16 +6062,16 @@
         <v>3.3</v>
       </c>
       <c r="AD35">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AE35">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF35">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AG35">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>1.3</v>
       </c>
       <c r="AK35">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6189,25 +6189,25 @@
         <v>2.09</v>
       </c>
       <c r="R36">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="S36">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T36">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="U36">
         <v>2.6</v>
       </c>
       <c r="V36">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W36">
         <v>1.07</v>
       </c>
       <c r="X36">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y36">
         <v>1.22</v>
@@ -6225,16 +6225,16 @@
         <v>3</v>
       </c>
       <c r="AD36">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE36">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF36">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AG36">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6675,52 +6675,52 @@
         <v>2.2</v>
       </c>
       <c r="Q39">
-        <v>3.5</v>
+        <v>3.86</v>
       </c>
       <c r="R39">
         <v>2.05</v>
       </c>
       <c r="S39">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="T39">
         <v>2.75</v>
       </c>
       <c r="U39">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="V39">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W39">
         <v>1.07</v>
       </c>
       <c r="X39">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y39">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z39">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="AA39">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AB39">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AC39">
         <v>3.5</v>
       </c>
       <c r="AD39">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE39">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF39">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AG39">
         <v>1.85</v>
@@ -6739,7 +6739,7 @@
         <v>1.28</v>
       </c>
       <c r="AK39">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="O40">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P40">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="Q40">
         <v>2.5</v>
@@ -6847,10 +6847,10 @@
         <v>1.3</v>
       </c>
       <c r="T40">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="U40">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V40">
         <v>1.44</v>
@@ -6862,25 +6862,25 @@
         <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z40">
-        <v>3.82</v>
+        <v>3.7</v>
       </c>
       <c r="AA40">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AB40">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC40">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="AD40">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AE40">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF40">
         <v>1.62</v>
@@ -6899,7 +6899,7 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AK40">
         <v>1.73</v>

--- a/jogos_2026-08-17.xlsx
+++ b/jogos_2026-08-17.xlsx
@@ -2609,7 +2609,7 @@
         <v>1.42</v>
       </c>
       <c r="T14">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="U14">
         <v>2.91</v>
@@ -3095,7 +3095,7 @@
         <v>2.3</v>
       </c>
       <c r="S17">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T17">
         <v>3</v>
@@ -3125,10 +3125,10 @@
         <v>1.8</v>
       </c>
       <c r="AC17">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="AD17">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE17">
         <v>1.13</v>
@@ -3569,25 +3569,25 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="O20">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P20">
         <v>3.2</v>
       </c>
       <c r="Q20">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="R20">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="S20">
         <v>1.31</v>
       </c>
       <c r="T20">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U20">
         <v>2.44</v>
@@ -3605,16 +3605,16 @@
         <v>1.22</v>
       </c>
       <c r="Z20">
-        <v>3.78</v>
+        <v>4.02</v>
       </c>
       <c r="AA20">
         <v>1.7</v>
       </c>
       <c r="AB20">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC20">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AD20">
         <v>1.38</v>
@@ -3623,7 +3623,7 @@
         <v>1.12</v>
       </c>
       <c r="AF20">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG20">
         <v>2.2</v>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK20">
         <v>1.68</v>
@@ -4547,49 +4547,49 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O26">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P26">
         <v>2.9</v>
       </c>
       <c r="Q26">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="R26">
         <v>2.18</v>
       </c>
       <c r="S26">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T26">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="U26">
         <v>2.94</v>
       </c>
       <c r="V26">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W26">
         <v>1.03</v>
       </c>
       <c r="X26">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z26">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="AA26">
         <v>2.1</v>
       </c>
       <c r="AB26">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AC26">
         <v>3.59</v>
@@ -4598,13 +4598,13 @@
         <v>1.25</v>
       </c>
       <c r="AE26">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF26">
         <v>1.74</v>
       </c>
       <c r="AG26">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="O28">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="P28">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="Q28">
         <v>2</v>
@@ -5706,7 +5706,7 @@
         <v>1.25</v>
       </c>
       <c r="T33">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="U33">
         <v>2.5</v>
@@ -5905,10 +5905,10 @@
         <v>1.08</v>
       </c>
       <c r="AF34">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AG34">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -6195,13 +6195,13 @@
         <v>1.36</v>
       </c>
       <c r="T36">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="U36">
         <v>2.6</v>
       </c>
       <c r="V36">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W36">
         <v>1.07</v>
@@ -6219,22 +6219,22 @@
         <v>1.83</v>
       </c>
       <c r="AB36">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AC36">
         <v>3</v>
       </c>
       <c r="AD36">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE36">
         <v>1.14</v>
       </c>
       <c r="AF36">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG36">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6696,7 +6696,7 @@
         <v>1.07</v>
       </c>
       <c r="X39">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
         <v>1.3</v>
@@ -6714,7 +6714,7 @@
         <v>3.5</v>
       </c>
       <c r="AD39">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE39">
         <v>1.03</v>
@@ -6862,16 +6862,16 @@
         <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z40">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="AA40">
         <v>1.71</v>
       </c>
       <c r="AB40">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AC40">
         <v>2.9</v>
@@ -6899,7 +6899,7 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK40">
         <v>1.73</v>

--- a/jogos_2026-08-17.xlsx
+++ b/jogos_2026-08-17.xlsx
@@ -3243,16 +3243,16 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="O18">
         <v>2.59</v>
       </c>
       <c r="P18">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q18">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="R18">
         <v>1.8</v>
@@ -3261,7 +3261,7 @@
         <v>1.7</v>
       </c>
       <c r="T18">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="U18">
         <v>4.45</v>
@@ -6343,13 +6343,13 @@
         <v>1.67</v>
       </c>
       <c r="O37">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P37">
         <v>4.15</v>
       </c>
       <c r="Q37">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="R37">
         <v>2.04</v>
@@ -6361,10 +6361,10 @@
         <v>2.71</v>
       </c>
       <c r="U37">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="V37">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W37">
         <v>1.08</v>
@@ -6373,10 +6373,10 @@
         <v>1.03</v>
       </c>
       <c r="Y37">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z37">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AA37">
         <v>1.9</v>
@@ -6391,13 +6391,13 @@
         <v>1.3</v>
       </c>
       <c r="AE37">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF37">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AG37">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AK37">
         <v>1.97</v>
@@ -6708,7 +6708,7 @@
         <v>2.15</v>
       </c>
       <c r="AB39">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AC39">
         <v>3.5</v>
@@ -7010,16 +7010,16 @@
         <v>1.3</v>
       </c>
       <c r="T41">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U41">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="V41">
         <v>1.5</v>
       </c>
       <c r="W41">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X41">
         <v>1.01</v>
@@ -7043,10 +7043,10 @@
         <v>1.37</v>
       </c>
       <c r="AE41">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF41">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AG41">
         <v>2.1</v>

--- a/jogos_2026-08-17.xlsx
+++ b/jogos_2026-08-17.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="O2">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P2">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -961,25 +961,25 @@
         </is>
       </c>
       <c r="N4">
-        <v>6.3</v>
+        <v>4.8</v>
       </c>
       <c r="O4">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="P4">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="Q4">
         <v>5.1</v>
       </c>
       <c r="R4">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="S4">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T4">
-        <v>3.02</v>
+        <v>2.96</v>
       </c>
       <c r="U4">
         <v>2.31</v>
@@ -994,7 +994,7 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z4">
         <v>4.2</v>
@@ -1009,10 +1009,10 @@
         <v>2.6</v>
       </c>
       <c r="AD4">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AE4">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF4">
         <v>1.67</v>
@@ -1293,7 +1293,7 @@
         <v>3.2</v>
       </c>
       <c r="P6">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="Q6">
         <v>4.16</v>
@@ -1302,10 +1302,10 @@
         <v>2.05</v>
       </c>
       <c r="S6">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T6">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="U6">
         <v>3.2</v>
@@ -1326,10 +1326,10 @@
         <v>2.84</v>
       </c>
       <c r="AA6">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AB6">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AC6">
         <v>3.25</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="O8">
         <v>3.8</v>
       </c>
       <c r="P8">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="Q8">
         <v>3.64</v>
@@ -1628,10 +1628,10 @@
         <v>2.3</v>
       </c>
       <c r="S8">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T8">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="U8">
         <v>2.45</v>
@@ -1655,7 +1655,7 @@
         <v>1.7</v>
       </c>
       <c r="AB8">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AC8">
         <v>2.7</v>
@@ -1667,7 +1667,7 @@
         <v>1.15</v>
       </c>
       <c r="AF8">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG8">
         <v>2.25</v>
@@ -1806,31 +1806,31 @@
         <v>1.03</v>
       </c>
       <c r="X9">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y9">
         <v>1.32</v>
       </c>
       <c r="Z9">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AA9">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AB9">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="AC9">
-        <v>3.58</v>
+        <v>3.79</v>
       </c>
       <c r="AD9">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AE9">
         <v>1.1</v>
       </c>
       <c r="AF9">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AG9">
         <v>1.85</v>
@@ -1942,10 +1942,10 @@
         <v>1.52</v>
       </c>
       <c r="O10">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="P10">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="Q10">
         <v>2.15</v>
@@ -1969,7 +1969,7 @@
         <v>1.02</v>
       </c>
       <c r="X10">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
         <v>1.4</v>
@@ -1984,10 +1984,10 @@
         <v>1.62</v>
       </c>
       <c r="AC10">
-        <v>3.88</v>
+        <v>4.09</v>
       </c>
       <c r="AD10">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AE10">
         <v>1.03</v>
@@ -2265,19 +2265,19 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="O12">
         <v>3.7</v>
       </c>
       <c r="P12">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
       </c>
       <c r="R12">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="S12">
         <v>1.3</v>
@@ -2319,7 +2319,7 @@
         <v>1.1</v>
       </c>
       <c r="AF12">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AG12">
         <v>2</v>
@@ -2434,7 +2434,7 @@
         <v>3.2</v>
       </c>
       <c r="P13">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -2455,10 +2455,10 @@
         <v>1.36</v>
       </c>
       <c r="W13">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X13">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y13">
         <v>1.28</v>
@@ -2473,16 +2473,16 @@
         <v>1.71</v>
       </c>
       <c r="AC13">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="AD13">
         <v>1.25</v>
       </c>
       <c r="AE13">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF13">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AG13">
         <v>1.94</v>
@@ -2591,16 +2591,16 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="O14">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="P14">
         <v>4.2</v>
       </c>
       <c r="Q14">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="R14">
         <v>2.04</v>
@@ -2609,7 +2609,7 @@
         <v>1.42</v>
       </c>
       <c r="T14">
-        <v>2.47</v>
+        <v>2.66</v>
       </c>
       <c r="U14">
         <v>2.91</v>
@@ -2618,7 +2618,7 @@
         <v>1.31</v>
       </c>
       <c r="W14">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X14">
         <v>1.03</v>
@@ -2754,31 +2754,31 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="O15">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="P15">
-        <v>7.3</v>
+        <v>7.75</v>
       </c>
       <c r="Q15">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="R15">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="S15">
         <v>1.19</v>
       </c>
       <c r="T15">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="U15">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="V15">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="W15">
         <v>1.16</v>
@@ -2802,7 +2802,7 @@
         <v>2.05</v>
       </c>
       <c r="AD15">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="AE15">
         <v>1.3</v>
@@ -2811,7 +2811,7 @@
         <v>1.73</v>
       </c>
       <c r="AG15">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2920,10 +2920,10 @@
         <v>1.45</v>
       </c>
       <c r="O16">
-        <v>4.2</v>
+        <v>4.35</v>
       </c>
       <c r="P16">
-        <v>5.75</v>
+        <v>6.4</v>
       </c>
       <c r="Q16">
         <v>1.93</v>
@@ -2935,16 +2935,16 @@
         <v>1.25</v>
       </c>
       <c r="T16">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="U16">
         <v>2.2</v>
       </c>
       <c r="V16">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="W16">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X16">
         <v>1.03</v>
@@ -3080,16 +3080,16 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.6</v>
+        <v>3.32</v>
       </c>
       <c r="O17">
         <v>3.45</v>
       </c>
       <c r="P17">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="Q17">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="R17">
         <v>2.3</v>
@@ -3119,7 +3119,7 @@
         <v>3.9</v>
       </c>
       <c r="AA17">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AB17">
         <v>1.8</v>
@@ -3409,19 +3409,19 @@
         <v>1.94</v>
       </c>
       <c r="O19">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P19">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="Q19">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="R19">
         <v>2.49</v>
       </c>
       <c r="S19">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="T19">
         <v>4.1</v>
@@ -3433,7 +3433,7 @@
         <v>1.85</v>
       </c>
       <c r="W19">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="X19">
         <v>1.01</v>
@@ -3581,7 +3581,7 @@
         <v>2.55</v>
       </c>
       <c r="R20">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="S20">
         <v>1.31</v>
@@ -3602,16 +3602,16 @@
         <v>1.04</v>
       </c>
       <c r="Y20">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z20">
-        <v>4.02</v>
+        <v>3.9</v>
       </c>
       <c r="AA20">
         <v>1.7</v>
       </c>
       <c r="AB20">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AC20">
         <v>2.75</v>
@@ -3642,7 +3642,7 @@
         <v>1.23</v>
       </c>
       <c r="AK20">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="O21">
-        <v>2.95</v>
+        <v>3.35</v>
       </c>
       <c r="P21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AA21">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="AB21">
         <v>1.44</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>3.35</v>
+        <v>2.89</v>
       </c>
       <c r="O22">
-        <v>3.74</v>
+        <v>3.6</v>
       </c>
       <c r="P22">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="Q22">
         <v>3.6</v>
@@ -3910,7 +3910,7 @@
         <v>2.3</v>
       </c>
       <c r="S22">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T22">
         <v>3.8</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,80 +4058,80 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.72</v>
+        <v>2.65</v>
       </c>
       <c r="O23">
-        <v>4.55</v>
+        <v>3.65</v>
       </c>
       <c r="P23">
-        <v>3.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q23">
-        <v>2.13</v>
+        <v>3.22</v>
       </c>
       <c r="R23">
-        <v>2.7</v>
+        <v>2.36</v>
       </c>
       <c r="S23">
+        <v>1.22</v>
+      </c>
+      <c r="T23">
+        <v>3.9</v>
+      </c>
+      <c r="U23">
+        <v>2.14</v>
+      </c>
+      <c r="V23">
+        <v>1.64</v>
+      </c>
+      <c r="W23">
         <v>1.13</v>
       </c>
-      <c r="T23">
-        <v>5.2</v>
-      </c>
-      <c r="U23">
-        <v>1.84</v>
-      </c>
-      <c r="V23">
-        <v>1.85</v>
-      </c>
-      <c r="W23">
-        <v>1.21</v>
-      </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="Z23">
-        <v>6.25</v>
+        <v>5.45</v>
       </c>
       <c r="AA23">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AB23">
-        <v>3.5</v>
+        <v>2.52</v>
       </c>
       <c r="AC23">
-        <v>1.78</v>
+        <v>2.14</v>
       </c>
       <c r="AD23">
-        <v>1.91</v>
+        <v>1.63</v>
       </c>
       <c r="AE23">
+        <v>1.28</v>
+      </c>
+      <c r="AF23">
+        <v>1.39</v>
+      </c>
+      <c r="AG23">
+        <v>2.65</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23">
+        <v>1.25</v>
+      </c>
+      <c r="AK23">
         <v>1.4</v>
-      </c>
-      <c r="AF23">
-        <v>1.33</v>
-      </c>
-      <c r="AG23">
-        <v>3.08</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23">
-        <v>1.17</v>
-      </c>
-      <c r="AK23">
-        <v>2.02</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="O24">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="P24">
-        <v>2.2</v>
+        <v>3.18</v>
       </c>
       <c r="Q24">
-        <v>3.37</v>
+        <v>2.13</v>
       </c>
       <c r="R24">
-        <v>2.36</v>
+        <v>2.75</v>
       </c>
       <c r="S24">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="T24">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="U24">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="V24">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="W24">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="X24">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Z24">
-        <v>5.45</v>
+        <v>6.4</v>
       </c>
       <c r="AA24">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="AB24">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="AC24">
-        <v>2.08</v>
+        <v>1.78</v>
       </c>
       <c r="AD24">
-        <v>1.64</v>
+        <v>1.95</v>
       </c>
       <c r="AE24">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AF24">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="AG24">
-        <v>2.65</v>
+        <v>3.08</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK24">
-        <v>1.4</v>
+        <v>2.02</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,19 +4384,19 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="O25">
-        <v>3.33</v>
+        <v>3.4</v>
       </c>
       <c r="P25">
-        <v>4</v>
+        <v>4.96</v>
       </c>
       <c r="Q25">
         <v>2.38</v>
       </c>
       <c r="R25">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S25">
         <v>1.39</v>
@@ -4414,7 +4414,7 @@
         <v>1.05</v>
       </c>
       <c r="X25">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y25">
         <v>1.28</v>
@@ -4426,7 +4426,7 @@
         <v>2</v>
       </c>
       <c r="AB25">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AC25">
         <v>3.4</v>
@@ -4435,10 +4435,10 @@
         <v>1.28</v>
       </c>
       <c r="AE25">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF25">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AG25">
         <v>1.85</v>
@@ -4553,7 +4553,7 @@
         <v>3.25</v>
       </c>
       <c r="P26">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="Q26">
         <v>2.82</v>
@@ -4571,7 +4571,7 @@
         <v>2.94</v>
       </c>
       <c r="V26">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W26">
         <v>1.03</v>
@@ -4595,10 +4595,10 @@
         <v>3.59</v>
       </c>
       <c r="AD26">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE26">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF26">
         <v>1.74</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="O27">
         <v>4.4</v>
       </c>
       <c r="P27">
-        <v>6.65</v>
+        <v>6.83</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4888,7 +4888,7 @@
         <v>2.4</v>
       </c>
       <c r="S28">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T28">
         <v>3.25</v>
@@ -4930,7 +4930,7 @@
         <v>1.73</v>
       </c>
       <c r="AG28">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -5036,16 +5036,16 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="O29">
         <v>3.15</v>
       </c>
       <c r="P29">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="Q29">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="R29">
         <v>1.95</v>
@@ -5078,7 +5078,7 @@
         <v>2.38</v>
       </c>
       <c r="AB29">
-        <v>1.59</v>
+        <v>1.68</v>
       </c>
       <c r="AC29">
         <v>4.4</v>
@@ -5202,16 +5202,16 @@
         <v>2.3</v>
       </c>
       <c r="O30">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="P30">
         <v>2.87</v>
       </c>
       <c r="Q30">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="R30">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="S30">
         <v>1.34</v>
@@ -5253,10 +5253,10 @@
         <v>1.14</v>
       </c>
       <c r="AF30">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AG30">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="O31">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="P31">
-        <v>3.25</v>
+        <v>2.93</v>
       </c>
       <c r="Q31">
         <v>2.3</v>
@@ -5525,7 +5525,7 @@
         </is>
       </c>
       <c r="N32">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="O32">
         <v>6.25</v>
@@ -5540,7 +5540,7 @@
         <v>2.62</v>
       </c>
       <c r="S32">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T32">
         <v>3.45</v>
@@ -5555,16 +5555,16 @@
         <v>1.1</v>
       </c>
       <c r="X32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z32">
         <v>4.42</v>
       </c>
       <c r="AA32">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AB32">
         <v>2.12</v>
@@ -5582,7 +5582,7 @@
         <v>2.15</v>
       </c>
       <c r="AG32">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5688,16 +5688,16 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="O33">
         <v>4.6</v>
       </c>
       <c r="P33">
-        <v>8.25</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q33">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="R33">
         <v>2.55</v>
@@ -5709,13 +5709,13 @@
         <v>3.42</v>
       </c>
       <c r="U33">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="V33">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="W33">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X33">
         <v>1.01</v>
@@ -5727,13 +5727,13 @@
         <v>4.5</v>
       </c>
       <c r="AA33">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB33">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="AC33">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="AD33">
         <v>1.46</v>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AK33">
         <v>3.25</v>
@@ -6032,7 +6032,7 @@
         <v>1.38</v>
       </c>
       <c r="T35">
-        <v>3</v>
+        <v>2.66</v>
       </c>
       <c r="U35">
         <v>2.8</v>
@@ -6349,16 +6349,16 @@
         <v>4.15</v>
       </c>
       <c r="Q37">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="R37">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="S37">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T37">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="U37">
         <v>2.75</v>
@@ -6379,25 +6379,25 @@
         <v>3.34</v>
       </c>
       <c r="AA37">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB37">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC37">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AD37">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE37">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF37">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AG37">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AK37">
         <v>1.97</v>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="O38">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="P38">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="Q38">
         <v>2.81</v>
@@ -6548,7 +6548,7 @@
         <v>1.67</v>
       </c>
       <c r="AC38">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="AD38">
         <v>1.22</v>
@@ -6560,7 +6560,7 @@
         <v>1.82</v>
       </c>
       <c r="AG38">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>2.3</v>
       </c>
       <c r="S40">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T40">
         <v>3.02</v>

--- a/jogos_2026-08-17.xlsx
+++ b/jogos_2026-08-17.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU41"/>
+  <dimension ref="A1:AU42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -3033,27 +3033,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,80 +3080,80 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.32</v>
+        <v>9</v>
       </c>
       <c r="O17">
+        <v>5.5</v>
+      </c>
+      <c r="P17">
+        <v>1.21</v>
+      </c>
+      <c r="Q17">
+        <v>8</v>
+      </c>
+      <c r="R17">
+        <v>2.61</v>
+      </c>
+      <c r="S17">
+        <v>1.24</v>
+      </c>
+      <c r="T17">
+        <v>3.34</v>
+      </c>
+      <c r="U17">
+        <v>2.2</v>
+      </c>
+      <c r="V17">
+        <v>1.65</v>
+      </c>
+      <c r="W17">
+        <v>1.12</v>
+      </c>
+      <c r="X17">
+        <v>1.01</v>
+      </c>
+      <c r="Y17">
+        <v>1.14</v>
+      </c>
+      <c r="Z17">
+        <v>4.7</v>
+      </c>
+      <c r="AA17">
+        <v>1.41</v>
+      </c>
+      <c r="AB17">
+        <v>2.55</v>
+      </c>
+      <c r="AC17">
+        <v>2.3</v>
+      </c>
+      <c r="AD17">
+        <v>1.64</v>
+      </c>
+      <c r="AE17">
+        <v>1.21</v>
+      </c>
+      <c r="AF17">
+        <v>1.93</v>
+      </c>
+      <c r="AG17">
+        <v>1.76</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17">
         <v>3.45</v>
       </c>
-      <c r="P17">
-        <v>1.94</v>
-      </c>
-      <c r="Q17">
-        <v>3.5</v>
-      </c>
-      <c r="R17">
-        <v>2.3</v>
-      </c>
-      <c r="S17">
-        <v>1.3</v>
-      </c>
-      <c r="T17">
-        <v>3</v>
-      </c>
-      <c r="U17">
-        <v>2.38</v>
-      </c>
-      <c r="V17">
-        <v>1.4</v>
-      </c>
-      <c r="W17">
-        <v>1.08</v>
-      </c>
-      <c r="X17">
-        <v>1</v>
-      </c>
-      <c r="Y17">
-        <v>1.17</v>
-      </c>
-      <c r="Z17">
-        <v>3.9</v>
-      </c>
-      <c r="AA17">
-        <v>1.55</v>
-      </c>
-      <c r="AB17">
-        <v>1.8</v>
-      </c>
-      <c r="AC17">
-        <v>2.52</v>
-      </c>
-      <c r="AD17">
-        <v>1.41</v>
-      </c>
-      <c r="AE17">
-        <v>1.13</v>
-      </c>
-      <c r="AF17">
-        <v>1.62</v>
-      </c>
-      <c r="AG17">
-        <v>2.2</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17">
-        <v>1.3</v>
-      </c>
       <c r="AK17">
-        <v>1.23</v>
+        <v>1.04</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2026-08-17 15:00:00</t>
+          <t>2026-08-17 14:30:00</t>
         </is>
       </c>
     </row>
@@ -3201,22 +3201,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,80 +3243,80 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.14</v>
+        <v>3.32</v>
       </c>
       <c r="O18">
-        <v>2.59</v>
+        <v>3.45</v>
       </c>
       <c r="P18">
-        <v>3.6</v>
+        <v>1.94</v>
       </c>
       <c r="Q18">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="R18">
+        <v>2.3</v>
+      </c>
+      <c r="S18">
+        <v>1.3</v>
+      </c>
+      <c r="T18">
+        <v>3</v>
+      </c>
+      <c r="U18">
+        <v>2.38</v>
+      </c>
+      <c r="V18">
+        <v>1.4</v>
+      </c>
+      <c r="W18">
+        <v>1.08</v>
+      </c>
+      <c r="X18">
+        <v>1</v>
+      </c>
+      <c r="Y18">
+        <v>1.17</v>
+      </c>
+      <c r="Z18">
+        <v>3.9</v>
+      </c>
+      <c r="AA18">
+        <v>1.55</v>
+      </c>
+      <c r="AB18">
         <v>1.8</v>
       </c>
-      <c r="S18">
-        <v>1.7</v>
-      </c>
-      <c r="T18">
-        <v>2.08</v>
-      </c>
-      <c r="U18">
-        <v>4.45</v>
-      </c>
-      <c r="V18">
-        <v>1.2</v>
-      </c>
-      <c r="W18">
-        <v>1.03</v>
-      </c>
-      <c r="X18">
-        <v>1.1</v>
-      </c>
-      <c r="Y18">
-        <v>1.55</v>
-      </c>
-      <c r="Z18">
-        <v>2.25</v>
-      </c>
-      <c r="AA18">
-        <v>3.14</v>
-      </c>
-      <c r="AB18">
+      <c r="AC18">
+        <v>2.52</v>
+      </c>
+      <c r="AD18">
+        <v>1.41</v>
+      </c>
+      <c r="AE18">
+        <v>1.13</v>
+      </c>
+      <c r="AF18">
+        <v>1.62</v>
+      </c>
+      <c r="AG18">
+        <v>2.2</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18">
         <v>1.3</v>
       </c>
-      <c r="AC18">
-        <v>7.1</v>
-      </c>
-      <c r="AD18">
-        <v>1.08</v>
-      </c>
-      <c r="AE18">
-        <v>1.02</v>
-      </c>
-      <c r="AF18">
-        <v>2.51</v>
-      </c>
-      <c r="AG18">
-        <v>1.44</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18">
-        <v>1.44</v>
-      </c>
       <c r="AK18">
-        <v>1.6</v>
+        <v>1.23</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="O19">
-        <v>3.75</v>
+        <v>2.7</v>
       </c>
       <c r="P19">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="Q19">
-        <v>2.38</v>
+        <v>3.1</v>
       </c>
       <c r="R19">
-        <v>2.49</v>
+        <v>1.8</v>
       </c>
       <c r="S19">
-        <v>1.17</v>
+        <v>1.7</v>
       </c>
       <c r="T19">
-        <v>4.1</v>
+        <v>2.08</v>
       </c>
       <c r="U19">
-        <v>1.92</v>
+        <v>4.45</v>
       </c>
       <c r="V19">
-        <v>1.85</v>
+        <v>1.2</v>
       </c>
       <c r="W19">
-        <v>1.22</v>
+        <v>1.03</v>
       </c>
       <c r="X19">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="Y19">
-        <v>1.11</v>
+        <v>1.55</v>
       </c>
       <c r="Z19">
-        <v>6.24</v>
+        <v>2</v>
       </c>
       <c r="AA19">
-        <v>1.29</v>
+        <v>3.14</v>
       </c>
       <c r="AB19">
-        <v>3.16</v>
+        <v>1.3</v>
       </c>
       <c r="AC19">
-        <v>1.83</v>
+        <v>7.1</v>
       </c>
       <c r="AD19">
-        <v>1.93</v>
+        <v>1.08</v>
       </c>
       <c r="AE19">
-        <v>1.36</v>
+        <v>1.02</v>
       </c>
       <c r="AF19">
-        <v>1.3</v>
+        <v>2.51</v>
       </c>
       <c r="AG19">
-        <v>3.1</v>
+        <v>1.44</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.17</v>
+        <v>1.44</v>
       </c>
       <c r="AK19">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3527,22 +3527,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="O20">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="P20">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="Q20">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="R20">
-        <v>2.32</v>
+        <v>2.49</v>
       </c>
       <c r="S20">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="T20">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="U20">
-        <v>2.44</v>
+        <v>1.92</v>
       </c>
       <c r="V20">
-        <v>1.46</v>
+        <v>1.85</v>
       </c>
       <c r="W20">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="X20">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="Z20">
-        <v>3.9</v>
+        <v>6.24</v>
       </c>
       <c r="AA20">
-        <v>1.7</v>
+        <v>1.29</v>
       </c>
       <c r="AB20">
-        <v>2.03</v>
+        <v>3.16</v>
       </c>
       <c r="AC20">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="AD20">
-        <v>1.38</v>
+        <v>1.93</v>
       </c>
       <c r="AE20">
-        <v>1.12</v>
+        <v>1.36</v>
       </c>
       <c r="AF20">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="AG20">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AK20">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.52</v>
+        <v>1.95</v>
       </c>
       <c r="O21">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P21">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="Q21">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="R21">
-        <v>1.95</v>
+        <v>2.32</v>
       </c>
       <c r="S21">
-        <v>1.53</v>
+        <v>1.31</v>
       </c>
       <c r="T21">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="U21">
-        <v>4</v>
+        <v>2.44</v>
       </c>
       <c r="V21">
-        <v>1.2</v>
+        <v>1.46</v>
       </c>
       <c r="W21">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="X21">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y21">
-        <v>1.48</v>
+        <v>1.19</v>
       </c>
       <c r="Z21">
-        <v>2.33</v>
+        <v>3.9</v>
       </c>
       <c r="AA21">
-        <v>2.54</v>
+        <v>1.7</v>
       </c>
       <c r="AB21">
-        <v>1.44</v>
+        <v>2.03</v>
       </c>
       <c r="AC21">
-        <v>4.8</v>
+        <v>2.75</v>
       </c>
       <c r="AD21">
-        <v>1.11</v>
+        <v>1.38</v>
       </c>
       <c r="AE21">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AF21">
-        <v>2.5</v>
+        <v>1.57</v>
       </c>
       <c r="AG21">
-        <v>1.45</v>
+        <v>2.2</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>1.23</v>
       </c>
       <c r="AK21">
-        <v>2.19</v>
+        <v>1.7</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,65 +3895,65 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.89</v>
+        <v>1.52</v>
       </c>
       <c r="O22">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="P22">
-        <v>1.97</v>
+        <v>6</v>
       </c>
       <c r="Q22">
-        <v>3.6</v>
+        <v>2.15</v>
       </c>
       <c r="R22">
+        <v>1.95</v>
+      </c>
+      <c r="S22">
+        <v>1.53</v>
+      </c>
+      <c r="T22">
         <v>2.3</v>
       </c>
-      <c r="S22">
-        <v>1.24</v>
-      </c>
-      <c r="T22">
-        <v>3.8</v>
-      </c>
       <c r="U22">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="V22">
-        <v>1.59</v>
+        <v>1.2</v>
       </c>
       <c r="W22">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="X22">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y22">
-        <v>1.15</v>
+        <v>1.48</v>
       </c>
       <c r="Z22">
-        <v>4.95</v>
+        <v>2.33</v>
       </c>
       <c r="AA22">
-        <v>1.47</v>
+        <v>2.54</v>
       </c>
       <c r="AB22">
-        <v>2.35</v>
+        <v>1.44</v>
       </c>
       <c r="AC22">
-        <v>2.31</v>
+        <v>4.8</v>
       </c>
       <c r="AD22">
-        <v>1.57</v>
+        <v>1.11</v>
       </c>
       <c r="AE22">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="AF22">
+        <v>2.5</v>
+      </c>
+      <c r="AG22">
         <v>1.45</v>
       </c>
-      <c r="AG22">
-        <v>2.5</v>
-      </c>
       <c r="AH22" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AK22">
-        <v>1.24</v>
+        <v>2.19</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.65</v>
+        <v>2.89</v>
       </c>
       <c r="O23">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P23">
+        <v>1.97</v>
+      </c>
+      <c r="Q23">
+        <v>3.6</v>
+      </c>
+      <c r="R23">
+        <v>2.3</v>
+      </c>
+      <c r="S23">
+        <v>1.24</v>
+      </c>
+      <c r="T23">
+        <v>3.8</v>
+      </c>
+      <c r="U23">
         <v>2.2</v>
       </c>
-      <c r="Q23">
-        <v>3.22</v>
-      </c>
-      <c r="R23">
-        <v>2.36</v>
-      </c>
-      <c r="S23">
-        <v>1.22</v>
-      </c>
-      <c r="T23">
-        <v>3.9</v>
-      </c>
-      <c r="U23">
-        <v>2.14</v>
-      </c>
       <c r="V23">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="W23">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X23">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y23">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z23">
-        <v>5.45</v>
+        <v>4.95</v>
       </c>
       <c r="AA23">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB23">
-        <v>2.52</v>
+        <v>2.35</v>
       </c>
       <c r="AC23">
-        <v>2.14</v>
+        <v>2.31</v>
       </c>
       <c r="AD23">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AE23">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AF23">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AG23">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK23">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4337,12 +4337,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,81 +4384,81 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.66</v>
+        <v>2.65</v>
       </c>
       <c r="O25">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="P25">
-        <v>4.96</v>
+        <v>2.2</v>
       </c>
       <c r="Q25">
-        <v>2.38</v>
+        <v>3.22</v>
       </c>
       <c r="R25">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="S25">
+        <v>1.22</v>
+      </c>
+      <c r="T25">
+        <v>3.9</v>
+      </c>
+      <c r="U25">
+        <v>2.14</v>
+      </c>
+      <c r="V25">
+        <v>1.64</v>
+      </c>
+      <c r="W25">
+        <v>1.13</v>
+      </c>
+      <c r="X25">
+        <v>1.02</v>
+      </c>
+      <c r="Y25">
+        <v>1.13</v>
+      </c>
+      <c r="Z25">
+        <v>5.45</v>
+      </c>
+      <c r="AA25">
+        <v>1.44</v>
+      </c>
+      <c r="AB25">
+        <v>2.52</v>
+      </c>
+      <c r="AC25">
+        <v>2.14</v>
+      </c>
+      <c r="AD25">
+        <v>1.63</v>
+      </c>
+      <c r="AE25">
+        <v>1.28</v>
+      </c>
+      <c r="AF25">
         <v>1.39</v>
       </c>
-      <c r="T25">
-        <v>2.89</v>
-      </c>
-      <c r="U25">
-        <v>2.8</v>
-      </c>
-      <c r="V25">
+      <c r="AG25">
+        <v>2.65</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25">
+        <v>1.25</v>
+      </c>
+      <c r="AK25">
         <v>1.4</v>
       </c>
-      <c r="W25">
-        <v>1.05</v>
-      </c>
-      <c r="X25">
-        <v>1.06</v>
-      </c>
-      <c r="Y25">
-        <v>1.28</v>
-      </c>
-      <c r="Z25">
-        <v>3.08</v>
-      </c>
-      <c r="AA25">
-        <v>2</v>
-      </c>
-      <c r="AB25">
-        <v>1.81</v>
-      </c>
-      <c r="AC25">
-        <v>3.4</v>
-      </c>
-      <c r="AD25">
-        <v>1.28</v>
-      </c>
-      <c r="AE25">
-        <v>1.1</v>
-      </c>
-      <c r="AF25">
-        <v>1.72</v>
-      </c>
-      <c r="AG25">
-        <v>1.85</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ25">
-        <v>1.19</v>
-      </c>
-      <c r="AK25">
-        <v>1.91</v>
-      </c>
       <c r="AL25">
         <v>0</v>
       </c>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>2026-08-17 15:15:00</t>
+          <t>2026-08-17 15:00:00</t>
         </is>
       </c>
     </row>
@@ -4500,12 +4500,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.25</v>
+        <v>1.66</v>
       </c>
       <c r="O26">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P26">
-        <v>3.2</v>
+        <v>4.96</v>
       </c>
       <c r="Q26">
-        <v>2.82</v>
+        <v>2.38</v>
       </c>
       <c r="R26">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="S26">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="T26">
-        <v>2.59</v>
+        <v>2.89</v>
       </c>
       <c r="U26">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="V26">
         <v>1.4</v>
       </c>
       <c r="W26">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X26">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y26">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z26">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="AA26">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB26">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="AC26">
-        <v>3.59</v>
+        <v>3.4</v>
       </c>
       <c r="AD26">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AE26">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF26">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AG26">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AK26">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>2026-08-17 15:30:00</t>
+          <t>2026-08-17 15:15:00</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Batman Petrolspor</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.34</v>
+        <v>2.25</v>
       </c>
       <c r="O27">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="P27">
-        <v>6.83</v>
+        <v>3.2</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Batman Petrolspor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.53</v>
+        <v>1.34</v>
       </c>
       <c r="O28">
-        <v>4.15</v>
+        <v>4.4</v>
       </c>
       <c r="P28">
-        <v>5.4</v>
+        <v>6.83</v>
       </c>
       <c r="Q28">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R28">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S28">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T28">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U28">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="V28">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W28">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y28">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z28">
-        <v>4.31</v>
+        <v>0</v>
       </c>
       <c r="AA28">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB28">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AC28">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD28">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AE28">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF28">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG28">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK28">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -4989,12 +4989,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,81 +5036,81 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.35</v>
+        <v>1.52</v>
       </c>
       <c r="O29">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="P29">
+        <v>5.25</v>
+      </c>
+      <c r="Q29">
+        <v>2</v>
+      </c>
+      <c r="R29">
+        <v>2.4</v>
+      </c>
+      <c r="S29">
+        <v>1.25</v>
+      </c>
+      <c r="T29">
         <v>3.25</v>
       </c>
-      <c r="Q29">
-        <v>3.1</v>
-      </c>
-      <c r="R29">
-        <v>1.95</v>
-      </c>
-      <c r="S29">
-        <v>1.55</v>
-      </c>
-      <c r="T29">
-        <v>2.44</v>
-      </c>
       <c r="U29">
-        <v>3.3</v>
+        <v>2.39</v>
       </c>
       <c r="V29">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="W29">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X29">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
+        <v>1.2</v>
+      </c>
+      <c r="Z29">
+        <v>4.37</v>
+      </c>
+      <c r="AA29">
+        <v>1.65</v>
+      </c>
+      <c r="AB29">
+        <v>2.17</v>
+      </c>
+      <c r="AC29">
+        <v>2.63</v>
+      </c>
+      <c r="AD29">
         <v>1.42</v>
       </c>
-      <c r="Z29">
-        <v>2.62</v>
-      </c>
-      <c r="AA29">
+      <c r="AE29">
+        <v>1.14</v>
+      </c>
+      <c r="AF29">
+        <v>1.73</v>
+      </c>
+      <c r="AG29">
+        <v>2</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29">
+        <v>1.14</v>
+      </c>
+      <c r="AK29">
         <v>2.38</v>
       </c>
-      <c r="AB29">
-        <v>1.68</v>
-      </c>
-      <c r="AC29">
-        <v>4.4</v>
-      </c>
-      <c r="AD29">
-        <v>1.2</v>
-      </c>
-      <c r="AE29">
-        <v>1.02</v>
-      </c>
-      <c r="AF29">
-        <v>1.91</v>
-      </c>
-      <c r="AG29">
-        <v>1.81</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ29">
-        <v>1.25</v>
-      </c>
-      <c r="AK29">
-        <v>1.58</v>
-      </c>
       <c r="AL29">
         <v>0</v>
       </c>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>2026-08-17 16:00:00</t>
+          <t>2026-08-17 15:30:00</t>
         </is>
       </c>
     </row>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="O30">
-        <v>3.42</v>
+        <v>3.15</v>
       </c>
       <c r="P30">
-        <v>2.87</v>
+        <v>3.25</v>
       </c>
       <c r="Q30">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="R30">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="S30">
-        <v>1.34</v>
+        <v>1.55</v>
       </c>
       <c r="T30">
-        <v>2.9</v>
+        <v>2.44</v>
       </c>
       <c r="U30">
-        <v>2.58</v>
+        <v>3.3</v>
       </c>
       <c r="V30">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="W30">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X30">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y30">
+        <v>1.42</v>
+      </c>
+      <c r="Z30">
+        <v>2.62</v>
+      </c>
+      <c r="AA30">
+        <v>2.38</v>
+      </c>
+      <c r="AB30">
+        <v>1.68</v>
+      </c>
+      <c r="AC30">
+        <v>4.4</v>
+      </c>
+      <c r="AD30">
         <v>1.2</v>
       </c>
-      <c r="Z30">
-        <v>4.1</v>
-      </c>
-      <c r="AA30">
-        <v>1.76</v>
-      </c>
-      <c r="AB30">
-        <v>2.09</v>
-      </c>
-      <c r="AC30">
-        <v>2.68</v>
-      </c>
-      <c r="AD30">
-        <v>1.4</v>
-      </c>
       <c r="AE30">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="AF30">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AG30">
-        <v>2.3</v>
+        <v>1.81</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AK30">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5315,27 +5315,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="O31">
-        <v>4.2</v>
+        <v>3.42</v>
       </c>
       <c r="P31">
-        <v>2.93</v>
+        <v>2.87</v>
       </c>
       <c r="Q31">
-        <v>2.3</v>
+        <v>2.74</v>
       </c>
       <c r="R31">
-        <v>2.88</v>
+        <v>2.35</v>
       </c>
       <c r="S31">
-        <v>1.13</v>
+        <v>1.34</v>
       </c>
       <c r="T31">
-        <v>4.75</v>
+        <v>2.9</v>
       </c>
       <c r="U31">
-        <v>1.73</v>
+        <v>2.58</v>
       </c>
       <c r="V31">
-        <v>2.1</v>
+        <v>1.46</v>
       </c>
       <c r="W31">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="X31">
         <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="Z31">
-        <v>7.8</v>
+        <v>4.1</v>
       </c>
       <c r="AA31">
-        <v>1.24</v>
+        <v>1.76</v>
       </c>
       <c r="AB31">
-        <v>3.82</v>
+        <v>2.09</v>
       </c>
       <c r="AC31">
+        <v>2.68</v>
+      </c>
+      <c r="AD31">
+        <v>1.4</v>
+      </c>
+      <c r="AE31">
+        <v>1.14</v>
+      </c>
+      <c r="AF31">
         <v>1.62</v>
       </c>
-      <c r="AD31">
-        <v>2.24</v>
-      </c>
-      <c r="AE31">
-        <v>1.51</v>
-      </c>
-      <c r="AF31">
-        <v>1.25</v>
-      </c>
       <c r="AG31">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="AK31">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>2026-08-17 16:15:00</t>
+          <t>2026-08-17 16:00:00</t>
         </is>
       </c>
     </row>
@@ -5483,22 +5483,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>9.4</v>
+        <v>1.92</v>
       </c>
       <c r="O32">
-        <v>6.25</v>
+        <v>4.2</v>
       </c>
       <c r="P32">
-        <v>1.18</v>
+        <v>2.93</v>
       </c>
       <c r="Q32">
-        <v>11</v>
+        <v>2.3</v>
       </c>
       <c r="R32">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="S32">
+        <v>1.13</v>
+      </c>
+      <c r="T32">
+        <v>4.75</v>
+      </c>
+      <c r="U32">
+        <v>1.73</v>
+      </c>
+      <c r="V32">
+        <v>2.1</v>
+      </c>
+      <c r="W32">
         <v>1.28</v>
-      </c>
-      <c r="T32">
-        <v>3.45</v>
-      </c>
-      <c r="U32">
-        <v>2.25</v>
-      </c>
-      <c r="V32">
-        <v>1.52</v>
-      </c>
-      <c r="W32">
-        <v>1.1</v>
       </c>
       <c r="X32">
         <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="Z32">
-        <v>4.42</v>
+        <v>7.8</v>
       </c>
       <c r="AA32">
-        <v>1.61</v>
+        <v>1.24</v>
       </c>
       <c r="AB32">
-        <v>2.12</v>
+        <v>3.82</v>
       </c>
       <c r="AC32">
-        <v>2.38</v>
+        <v>1.62</v>
       </c>
       <c r="AD32">
-        <v>1.5</v>
+        <v>2.24</v>
       </c>
       <c r="AE32">
-        <v>1.16</v>
+        <v>1.51</v>
       </c>
       <c r="AF32">
-        <v>2.15</v>
+        <v>1.25</v>
       </c>
       <c r="AG32">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>4.46</v>
+        <v>1.19</v>
       </c>
       <c r="AK32">
-        <v>1.02</v>
+        <v>1.77</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.3</v>
+        <v>9.4</v>
       </c>
       <c r="O33">
-        <v>4.6</v>
+        <v>6.25</v>
       </c>
       <c r="P33">
-        <v>9.300000000000001</v>
+        <v>1.18</v>
       </c>
       <c r="Q33">
-        <v>1.73</v>
+        <v>11</v>
       </c>
       <c r="R33">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="S33">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T33">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="U33">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="V33">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W33">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X33">
         <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z33">
-        <v>4.5</v>
+        <v>4.42</v>
       </c>
       <c r="AA33">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AB33">
-        <v>2.26</v>
+        <v>2.12</v>
       </c>
       <c r="AC33">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AD33">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AE33">
         <v>1.16</v>
       </c>
       <c r="AF33">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AG33">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.15</v>
+        <v>4.46</v>
       </c>
       <c r="AK33">
-        <v>3.25</v>
+        <v>1.02</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>2026-08-17 16:30:00</t>
+          <t>2026-08-17 16:15:00</t>
         </is>
       </c>
     </row>
@@ -5804,27 +5804,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.92</v>
+        <v>1.3</v>
       </c>
       <c r="O34">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="P34">
-        <v>3.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q34">
-        <v>2.4</v>
+        <v>1.73</v>
       </c>
       <c r="R34">
-        <v>2.02</v>
+        <v>2.55</v>
       </c>
       <c r="S34">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="T34">
-        <v>2.69</v>
+        <v>3.42</v>
       </c>
       <c r="U34">
-        <v>2.9</v>
+        <v>2.38</v>
       </c>
       <c r="V34">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="W34">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X34">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="Z34">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="AA34">
-        <v>2.06</v>
+        <v>1.65</v>
       </c>
       <c r="AB34">
-        <v>1.72</v>
+        <v>2.26</v>
       </c>
       <c r="AC34">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="AD34">
-        <v>1.29</v>
+        <v>1.46</v>
       </c>
       <c r="AE34">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="AF34">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="AG34">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="AK34">
-        <v>1.8</v>
+        <v>3.25</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>2026-08-17 19:00:00</t>
+          <t>2026-08-17 16:30:00</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,65 +6014,65 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.19</v>
+        <v>1.91</v>
       </c>
       <c r="O35">
+        <v>3.2</v>
+      </c>
+      <c r="P35">
+        <v>3.5</v>
+      </c>
+      <c r="Q35">
+        <v>2.56</v>
+      </c>
+      <c r="R35">
+        <v>2.02</v>
+      </c>
+      <c r="S35">
+        <v>1.41</v>
+      </c>
+      <c r="T35">
+        <v>2.59</v>
+      </c>
+      <c r="U35">
+        <v>2.9</v>
+      </c>
+      <c r="V35">
+        <v>1.33</v>
+      </c>
+      <c r="W35">
+        <v>1.05</v>
+      </c>
+      <c r="X35">
+        <v>1.02</v>
+      </c>
+      <c r="Y35">
+        <v>1.27</v>
+      </c>
+      <c r="Z35">
+        <v>3.2</v>
+      </c>
+      <c r="AA35">
+        <v>2.06</v>
+      </c>
+      <c r="AB35">
+        <v>1.72</v>
+      </c>
+      <c r="AC35">
         <v>3.1</v>
       </c>
-      <c r="P35">
-        <v>2.99</v>
-      </c>
-      <c r="Q35">
-        <v>2.8</v>
-      </c>
-      <c r="R35">
-        <v>2.1</v>
-      </c>
-      <c r="S35">
-        <v>1.38</v>
-      </c>
-      <c r="T35">
-        <v>2.66</v>
-      </c>
-      <c r="U35">
-        <v>2.8</v>
-      </c>
-      <c r="V35">
-        <v>1.39</v>
-      </c>
-      <c r="W35">
-        <v>1.07</v>
-      </c>
-      <c r="X35">
-        <v>1.06</v>
-      </c>
-      <c r="Y35">
-        <v>1.25</v>
-      </c>
-      <c r="Z35">
-        <v>3.3</v>
-      </c>
-      <c r="AA35">
+      <c r="AD35">
+        <v>1.29</v>
+      </c>
+      <c r="AE35">
+        <v>1.08</v>
+      </c>
+      <c r="AF35">
+        <v>1.83</v>
+      </c>
+      <c r="AG35">
         <v>1.91</v>
       </c>
-      <c r="AB35">
-        <v>1.75</v>
-      </c>
-      <c r="AC35">
-        <v>3.3</v>
-      </c>
-      <c r="AD35">
-        <v>1.27</v>
-      </c>
-      <c r="AE35">
-        <v>1.1</v>
-      </c>
-      <c r="AF35">
-        <v>1.71</v>
-      </c>
-      <c r="AG35">
-        <v>2</v>
-      </c>
       <c r="AH35" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK35">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6130,12 +6130,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.64</v>
+        <v>2.19</v>
       </c>
       <c r="O36">
-        <v>3.96</v>
+        <v>3.1</v>
       </c>
       <c r="P36">
-        <v>5.61</v>
+        <v>2.99</v>
       </c>
       <c r="Q36">
-        <v>2.09</v>
+        <v>2.8</v>
       </c>
       <c r="R36">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="S36">
+        <v>1.39</v>
+      </c>
+      <c r="T36">
+        <v>2.66</v>
+      </c>
+      <c r="U36">
+        <v>2.78</v>
+      </c>
+      <c r="V36">
         <v>1.36</v>
-      </c>
-      <c r="T36">
-        <v>2.82</v>
-      </c>
-      <c r="U36">
-        <v>2.6</v>
-      </c>
-      <c r="V36">
-        <v>1.44</v>
       </c>
       <c r="W36">
         <v>1.07</v>
       </c>
       <c r="X36">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="Z36">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="AA36">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AB36">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AC36">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="AD36">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AE36">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AF36">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AG36">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK36">
-        <v>2.38</v>
+        <v>1.57</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>2026-08-17 20:00:00</t>
+          <t>2026-08-17 19:00:00</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="O37">
-        <v>3.25</v>
+        <v>3.96</v>
       </c>
       <c r="P37">
-        <v>4.15</v>
+        <v>5.61</v>
       </c>
       <c r="Q37">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="R37">
-        <v>2.03</v>
+        <v>2.23</v>
       </c>
       <c r="S37">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T37">
-        <v>2.67</v>
+        <v>2.82</v>
       </c>
       <c r="U37">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="V37">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W37">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X37">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z37">
-        <v>3.34</v>
+        <v>3.7</v>
       </c>
       <c r="AA37">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AB37">
+        <v>1.88</v>
+      </c>
+      <c r="AC37">
+        <v>3</v>
+      </c>
+      <c r="AD37">
+        <v>1.33</v>
+      </c>
+      <c r="AE37">
+        <v>1.14</v>
+      </c>
+      <c r="AF37">
         <v>1.85</v>
       </c>
-      <c r="AC37">
-        <v>3.4</v>
-      </c>
-      <c r="AD37">
-        <v>1.29</v>
-      </c>
-      <c r="AE37">
-        <v>1.1</v>
-      </c>
-      <c r="AF37">
-        <v>1.79</v>
-      </c>
       <c r="AG37">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK37">
-        <v>1.97</v>
+        <v>2.38</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6619,12 +6619,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.85</v>
+        <v>1.67</v>
       </c>
       <c r="O39">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P39">
-        <v>2.2</v>
+        <v>4.15</v>
       </c>
       <c r="Q39">
-        <v>3.86</v>
+        <v>2.3</v>
       </c>
       <c r="R39">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="S39">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="T39">
+        <v>2.67</v>
+      </c>
+      <c r="U39">
         <v>2.75</v>
-      </c>
-      <c r="U39">
-        <v>2.8</v>
       </c>
       <c r="V39">
         <v>1.36</v>
       </c>
       <c r="W39">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X39">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y39">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Z39">
-        <v>3.07</v>
+        <v>3.34</v>
       </c>
       <c r="AA39">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AB39">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AC39">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AD39">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AE39">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AF39">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AG39">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AK39">
-        <v>1.33</v>
+        <v>1.97</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>2026-08-17 21:00:00</t>
+          <t>2026-08-17 20:00:00</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.95</v>
+        <v>2.85</v>
       </c>
       <c r="O40">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P40">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="Q40">
-        <v>2.5</v>
+        <v>3.86</v>
       </c>
       <c r="R40">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="S40">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="T40">
-        <v>3.02</v>
+        <v>2.75</v>
       </c>
       <c r="U40">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="V40">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W40">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X40">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="Z40">
-        <v>3.74</v>
+        <v>3.07</v>
       </c>
       <c r="AA40">
-        <v>1.71</v>
+        <v>2.15</v>
       </c>
       <c r="AB40">
-        <v>1.96</v>
+        <v>1.7</v>
       </c>
       <c r="AC40">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="AD40">
-        <v>1.35</v>
+        <v>1.21</v>
       </c>
       <c r="AE40">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AF40">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="AG40">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AK40">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6933,7 +6933,7 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>2026-08-17 21:30:00</t>
+          <t>2026-08-17 21:00:00</t>
         </is>
       </c>
     </row>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,109 +6992,272 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="O41">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P41">
-        <v>4.22</v>
+        <v>3.2</v>
       </c>
       <c r="Q41">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="R41">
         <v>2.3</v>
       </c>
       <c r="S41">
+        <v>1.34</v>
+      </c>
+      <c r="T41">
+        <v>3.02</v>
+      </c>
+      <c r="U41">
+        <v>2.63</v>
+      </c>
+      <c r="V41">
+        <v>1.44</v>
+      </c>
+      <c r="W41">
+        <v>1.1</v>
+      </c>
+      <c r="X41">
+        <v>1.02</v>
+      </c>
+      <c r="Y41">
+        <v>1.19</v>
+      </c>
+      <c r="Z41">
+        <v>3.74</v>
+      </c>
+      <c r="AA41">
+        <v>1.71</v>
+      </c>
+      <c r="AB41">
+        <v>1.96</v>
+      </c>
+      <c r="AC41">
+        <v>2.9</v>
+      </c>
+      <c r="AD41">
+        <v>1.35</v>
+      </c>
+      <c r="AE41">
+        <v>1.13</v>
+      </c>
+      <c r="AF41">
+        <v>1.62</v>
+      </c>
+      <c r="AG41">
+        <v>2.2</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ41">
+        <v>1.23</v>
+      </c>
+      <c r="AK41">
+        <v>1.73</v>
+      </c>
+      <c r="AL41">
+        <v>0</v>
+      </c>
+      <c r="AM41">
+        <v>-1</v>
+      </c>
+      <c r="AN41">
+        <v>-1</v>
+      </c>
+      <c r="AO41">
+        <v>-1</v>
+      </c>
+      <c r="AP41">
+        <v>-1</v>
+      </c>
+      <c r="AQ41">
+        <v>0</v>
+      </c>
+      <c r="AR41">
+        <v>0</v>
+      </c>
+      <c r="AS41">
+        <v>0</v>
+      </c>
+      <c r="AT41">
+        <v>0</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>2026-08-17 21:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Palestino</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Huachipato</t>
+        </is>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N42">
+        <v>1.72</v>
+      </c>
+      <c r="O42">
+        <v>3.55</v>
+      </c>
+      <c r="P42">
+        <v>4.18</v>
+      </c>
+      <c r="Q42">
+        <v>2.3</v>
+      </c>
+      <c r="R42">
+        <v>2.3</v>
+      </c>
+      <c r="S42">
         <v>1.3</v>
       </c>
-      <c r="T41">
-        <v>3.25</v>
-      </c>
-      <c r="U41">
-        <v>2.37</v>
-      </c>
-      <c r="V41">
+      <c r="T42">
+        <v>3.2</v>
+      </c>
+      <c r="U42">
+        <v>2.53</v>
+      </c>
+      <c r="V42">
         <v>1.5</v>
       </c>
-      <c r="W41">
+      <c r="W42">
         <v>1.11</v>
       </c>
-      <c r="X41">
+      <c r="X42">
         <v>1.01</v>
       </c>
-      <c r="Y41">
+      <c r="Y42">
         <v>1.2</v>
       </c>
-      <c r="Z41">
+      <c r="Z42">
         <v>4</v>
       </c>
-      <c r="AA41">
+      <c r="AA42">
         <v>1.74</v>
       </c>
-      <c r="AB41">
+      <c r="AB42">
         <v>2.1</v>
       </c>
-      <c r="AC41">
+      <c r="AC42">
         <v>2.66</v>
       </c>
-      <c r="AD41">
+      <c r="AD42">
         <v>1.37</v>
       </c>
-      <c r="AE41">
+      <c r="AE42">
         <v>1.1</v>
       </c>
-      <c r="AF41">
+      <c r="AF42">
         <v>1.6</v>
       </c>
-      <c r="AG41">
+      <c r="AG42">
         <v>2.1</v>
       </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ41">
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ42">
         <v>1.15</v>
       </c>
-      <c r="AK41">
+      <c r="AK42">
         <v>1.9</v>
       </c>
-      <c r="AL41">
-        <v>0</v>
-      </c>
-      <c r="AM41">
-        <v>-1</v>
-      </c>
-      <c r="AN41">
-        <v>-1</v>
-      </c>
-      <c r="AO41">
-        <v>-1</v>
-      </c>
-      <c r="AP41">
-        <v>-1</v>
-      </c>
-      <c r="AQ41">
-        <v>0</v>
-      </c>
-      <c r="AR41">
-        <v>0</v>
-      </c>
-      <c r="AS41">
-        <v>0</v>
-      </c>
-      <c r="AT41">
-        <v>0</v>
-      </c>
-      <c r="AU41" t="inlineStr">
+      <c r="AL42">
+        <v>0</v>
+      </c>
+      <c r="AM42">
+        <v>-1</v>
+      </c>
+      <c r="AN42">
+        <v>-1</v>
+      </c>
+      <c r="AO42">
+        <v>-1</v>
+      </c>
+      <c r="AP42">
+        <v>-1</v>
+      </c>
+      <c r="AQ42">
+        <v>0</v>
+      </c>
+      <c r="AR42">
+        <v>0</v>
+      </c>
+      <c r="AS42">
+        <v>0</v>
+      </c>
+      <c r="AT42">
+        <v>0</v>
+      </c>
+      <c r="AU42" t="inlineStr">
         <is>
           <t>2026-08-17 21:30:00</t>
         </is>

--- a/jogos_2026-08-17.xlsx
+++ b/jogos_2026-08-17.xlsx
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="O8">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="P8">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="Q8">
         <v>3.64</v>
@@ -1628,7 +1628,7 @@
         <v>2.3</v>
       </c>
       <c r="S8">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T8">
         <v>3.14</v>
@@ -1942,22 +1942,22 @@
         <v>1.52</v>
       </c>
       <c r="O10">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P10">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="Q10">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="R10">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="S10">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T10">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U10">
         <v>3.16</v>
@@ -1972,22 +1972,22 @@
         <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Z10">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="AA10">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AB10">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AC10">
-        <v>4.09</v>
+        <v>4.13</v>
       </c>
       <c r="AD10">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE10">
         <v>1.03</v>
@@ -2012,7 +2012,7 @@
         <v>1.2</v>
       </c>
       <c r="AK10">
-        <v>2.03</v>
+        <v>2.21</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,80 +4221,80 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.75</v>
+        <v>2.65</v>
       </c>
       <c r="O24">
+        <v>3.65</v>
+      </c>
+      <c r="P24">
+        <v>2.2</v>
+      </c>
+      <c r="Q24">
+        <v>3.22</v>
+      </c>
+      <c r="R24">
+        <v>2.36</v>
+      </c>
+      <c r="S24">
+        <v>1.22</v>
+      </c>
+      <c r="T24">
         <v>3.9</v>
       </c>
-      <c r="P24">
-        <v>3.18</v>
-      </c>
-      <c r="Q24">
-        <v>2.13</v>
-      </c>
-      <c r="R24">
-        <v>2.75</v>
-      </c>
-      <c r="S24">
+      <c r="U24">
+        <v>2.14</v>
+      </c>
+      <c r="V24">
+        <v>1.64</v>
+      </c>
+      <c r="W24">
         <v>1.13</v>
       </c>
-      <c r="T24">
-        <v>5.2</v>
-      </c>
-      <c r="U24">
-        <v>1.82</v>
-      </c>
-      <c r="V24">
-        <v>1.85</v>
-      </c>
-      <c r="W24">
+      <c r="X24">
+        <v>1.02</v>
+      </c>
+      <c r="Y24">
+        <v>1.13</v>
+      </c>
+      <c r="Z24">
+        <v>5.45</v>
+      </c>
+      <c r="AA24">
+        <v>1.44</v>
+      </c>
+      <c r="AB24">
+        <v>2.52</v>
+      </c>
+      <c r="AC24">
+        <v>2.14</v>
+      </c>
+      <c r="AD24">
+        <v>1.63</v>
+      </c>
+      <c r="AE24">
+        <v>1.28</v>
+      </c>
+      <c r="AF24">
+        <v>1.39</v>
+      </c>
+      <c r="AG24">
+        <v>2.65</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24">
         <v>1.25</v>
       </c>
-      <c r="X24">
-        <v>1.01</v>
-      </c>
-      <c r="Y24">
-        <v>1.03</v>
-      </c>
-      <c r="Z24">
-        <v>6.4</v>
-      </c>
-      <c r="AA24">
-        <v>1.3</v>
-      </c>
-      <c r="AB24">
-        <v>3.3</v>
-      </c>
-      <c r="AC24">
-        <v>1.78</v>
-      </c>
-      <c r="AD24">
-        <v>1.95</v>
-      </c>
-      <c r="AE24">
-        <v>1.38</v>
-      </c>
-      <c r="AF24">
-        <v>1.31</v>
-      </c>
-      <c r="AG24">
-        <v>3.08</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ24">
-        <v>1.17</v>
-      </c>
       <c r="AK24">
-        <v>2.02</v>
+        <v>1.4</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.65</v>
+        <v>1.75</v>
       </c>
       <c r="O25">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="P25">
-        <v>2.2</v>
+        <v>3.18</v>
       </c>
       <c r="Q25">
-        <v>3.22</v>
+        <v>2.13</v>
       </c>
       <c r="R25">
-        <v>2.36</v>
+        <v>2.75</v>
       </c>
       <c r="S25">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="T25">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="U25">
-        <v>2.14</v>
+        <v>1.82</v>
       </c>
       <c r="V25">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="W25">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="X25">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="Z25">
-        <v>5.45</v>
+        <v>6.4</v>
       </c>
       <c r="AA25">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AB25">
-        <v>2.52</v>
+        <v>3.3</v>
       </c>
       <c r="AC25">
-        <v>2.14</v>
+        <v>1.78</v>
       </c>
       <c r="AD25">
-        <v>1.63</v>
+        <v>1.95</v>
       </c>
       <c r="AE25">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AF25">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="AG25">
-        <v>2.65</v>
+        <v>3.08</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK25">
-        <v>1.4</v>
+        <v>2.02</v>
       </c>
       <c r="AL25">
         <v>0</v>

--- a/jogos_2026-08-17.xlsx
+++ b/jogos_2026-08-17.xlsx
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O4">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="P4">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="Q4">
         <v>5.1</v>
@@ -976,43 +976,43 @@
         <v>2.35</v>
       </c>
       <c r="S4">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="T4">
-        <v>2.96</v>
+        <v>3.5</v>
       </c>
       <c r="U4">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="V4">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="W4">
         <v>1.1</v>
       </c>
       <c r="X4">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y4">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z4">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AA4">
         <v>1.62</v>
       </c>
       <c r="AB4">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="AC4">
         <v>2.6</v>
       </c>
       <c r="AD4">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AE4">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF4">
         <v>1.67</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AK4">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="O8">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P8">
         <v>1.95</v>
@@ -1640,37 +1640,37 @@
         <v>1.5</v>
       </c>
       <c r="W8">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X8">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
         <v>1.2</v>
       </c>
       <c r="Z8">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="AA8">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB8">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AC8">
         <v>2.7</v>
       </c>
       <c r="AD8">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE8">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF8">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG8">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2265,19 +2265,19 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="O12">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="P12">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="Q12">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="R12">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="S12">
         <v>1.3</v>
@@ -2295,31 +2295,31 @@
         <v>1.11</v>
       </c>
       <c r="X12">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
         <v>1.22</v>
       </c>
       <c r="Z12">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AA12">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="AB12">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="AC12">
         <v>2.75</v>
       </c>
       <c r="AD12">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AE12">
         <v>1.1</v>
       </c>
       <c r="AF12">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AG12">
         <v>2</v>
@@ -2431,16 +2431,16 @@
         <v>2.15</v>
       </c>
       <c r="O13">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="P13">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="Q13">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="R13">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="S13">
         <v>1.42</v>
@@ -2452,13 +2452,13 @@
         <v>3</v>
       </c>
       <c r="V13">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W13">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X13">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y13">
         <v>1.28</v>
@@ -2467,13 +2467,13 @@
         <v>3.08</v>
       </c>
       <c r="AA13">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="AB13">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AC13">
-        <v>3.59</v>
+        <v>3.42</v>
       </c>
       <c r="AD13">
         <v>1.25</v>
@@ -2482,7 +2482,7 @@
         <v>1.08</v>
       </c>
       <c r="AF13">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AG13">
         <v>1.94</v>
@@ -2501,7 +2501,7 @@
         <v>1.33</v>
       </c>
       <c r="AK13">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2754,19 +2754,19 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="O15">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="P15">
-        <v>7.75</v>
+        <v>7.33</v>
       </c>
       <c r="Q15">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="R15">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="S15">
         <v>1.19</v>
@@ -2775,10 +2775,10 @@
         <v>3.94</v>
       </c>
       <c r="U15">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="V15">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W15">
         <v>1.16</v>
@@ -2799,10 +2799,10 @@
         <v>2.8</v>
       </c>
       <c r="AC15">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AD15">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AE15">
         <v>1.3</v>
@@ -2917,40 +2917,40 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="O16">
-        <v>4.35</v>
+        <v>4.65</v>
       </c>
       <c r="P16">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="Q16">
         <v>1.93</v>
       </c>
       <c r="R16">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="S16">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T16">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="U16">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="V16">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="W16">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X16">
         <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z16">
         <v>4.6</v>
@@ -2959,22 +2959,22 @@
         <v>1.57</v>
       </c>
       <c r="AB16">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="AC16">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AD16">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AE16">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AF16">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG16">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>1.17</v>
       </c>
       <c r="AK16">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3735,7 +3735,7 @@
         <v>1.95</v>
       </c>
       <c r="O21">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P21">
         <v>3.2</v>
@@ -3753,10 +3753,10 @@
         <v>3</v>
       </c>
       <c r="U21">
-        <v>2.44</v>
+        <v>2.58</v>
       </c>
       <c r="V21">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="W21">
         <v>1.08</v>
@@ -3765,31 +3765,31 @@
         <v>1.04</v>
       </c>
       <c r="Y21">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z21">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AA21">
         <v>1.7</v>
       </c>
       <c r="AB21">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AC21">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AD21">
         <v>1.38</v>
       </c>
       <c r="AE21">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF21">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG21">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK21">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4058,31 +4058,31 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="O23">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P23">
         <v>1.97</v>
       </c>
       <c r="Q23">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="R23">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S23">
         <v>1.24</v>
       </c>
       <c r="T23">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="U23">
         <v>2.2</v>
       </c>
       <c r="V23">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="W23">
         <v>1.17</v>
@@ -4091,10 +4091,10 @@
         <v>1.03</v>
       </c>
       <c r="Y23">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z23">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="AA23">
         <v>1.47</v>
@@ -4112,7 +4112,7 @@
         <v>1.18</v>
       </c>
       <c r="AF23">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AG23">
         <v>2.5</v>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AK23">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.65</v>
+        <v>1.77</v>
       </c>
       <c r="O24">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="P24">
-        <v>2.2</v>
+        <v>3.18</v>
       </c>
       <c r="Q24">
-        <v>3.22</v>
+        <v>2.11</v>
       </c>
       <c r="R24">
-        <v>2.36</v>
+        <v>2.7</v>
       </c>
       <c r="S24">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="T24">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="U24">
-        <v>2.14</v>
+        <v>1.82</v>
       </c>
       <c r="V24">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="W24">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="X24">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Z24">
-        <v>5.45</v>
+        <v>6.4</v>
       </c>
       <c r="AA24">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AB24">
-        <v>2.52</v>
+        <v>3.4</v>
       </c>
       <c r="AC24">
-        <v>2.14</v>
+        <v>1.77</v>
       </c>
       <c r="AD24">
-        <v>1.63</v>
+        <v>2</v>
       </c>
       <c r="AE24">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="AF24">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AG24">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AK24">
-        <v>1.4</v>
+        <v>2.04</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.75</v>
+        <v>2.89</v>
       </c>
       <c r="O25">
+        <v>3.55</v>
+      </c>
+      <c r="P25">
+        <v>2.2</v>
+      </c>
+      <c r="Q25">
+        <v>3.1</v>
+      </c>
+      <c r="R25">
+        <v>2.29</v>
+      </c>
+      <c r="S25">
+        <v>1.22</v>
+      </c>
+      <c r="T25">
         <v>3.9</v>
       </c>
-      <c r="P25">
-        <v>3.18</v>
-      </c>
-      <c r="Q25">
-        <v>2.13</v>
-      </c>
-      <c r="R25">
-        <v>2.75</v>
-      </c>
-      <c r="S25">
+      <c r="U25">
+        <v>2.15</v>
+      </c>
+      <c r="V25">
+        <v>1.67</v>
+      </c>
+      <c r="W25">
         <v>1.13</v>
       </c>
-      <c r="T25">
-        <v>5.2</v>
-      </c>
-      <c r="U25">
-        <v>1.82</v>
-      </c>
-      <c r="V25">
-        <v>1.85</v>
-      </c>
-      <c r="W25">
+      <c r="X25">
+        <v>1.02</v>
+      </c>
+      <c r="Y25">
+        <v>1.08</v>
+      </c>
+      <c r="Z25">
+        <v>5.5</v>
+      </c>
+      <c r="AA25">
+        <v>1.44</v>
+      </c>
+      <c r="AB25">
+        <v>2.55</v>
+      </c>
+      <c r="AC25">
+        <v>2.2</v>
+      </c>
+      <c r="AD25">
+        <v>1.65</v>
+      </c>
+      <c r="AE25">
         <v>1.25</v>
       </c>
-      <c r="X25">
-        <v>1.01</v>
-      </c>
-      <c r="Y25">
-        <v>1.03</v>
-      </c>
-      <c r="Z25">
-        <v>6.4</v>
-      </c>
-      <c r="AA25">
-        <v>1.3</v>
-      </c>
-      <c r="AB25">
-        <v>3.3</v>
-      </c>
-      <c r="AC25">
-        <v>1.78</v>
-      </c>
-      <c r="AD25">
-        <v>1.95</v>
-      </c>
-      <c r="AE25">
-        <v>1.38</v>
-      </c>
       <c r="AF25">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="AG25">
-        <v>3.08</v>
+        <v>2.65</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AK25">
-        <v>2.02</v>
+        <v>1.4</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -5362,37 +5362,37 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="O31">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="P31">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="Q31">
-        <v>2.74</v>
+        <v>3.05</v>
       </c>
       <c r="R31">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="S31">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T31">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="U31">
-        <v>2.58</v>
+        <v>2.69</v>
       </c>
       <c r="V31">
         <v>1.46</v>
       </c>
       <c r="W31">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X31">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y31">
         <v>1.2</v>
@@ -5401,25 +5401,25 @@
         <v>4.1</v>
       </c>
       <c r="AA31">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AB31">
-        <v>2.09</v>
+        <v>2.01</v>
       </c>
       <c r="AC31">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="AD31">
         <v>1.4</v>
       </c>
       <c r="AE31">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF31">
         <v>1.62</v>
       </c>
       <c r="AG31">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>1.4</v>
       </c>
       <c r="AK31">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5691,10 +5691,10 @@
         <v>9.4</v>
       </c>
       <c r="O33">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="P33">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Q33">
         <v>11</v>
@@ -5706,13 +5706,13 @@
         <v>1.28</v>
       </c>
       <c r="T33">
-        <v>3.45</v>
+        <v>3.34</v>
       </c>
       <c r="U33">
         <v>2.25</v>
       </c>
       <c r="V33">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W33">
         <v>1.1</v>
@@ -5724,13 +5724,13 @@
         <v>1.18</v>
       </c>
       <c r="Z33">
-        <v>4.42</v>
+        <v>4.6</v>
       </c>
       <c r="AA33">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AB33">
-        <v>2.12</v>
+        <v>2.35</v>
       </c>
       <c r="AC33">
         <v>2.38</v>
@@ -5742,7 +5742,7 @@
         <v>1.16</v>
       </c>
       <c r="AF33">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AG33">
         <v>1.6</v>
@@ -5761,7 +5761,7 @@
         <v>4.46</v>
       </c>
       <c r="AK33">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AL33">
         <v>0</v>

--- a/jogos_2026-08-17.xlsx
+++ b/jogos_2026-08-17.xlsx
@@ -638,10 +638,10 @@
         <v>2.75</v>
       </c>
       <c r="O2">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P2">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
+        <v>1.48</v>
+      </c>
+      <c r="O3">
+        <v>3.75</v>
+      </c>
+      <c r="P3">
+        <v>4.85</v>
+      </c>
+      <c r="Q3">
+        <v>1.91</v>
+      </c>
+      <c r="R3">
+        <v>2.5</v>
+      </c>
+      <c r="S3">
+        <v>1.22</v>
+      </c>
+      <c r="T3">
+        <v>3.2</v>
+      </c>
+      <c r="U3">
+        <v>2.22</v>
+      </c>
+      <c r="V3">
+        <v>1.57</v>
+      </c>
+      <c r="W3">
+        <v>1.14</v>
+      </c>
+      <c r="X3">
+        <v>1.03</v>
+      </c>
+      <c r="Y3">
+        <v>1.13</v>
+      </c>
+      <c r="Z3">
+        <v>4.6</v>
+      </c>
+      <c r="AA3">
+        <v>1.52</v>
+      </c>
+      <c r="AB3">
+        <v>2.23</v>
+      </c>
+      <c r="AC3">
+        <v>2.3</v>
+      </c>
+      <c r="AD3">
         <v>1.5</v>
       </c>
-      <c r="O3">
-        <v>4.2</v>
-      </c>
-      <c r="P3">
-        <v>4.8</v>
-      </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
-      <c r="V3">
-        <v>0</v>
-      </c>
-      <c r="W3">
-        <v>0</v>
-      </c>
-      <c r="X3">
-        <v>0</v>
-      </c>
-      <c r="Y3">
-        <v>0</v>
-      </c>
-      <c r="Z3">
-        <v>0</v>
-      </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <v>0</v>
-      </c>
-      <c r="AC3">
-        <v>0</v>
-      </c>
-      <c r="AD3">
-        <v>0</v>
-      </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,28 +961,28 @@
         </is>
       </c>
       <c r="N4">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="O4">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="P4">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Q4">
         <v>5.1</v>
       </c>
       <c r="R4">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="S4">
         <v>1.25</v>
       </c>
       <c r="T4">
-        <v>3.5</v>
+        <v>2.96</v>
       </c>
       <c r="U4">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="V4">
         <v>1.57</v>
@@ -991,16 +991,16 @@
         <v>1.1</v>
       </c>
       <c r="X4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z4">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="AA4">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AB4">
         <v>2.25</v>
@@ -1009,13 +1009,13 @@
         <v>2.6</v>
       </c>
       <c r="AD4">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AE4">
         <v>1.2</v>
       </c>
       <c r="AF4">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AG4">
         <v>2.1</v>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AK4">
         <v>1.08</v>
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O6">
         <v>3.2</v>
@@ -1305,16 +1305,16 @@
         <v>1.42</v>
       </c>
       <c r="T6">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="U6">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="V6">
         <v>1.3</v>
       </c>
       <c r="W6">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X6">
         <v>1.03</v>
@@ -1329,10 +1329,10 @@
         <v>2.15</v>
       </c>
       <c r="AB6">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AC6">
-        <v>3.25</v>
+        <v>3.82</v>
       </c>
       <c r="AD6">
         <v>1.26</v>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK6">
         <v>1.25</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="O7">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="P7">
-        <v>2.47</v>
+        <v>2.37</v>
       </c>
       <c r="Q7">
         <v>3.18</v>
@@ -1471,7 +1471,7 @@
         <v>2.75</v>
       </c>
       <c r="U7">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="V7">
         <v>1.34</v>
@@ -1492,7 +1492,7 @@
         <v>1.93</v>
       </c>
       <c r="AB7">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AC7">
         <v>3.34</v>
@@ -1788,49 +1788,49 @@
         <v>2.5</v>
       </c>
       <c r="R9">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="S9">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T9">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="U9">
         <v>2.75</v>
       </c>
       <c r="V9">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="W9">
         <v>1.03</v>
       </c>
       <c r="X9">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y9">
         <v>1.32</v>
       </c>
       <c r="Z9">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AA9">
-        <v>2.11</v>
+        <v>1.94</v>
       </c>
       <c r="AB9">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AC9">
-        <v>3.79</v>
+        <v>3.7</v>
       </c>
       <c r="AD9">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE9">
         <v>1.1</v>
       </c>
       <c r="AF9">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AG9">
         <v>1.85</v>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AK9">
         <v>1.83</v>
@@ -1945,7 +1945,7 @@
         <v>3.55</v>
       </c>
       <c r="P10">
-        <v>4.5</v>
+        <v>5.35</v>
       </c>
       <c r="Q10">
         <v>2.2</v>
@@ -1960,7 +1960,7 @@
         <v>2.5</v>
       </c>
       <c r="U10">
-        <v>3.16</v>
+        <v>3.35</v>
       </c>
       <c r="V10">
         <v>1.3</v>
@@ -1987,7 +1987,7 @@
         <v>4.13</v>
       </c>
       <c r="AD10">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE10">
         <v>1.03</v>
@@ -1996,7 +1996,7 @@
         <v>2.14</v>
       </c>
       <c r="AG10">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK10">
         <v>2.21</v>
@@ -2268,16 +2268,16 @@
         <v>1.72</v>
       </c>
       <c r="O12">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P12">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="Q12">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="R12">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="S12">
         <v>1.3</v>
@@ -2295,25 +2295,25 @@
         <v>1.11</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y12">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z12">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AA12">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AB12">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AC12">
-        <v>2.75</v>
+        <v>3.11</v>
       </c>
       <c r="AD12">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AE12">
         <v>1.1</v>
@@ -2434,16 +2434,16 @@
         <v>3.05</v>
       </c>
       <c r="P13">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="Q13">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="R13">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S13">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="T13">
         <v>2.59</v>
@@ -2452,40 +2452,40 @@
         <v>3</v>
       </c>
       <c r="V13">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W13">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X13">
         <v>1.06</v>
       </c>
       <c r="Y13">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="Z13">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AA13">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AB13">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AC13">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="AD13">
         <v>1.25</v>
       </c>
       <c r="AE13">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF13">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AG13">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>1.33</v>
       </c>
       <c r="AK13">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="O14">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P14">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="Q14">
         <v>2.38</v>
@@ -2609,13 +2609,13 @@
         <v>1.42</v>
       </c>
       <c r="T14">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="U14">
         <v>2.91</v>
       </c>
       <c r="V14">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W14">
         <v>1.05</v>
@@ -2642,7 +2642,7 @@
         <v>1.2</v>
       </c>
       <c r="AE14">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF14">
         <v>1.95</v>
@@ -2664,7 +2664,7 @@
         <v>1.2</v>
       </c>
       <c r="AK14">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,19 +2754,19 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="O15">
         <v>5.8</v>
       </c>
       <c r="P15">
-        <v>7.33</v>
+        <v>7.4</v>
       </c>
       <c r="Q15">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="R15">
-        <v>2.73</v>
+        <v>2.96</v>
       </c>
       <c r="S15">
         <v>1.19</v>
@@ -2775,10 +2775,10 @@
         <v>3.94</v>
       </c>
       <c r="U15">
-        <v>2.07</v>
+        <v>1.91</v>
       </c>
       <c r="V15">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="W15">
         <v>1.16</v>
@@ -2790,10 +2790,10 @@
         <v>1.14</v>
       </c>
       <c r="Z15">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AA15">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB15">
         <v>2.8</v>
@@ -2808,10 +2808,10 @@
         <v>1.3</v>
       </c>
       <c r="AF15">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG15">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>1.15</v>
       </c>
       <c r="AK15">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3089,10 +3089,10 @@
         <v>1.21</v>
       </c>
       <c r="Q17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R17">
-        <v>2.61</v>
+        <v>2.8</v>
       </c>
       <c r="S17">
         <v>1.24</v>
@@ -3104,7 +3104,7 @@
         <v>2.2</v>
       </c>
       <c r="V17">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="W17">
         <v>1.12</v>
@@ -3113,31 +3113,31 @@
         <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z17">
         <v>4.7</v>
       </c>
       <c r="AA17">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="AB17">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="AC17">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="AD17">
         <v>1.64</v>
       </c>
       <c r="AE17">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AF17">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AG17">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>3.45</v>
       </c>
       <c r="AK17">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,19 +3243,19 @@
         </is>
       </c>
       <c r="N18">
-        <v>3.32</v>
+        <v>3.5</v>
       </c>
       <c r="O18">
         <v>3.45</v>
       </c>
       <c r="P18">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="Q18">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="R18">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S18">
         <v>1.3</v>
@@ -3264,10 +3264,10 @@
         <v>3</v>
       </c>
       <c r="U18">
-        <v>2.38</v>
+        <v>2.07</v>
       </c>
       <c r="V18">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W18">
         <v>1.08</v>
@@ -3276,16 +3276,16 @@
         <v>1</v>
       </c>
       <c r="Y18">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z18">
         <v>3.9</v>
       </c>
       <c r="AA18">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AB18">
-        <v>1.8</v>
+        <v>2.11</v>
       </c>
       <c r="AC18">
         <v>2.52</v>
@@ -3316,7 +3316,7 @@
         <v>1.3</v>
       </c>
       <c r="AK18">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3569,16 +3569,16 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.94</v>
+        <v>2.07</v>
       </c>
       <c r="O20">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="P20">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="Q20">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R20">
         <v>2.49</v>
@@ -3587,16 +3587,16 @@
         <v>1.17</v>
       </c>
       <c r="T20">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="U20">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="V20">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="W20">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="X20">
         <v>1.01</v>
@@ -3608,25 +3608,25 @@
         <v>6.24</v>
       </c>
       <c r="AA20">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AB20">
-        <v>3.16</v>
+        <v>3.4</v>
       </c>
       <c r="AC20">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AD20">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="AE20">
         <v>1.36</v>
       </c>
       <c r="AF20">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AG20">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK20">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,7 +3732,7 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O21">
         <v>3.5</v>
@@ -3747,25 +3747,25 @@
         <v>2.32</v>
       </c>
       <c r="S21">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T21">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U21">
-        <v>2.58</v>
+        <v>2.44</v>
       </c>
       <c r="V21">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="W21">
         <v>1.08</v>
       </c>
       <c r="X21">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z21">
         <v>3.8</v>
@@ -3774,19 +3774,19 @@
         <v>1.7</v>
       </c>
       <c r="AB21">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC21">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AD21">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE21">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF21">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG21">
         <v>2.15</v>
@@ -3895,10 +3895,10 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="O22">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P22">
         <v>6</v>
@@ -3910,37 +3910,37 @@
         <v>1.95</v>
       </c>
       <c r="S22">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="T22">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="U22">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="V22">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="W22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X22">
         <v>1.07</v>
       </c>
       <c r="Y22">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="Z22">
         <v>2.33</v>
       </c>
       <c r="AA22">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="AB22">
         <v>1.44</v>
       </c>
       <c r="AC22">
-        <v>4.8</v>
+        <v>4.85</v>
       </c>
       <c r="AD22">
         <v>1.11</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.23</v>
+        <v>1.06</v>
       </c>
       <c r="AK22">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4547,31 +4547,31 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="O26">
-        <v>3.4</v>
+        <v>3.72</v>
       </c>
       <c r="P26">
-        <v>4.96</v>
+        <v>4</v>
       </c>
       <c r="Q26">
-        <v>2.38</v>
+        <v>2.21</v>
       </c>
       <c r="R26">
         <v>2.2</v>
       </c>
       <c r="S26">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T26">
-        <v>2.89</v>
+        <v>2.93</v>
       </c>
       <c r="U26">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="V26">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W26">
         <v>1.05</v>
@@ -4580,22 +4580,22 @@
         <v>1.06</v>
       </c>
       <c r="Y26">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z26">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="AA26">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB26">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AC26">
         <v>3.4</v>
       </c>
       <c r="AD26">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE26">
         <v>1.1</v>
@@ -4604,7 +4604,7 @@
         <v>1.72</v>
       </c>
       <c r="AG26">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AK26">
         <v>1.91</v>
@@ -4710,37 +4710,37 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="O27">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P27">
         <v>3.2</v>
       </c>
       <c r="Q27">
-        <v>2.82</v>
+        <v>2.77</v>
       </c>
       <c r="R27">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="S27">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T27">
-        <v>2.59</v>
+        <v>2.73</v>
       </c>
       <c r="U27">
-        <v>2.94</v>
+        <v>2.7</v>
       </c>
       <c r="V27">
         <v>1.4</v>
       </c>
       <c r="W27">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X27">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
         <v>1.3</v>
@@ -4749,25 +4749,25 @@
         <v>3.15</v>
       </c>
       <c r="AA27">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AB27">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AC27">
-        <v>3.59</v>
+        <v>3.37</v>
       </c>
       <c r="AD27">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AE27">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF27">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AG27">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="O28">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="P28">
-        <v>6.83</v>
+        <v>5.95</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="O29">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="P29">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="Q29">
         <v>2</v>
@@ -5051,16 +5051,16 @@
         <v>2.4</v>
       </c>
       <c r="S29">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T29">
         <v>3.25</v>
       </c>
       <c r="U29">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="V29">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W29">
         <v>1.11</v>
@@ -5072,7 +5072,7 @@
         <v>1.2</v>
       </c>
       <c r="Z29">
-        <v>4.37</v>
+        <v>4.4</v>
       </c>
       <c r="AA29">
         <v>1.65</v>
@@ -5081,7 +5081,7 @@
         <v>2.17</v>
       </c>
       <c r="AC29">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AD29">
         <v>1.42</v>
@@ -5090,10 +5090,10 @@
         <v>1.14</v>
       </c>
       <c r="AF29">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG29">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AK29">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,16 +5199,16 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.35</v>
+        <v>2.22</v>
       </c>
       <c r="O30">
-        <v>3.15</v>
+        <v>2.95</v>
       </c>
       <c r="P30">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="Q30">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="R30">
         <v>1.95</v>
@@ -5217,46 +5217,46 @@
         <v>1.55</v>
       </c>
       <c r="T30">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="U30">
         <v>3.3</v>
       </c>
       <c r="V30">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W30">
         <v>1.03</v>
       </c>
       <c r="X30">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y30">
         <v>1.42</v>
       </c>
       <c r="Z30">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AA30">
         <v>2.38</v>
       </c>
       <c r="AB30">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="AC30">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="AD30">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE30">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF30">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AG30">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5365,13 +5365,13 @@
         <v>2.4</v>
       </c>
       <c r="O31">
-        <v>3.5</v>
+        <v>3.41</v>
       </c>
       <c r="P31">
         <v>2.8</v>
       </c>
       <c r="Q31">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="R31">
         <v>2.23</v>
@@ -5383,10 +5383,10 @@
         <v>2.82</v>
       </c>
       <c r="U31">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="V31">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W31">
         <v>1.07</v>
@@ -5401,25 +5401,25 @@
         <v>4.1</v>
       </c>
       <c r="AA31">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AB31">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="AC31">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AD31">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE31">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF31">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AG31">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5525,40 +5525,40 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="O32">
         <v>4.2</v>
       </c>
       <c r="P32">
-        <v>2.93</v>
+        <v>3.02</v>
       </c>
       <c r="Q32">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R32">
         <v>2.88</v>
       </c>
       <c r="S32">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="T32">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="U32">
         <v>1.73</v>
       </c>
       <c r="V32">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="W32">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X32">
         <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Z32">
         <v>7.8</v>
@@ -5567,22 +5567,22 @@
         <v>1.24</v>
       </c>
       <c r="AB32">
-        <v>3.82</v>
+        <v>3.86</v>
       </c>
       <c r="AC32">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AD32">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="AE32">
         <v>1.51</v>
       </c>
       <c r="AF32">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AG32">
-        <v>3.4</v>
+        <v>3.56</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AK32">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5691,10 +5691,10 @@
         <v>9.4</v>
       </c>
       <c r="O33">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="P33">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Q33">
         <v>11</v>
@@ -5706,31 +5706,31 @@
         <v>1.28</v>
       </c>
       <c r="T33">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="U33">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="V33">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W33">
         <v>1.1</v>
       </c>
       <c r="X33">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z33">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AA33">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB33">
-        <v>2.35</v>
+        <v>2.12</v>
       </c>
       <c r="AC33">
         <v>2.38</v>
@@ -5742,10 +5742,10 @@
         <v>1.16</v>
       </c>
       <c r="AF33">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AG33">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>4.46</v>
+        <v>4.6</v>
       </c>
       <c r="AK33">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="O34">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="P34">
-        <v>9.300000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="Q34">
         <v>1.73</v>
@@ -5866,49 +5866,49 @@
         <v>2.55</v>
       </c>
       <c r="S34">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T34">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="U34">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="V34">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W34">
         <v>1.12</v>
       </c>
       <c r="X34">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y34">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z34">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="AA34">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AB34">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="AC34">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="AD34">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AE34">
         <v>1.16</v>
       </c>
       <c r="AF34">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG34">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AK34">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6017,28 +6017,28 @@
         <v>1.91</v>
       </c>
       <c r="O35">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P35">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="Q35">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="R35">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="S35">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="T35">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="U35">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="V35">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W35">
         <v>1.05</v>
@@ -6047,16 +6047,16 @@
         <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z35">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AA35">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="AB35">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AC35">
         <v>3.1</v>
@@ -6068,7 +6068,7 @@
         <v>1.08</v>
       </c>
       <c r="AF35">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG35">
         <v>1.91</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AK35">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,31 +6177,31 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="O36">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P36">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="Q36">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="R36">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S36">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="T36">
-        <v>2.66</v>
+        <v>2.85</v>
       </c>
       <c r="U36">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="V36">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W36">
         <v>1.07</v>
@@ -6210,47 +6210,47 @@
         <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z36">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="AA36">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB36">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC36">
-        <v>3.14</v>
+        <v>3.34</v>
       </c>
       <c r="AD36">
+        <v>1.24</v>
+      </c>
+      <c r="AE36">
+        <v>1.08</v>
+      </c>
+      <c r="AF36">
+        <v>1.75</v>
+      </c>
+      <c r="AG36">
+        <v>1.95</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ36">
         <v>1.27</v>
       </c>
-      <c r="AE36">
-        <v>1.06</v>
-      </c>
-      <c r="AF36">
-        <v>1.71</v>
-      </c>
-      <c r="AG36">
-        <v>2</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ36">
-        <v>1.3</v>
-      </c>
       <c r="AK36">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6352,13 +6352,13 @@
         <v>2.09</v>
       </c>
       <c r="R37">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="S37">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T37">
-        <v>2.82</v>
+        <v>2.99</v>
       </c>
       <c r="U37">
         <v>2.6</v>
@@ -6370,13 +6370,13 @@
         <v>1.07</v>
       </c>
       <c r="X37">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y37">
         <v>1.22</v>
       </c>
       <c r="Z37">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AA37">
         <v>1.83</v>
@@ -6391,7 +6391,7 @@
         <v>1.33</v>
       </c>
       <c r="AE37">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF37">
         <v>1.85</v>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK37">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,31 +6503,31 @@
         </is>
       </c>
       <c r="N38">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O38">
         <v>3.2</v>
       </c>
       <c r="P38">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q38">
-        <v>2.81</v>
+        <v>2.95</v>
       </c>
       <c r="R38">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="S38">
         <v>1.42</v>
       </c>
       <c r="T38">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="U38">
         <v>3</v>
       </c>
       <c r="V38">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W38">
         <v>1.04</v>
@@ -6536,31 +6536,31 @@
         <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="Z38">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="AA38">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AB38">
         <v>1.67</v>
       </c>
       <c r="AC38">
-        <v>3.72</v>
+        <v>3.5</v>
       </c>
       <c r="AD38">
         <v>1.22</v>
       </c>
       <c r="AE38">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF38">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AG38">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK38">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="O39">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="P39">
-        <v>4.15</v>
+        <v>3.9</v>
       </c>
       <c r="Q39">
         <v>2.3</v>
@@ -6681,13 +6681,13 @@
         <v>2.03</v>
       </c>
       <c r="S39">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T39">
-        <v>2.67</v>
+        <v>2.84</v>
       </c>
       <c r="U39">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="V39">
         <v>1.36</v>
@@ -6708,7 +6708,7 @@
         <v>1.95</v>
       </c>
       <c r="AB39">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AC39">
         <v>3.4</v>
@@ -6717,7 +6717,7 @@
         <v>1.29</v>
       </c>
       <c r="AE39">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF39">
         <v>1.79</v>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AK39">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,22 +6829,22 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="O40">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P40">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q40">
-        <v>3.86</v>
+        <v>3.6</v>
       </c>
       <c r="R40">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="S40">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T40">
         <v>2.75</v>
@@ -6853,7 +6853,7 @@
         <v>2.8</v>
       </c>
       <c r="V40">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="W40">
         <v>1.07</v>
@@ -6862,13 +6862,13 @@
         <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z40">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="AA40">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AB40">
         <v>1.7</v>
@@ -6880,13 +6880,13 @@
         <v>1.21</v>
       </c>
       <c r="AE40">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF40">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AG40">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>1.28</v>
       </c>
       <c r="AK40">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,25 +6992,25 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O41">
         <v>3.4</v>
       </c>
       <c r="P41">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q41">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="R41">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S41">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T41">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="U41">
         <v>2.63</v>
@@ -7022,28 +7022,28 @@
         <v>1.1</v>
       </c>
       <c r="X41">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z41">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="AA41">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AB41">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="AC41">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="AD41">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE41">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF41">
         <v>1.62</v>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK41">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AL41">
         <v>0</v>

--- a/jogos_2026-08-17.xlsx
+++ b/jogos_2026-08-17.xlsx
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="O5">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="P5">
-        <v>4.01</v>
+        <v>3.4</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC5">
         <v>0</v>
@@ -1788,7 +1788,7 @@
         <v>2.5</v>
       </c>
       <c r="R9">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="S9">
         <v>1.4</v>
@@ -2304,13 +2304,13 @@
         <v>3.8</v>
       </c>
       <c r="AA12">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AB12">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AC12">
-        <v>3.11</v>
+        <v>3.13</v>
       </c>
       <c r="AD12">
         <v>1.35</v>
@@ -2319,7 +2319,7 @@
         <v>1.1</v>
       </c>
       <c r="AF12">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG12">
         <v>2</v>
@@ -2428,16 +2428,16 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="O13">
         <v>3.05</v>
       </c>
       <c r="P13">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q13">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="R13">
         <v>2</v>
@@ -2446,7 +2446,7 @@
         <v>1.38</v>
       </c>
       <c r="T13">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="U13">
         <v>3</v>
@@ -2470,22 +2470,22 @@
         <v>2.1</v>
       </c>
       <c r="AB13">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AC13">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AD13">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE13">
         <v>1.07</v>
       </c>
       <c r="AF13">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG13">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2609,10 +2609,10 @@
         <v>1.42</v>
       </c>
       <c r="T14">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="U14">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="V14">
         <v>1.32</v>
@@ -2633,7 +2633,7 @@
         <v>2.2</v>
       </c>
       <c r="AB14">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC14">
         <v>4.1</v>
@@ -2766,7 +2766,7 @@
         <v>1.67</v>
       </c>
       <c r="R15">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="S15">
         <v>1.19</v>
@@ -2827,7 +2827,7 @@
         <v>1.15</v>
       </c>
       <c r="AK15">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3116,13 +3116,13 @@
         <v>1.12</v>
       </c>
       <c r="Z17">
-        <v>4.7</v>
+        <v>4.65</v>
       </c>
       <c r="AA17">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="AB17">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="AC17">
         <v>2.02</v>
@@ -3249,7 +3249,7 @@
         <v>3.45</v>
       </c>
       <c r="P18">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q18">
         <v>3.9</v>
@@ -3409,22 +3409,22 @@
         <v>2.2</v>
       </c>
       <c r="O19">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="P19">
+        <v>3.35</v>
+      </c>
+      <c r="Q19">
         <v>3.08</v>
-      </c>
-      <c r="Q19">
-        <v>3.1</v>
       </c>
       <c r="R19">
         <v>1.8</v>
       </c>
       <c r="S19">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="T19">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="U19">
         <v>4.45</v>
@@ -3436,19 +3436,19 @@
         <v>1.03</v>
       </c>
       <c r="X19">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="Y19">
         <v>1.55</v>
       </c>
       <c r="Z19">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AA19">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="AB19">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AC19">
         <v>7.1</v>
@@ -3457,13 +3457,13 @@
         <v>1.08</v>
       </c>
       <c r="AE19">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF19">
         <v>2.51</v>
       </c>
       <c r="AG19">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.44</v>
+        <v>1.2</v>
       </c>
       <c r="AK19">
         <v>1.55</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="O20">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P20">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
@@ -3593,7 +3593,7 @@
         <v>1.85</v>
       </c>
       <c r="V20">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="W20">
         <v>1.24</v>
@@ -3611,10 +3611,10 @@
         <v>1.27</v>
       </c>
       <c r="AB20">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="AC20">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AD20">
         <v>2.01</v>
@@ -3626,7 +3626,7 @@
         <v>1.2</v>
       </c>
       <c r="AG20">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>2</v>
       </c>
       <c r="O21">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P21">
         <v>3.2</v>
@@ -3895,43 +3895,43 @@
         </is>
       </c>
       <c r="N22">
+        <v>1.36</v>
+      </c>
+      <c r="O22">
+        <v>3.85</v>
+      </c>
+      <c r="P22">
+        <v>7.7</v>
+      </c>
+      <c r="Q22">
+        <v>2</v>
+      </c>
+      <c r="R22">
+        <v>2.05</v>
+      </c>
+      <c r="S22">
+        <v>1.44</v>
+      </c>
+      <c r="T22">
+        <v>2.36</v>
+      </c>
+      <c r="U22">
+        <v>3.2</v>
+      </c>
+      <c r="V22">
+        <v>1.29</v>
+      </c>
+      <c r="W22">
+        <v>1.05</v>
+      </c>
+      <c r="X22">
+        <v>1.05</v>
+      </c>
+      <c r="Y22">
         <v>1.46</v>
       </c>
-      <c r="O22">
-        <v>3.4</v>
-      </c>
-      <c r="P22">
-        <v>6</v>
-      </c>
-      <c r="Q22">
-        <v>2.15</v>
-      </c>
-      <c r="R22">
-        <v>1.95</v>
-      </c>
-      <c r="S22">
-        <v>1.5</v>
-      </c>
-      <c r="T22">
-        <v>2.31</v>
-      </c>
-      <c r="U22">
-        <v>3.3</v>
-      </c>
-      <c r="V22">
-        <v>1.25</v>
-      </c>
-      <c r="W22">
-        <v>1.04</v>
-      </c>
-      <c r="X22">
-        <v>1.07</v>
-      </c>
-      <c r="Y22">
-        <v>1.51</v>
-      </c>
       <c r="Z22">
-        <v>2.33</v>
+        <v>2.46</v>
       </c>
       <c r="AA22">
         <v>2.62</v>
@@ -3940,19 +3940,19 @@
         <v>1.44</v>
       </c>
       <c r="AC22">
-        <v>4.85</v>
+        <v>4.5</v>
       </c>
       <c r="AD22">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AE22">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF22">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="AG22">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AK22">
-        <v>2.21</v>
+        <v>2.59</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="O26">
         <v>3.72</v>
       </c>
       <c r="P26">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="Q26">
         <v>2.21</v>
@@ -4565,7 +4565,7 @@
         <v>1.36</v>
       </c>
       <c r="T26">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="U26">
         <v>2.77</v>
@@ -4586,7 +4586,7 @@
         <v>3.4</v>
       </c>
       <c r="AA26">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AB26">
         <v>1.84</v>
@@ -4604,7 +4604,7 @@
         <v>1.72</v>
       </c>
       <c r="AG26">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="O27">
         <v>3.3</v>
@@ -4719,7 +4719,7 @@
         <v>3.2</v>
       </c>
       <c r="Q27">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="R27">
         <v>2.17</v>
@@ -4755,7 +4755,7 @@
         <v>1.79</v>
       </c>
       <c r="AC27">
-        <v>3.37</v>
+        <v>3.4</v>
       </c>
       <c r="AD27">
         <v>1.3</v>
@@ -4873,31 +4873,31 @@
         </is>
       </c>
       <c r="N28">
+        <v>1.5</v>
+      </c>
+      <c r="O28">
+        <v>4.5</v>
+      </c>
+      <c r="P28">
+        <v>5</v>
+      </c>
+      <c r="Q28">
+        <v>2</v>
+      </c>
+      <c r="R28">
+        <v>2.38</v>
+      </c>
+      <c r="S28">
+        <v>1.28</v>
+      </c>
+      <c r="T28">
+        <v>3.18</v>
+      </c>
+      <c r="U28">
+        <v>2.5</v>
+      </c>
+      <c r="V28">
         <v>1.44</v>
-      </c>
-      <c r="O28">
-        <v>4.6</v>
-      </c>
-      <c r="P28">
-        <v>5.95</v>
-      </c>
-      <c r="Q28">
-        <v>1.85</v>
-      </c>
-      <c r="R28">
-        <v>2.4</v>
-      </c>
-      <c r="S28">
-        <v>1.31</v>
-      </c>
-      <c r="T28">
-        <v>3.02</v>
-      </c>
-      <c r="U28">
-        <v>2.3</v>
-      </c>
-      <c r="V28">
-        <v>1.5</v>
       </c>
       <c r="W28">
         <v>1.08</v>
@@ -4906,47 +4906,47 @@
         <v>1.04</v>
       </c>
       <c r="Y28">
+        <v>1.19</v>
+      </c>
+      <c r="Z28">
+        <v>3.75</v>
+      </c>
+      <c r="AA28">
+        <v>1.73</v>
+      </c>
+      <c r="AB28">
+        <v>1.99</v>
+      </c>
+      <c r="AC28">
+        <v>2.78</v>
+      </c>
+      <c r="AD28">
+        <v>1.34</v>
+      </c>
+      <c r="AE28">
+        <v>1.14</v>
+      </c>
+      <c r="AF28">
+        <v>1.8</v>
+      </c>
+      <c r="AG28">
+        <v>1.86</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28">
         <v>1.17</v>
       </c>
-      <c r="Z28">
-        <v>3.98</v>
-      </c>
-      <c r="AA28">
-        <v>1.66</v>
-      </c>
-      <c r="AB28">
-        <v>2.09</v>
-      </c>
-      <c r="AC28">
-        <v>2.56</v>
-      </c>
-      <c r="AD28">
-        <v>1.4</v>
-      </c>
-      <c r="AE28">
-        <v>1.15</v>
-      </c>
-      <c r="AF28">
-        <v>1.81</v>
-      </c>
-      <c r="AG28">
-        <v>1.85</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28">
-        <v>1.14</v>
-      </c>
       <c r="AK28">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5051,16 +5051,16 @@
         <v>2.4</v>
       </c>
       <c r="S29">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T29">
         <v>3.25</v>
       </c>
       <c r="U29">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="V29">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W29">
         <v>1.11</v>
@@ -5072,7 +5072,7 @@
         <v>1.2</v>
       </c>
       <c r="Z29">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="AA29">
         <v>1.65</v>
@@ -5531,7 +5531,7 @@
         <v>4.2</v>
       </c>
       <c r="P32">
-        <v>3.02</v>
+        <v>3.25</v>
       </c>
       <c r="Q32">
         <v>2.28</v>
@@ -5555,7 +5555,7 @@
         <v>1.3</v>
       </c>
       <c r="X32">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y32">
         <v>1.06</v>
@@ -5579,7 +5579,7 @@
         <v>1.51</v>
       </c>
       <c r="AF32">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AG32">
         <v>3.56</v>
@@ -5691,7 +5691,7 @@
         <v>9.4</v>
       </c>
       <c r="O33">
-        <v>6.3</v>
+        <v>6.25</v>
       </c>
       <c r="P33">
         <v>1.18</v>
@@ -5712,7 +5712,7 @@
         <v>2.34</v>
       </c>
       <c r="V33">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="W33">
         <v>1.1</v>
@@ -5730,13 +5730,13 @@
         <v>1.6</v>
       </c>
       <c r="AB33">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="AC33">
         <v>2.38</v>
       </c>
       <c r="AD33">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AE33">
         <v>1.16</v>
@@ -5878,7 +5878,7 @@
         <v>1.55</v>
       </c>
       <c r="W34">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X34">
         <v>1.04</v>
@@ -5887,10 +5887,10 @@
         <v>1.13</v>
       </c>
       <c r="Z34">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="AA34">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AB34">
         <v>2.2</v>
@@ -5905,7 +5905,7 @@
         <v>1.16</v>
       </c>
       <c r="AF34">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AG34">
         <v>1.75</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="O35">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P35">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="Q35">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="R35">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="S35">
+        <v>1.35</v>
+      </c>
+      <c r="T35">
+        <v>2.85</v>
+      </c>
+      <c r="U35">
+        <v>2.88</v>
+      </c>
+      <c r="V35">
         <v>1.34</v>
       </c>
-      <c r="T35">
-        <v>2.75</v>
-      </c>
-      <c r="U35">
-        <v>2.82</v>
-      </c>
-      <c r="V35">
-        <v>1.35</v>
-      </c>
       <c r="W35">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X35">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
         <v>1.3</v>
       </c>
       <c r="Z35">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="AA35">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AB35">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AC35">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="AD35">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AE35">
         <v>1.08</v>
       </c>
       <c r="AF35">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG35">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AK35">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="O36">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P36">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="Q36">
-        <v>2.63</v>
+        <v>2.53</v>
       </c>
       <c r="R36">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="S36">
+        <v>1.34</v>
+      </c>
+      <c r="T36">
+        <v>2.75</v>
+      </c>
+      <c r="U36">
+        <v>2.82</v>
+      </c>
+      <c r="V36">
         <v>1.35</v>
       </c>
-      <c r="T36">
-        <v>2.85</v>
-      </c>
-      <c r="U36">
-        <v>2.88</v>
-      </c>
-      <c r="V36">
-        <v>1.34</v>
-      </c>
       <c r="W36">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X36">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y36">
         <v>1.3</v>
       </c>
       <c r="Z36">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="AA36">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AB36">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AC36">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="AD36">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AE36">
         <v>1.08</v>
       </c>
       <c r="AF36">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG36">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AK36">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6373,7 +6373,7 @@
         <v>1.04</v>
       </c>
       <c r="Y37">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z37">
         <v>3.65</v>
@@ -6382,7 +6382,7 @@
         <v>1.83</v>
       </c>
       <c r="AB37">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AC37">
         <v>3</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="O42">
         <v>3.55</v>
       </c>
       <c r="P42">
-        <v>4.18</v>
+        <v>4.22</v>
       </c>
       <c r="Q42">
         <v>2.3</v>
@@ -7170,13 +7170,13 @@
         <v>2.3</v>
       </c>
       <c r="S42">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T42">
         <v>3.2</v>
       </c>
       <c r="U42">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="V42">
         <v>1.5</v>
@@ -7188,16 +7188,16 @@
         <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z42">
         <v>4</v>
       </c>
       <c r="AA42">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AB42">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AC42">
         <v>2.66</v>
@@ -7206,10 +7206,10 @@
         <v>1.37</v>
       </c>
       <c r="AE42">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF42">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AG42">
         <v>2.1</v>

--- a/jogos_2026-08-17.xlsx
+++ b/jogos_2026-08-17.xlsx
@@ -5208,7 +5208,7 @@
         <v>3.35</v>
       </c>
       <c r="Q30">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="R30">
         <v>1.95</v>
@@ -5244,7 +5244,7 @@
         <v>1.59</v>
       </c>
       <c r="AC30">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AD30">
         <v>1.21</v>
@@ -5253,10 +5253,10 @@
         <v>1.03</v>
       </c>
       <c r="AF30">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG30">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>1.25</v>
       </c>
       <c r="AK30">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -6186,7 +6186,7 @@
         <v>3.75</v>
       </c>
       <c r="Q36">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="R36">
         <v>2.04</v>
@@ -6216,10 +6216,10 @@
         <v>3.1</v>
       </c>
       <c r="AA36">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AB36">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AC36">
         <v>3.1</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK36">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6352,7 +6352,7 @@
         <v>2.09</v>
       </c>
       <c r="R37">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="S37">
         <v>1.34</v>
@@ -6361,10 +6361,10 @@
         <v>2.99</v>
       </c>
       <c r="U37">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="V37">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W37">
         <v>1.07</v>
@@ -6373,7 +6373,7 @@
         <v>1.04</v>
       </c>
       <c r="Y37">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z37">
         <v>3.65</v>
@@ -6391,7 +6391,7 @@
         <v>1.33</v>
       </c>
       <c r="AE37">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF37">
         <v>1.85</v>
@@ -6560,7 +6560,7 @@
         <v>1.78</v>
       </c>
       <c r="AG38">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6669,16 +6669,16 @@
         <v>1.73</v>
       </c>
       <c r="O39">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P39">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q39">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="R39">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="S39">
         <v>1.33</v>
@@ -6838,7 +6838,7 @@
         <v>2.15</v>
       </c>
       <c r="Q40">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R40">
         <v>1.9</v>
@@ -6853,7 +6853,7 @@
         <v>2.8</v>
       </c>
       <c r="V40">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W40">
         <v>1.07</v>
@@ -6865,19 +6865,19 @@
         <v>1.32</v>
       </c>
       <c r="Z40">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="AA40">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AB40">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AC40">
         <v>3.5</v>
       </c>
       <c r="AD40">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE40">
         <v>1.08</v>
@@ -6886,7 +6886,7 @@
         <v>1.67</v>
       </c>
       <c r="AG40">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="O42">
         <v>3.55</v>

--- a/jogos_2026-08-17.xlsx
+++ b/jogos_2026-08-17.xlsx
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="O6">
         <v>3.2</v>
@@ -1302,16 +1302,16 @@
         <v>2.05</v>
       </c>
       <c r="S6">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="T6">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="U6">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="V6">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W6">
         <v>1.06</v>
@@ -1320,19 +1320,19 @@
         <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="Z6">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="AA6">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AB6">
         <v>1.65</v>
       </c>
       <c r="AC6">
-        <v>3.82</v>
+        <v>3.74</v>
       </c>
       <c r="AD6">
         <v>1.26</v>
@@ -1344,7 +1344,7 @@
         <v>1.91</v>
       </c>
       <c r="AG6">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -3089,22 +3089,22 @@
         <v>1.21</v>
       </c>
       <c r="Q17">
-        <v>7</v>
+        <v>5.75</v>
       </c>
       <c r="R17">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="S17">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T17">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="U17">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V17">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W17">
         <v>1.12</v>
@@ -3113,13 +3113,13 @@
         <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="Z17">
-        <v>4.65</v>
+        <v>5</v>
       </c>
       <c r="AA17">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AB17">
         <v>2.55</v>
@@ -3131,13 +3131,13 @@
         <v>1.64</v>
       </c>
       <c r="AE17">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF17">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG17">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>3.45</v>
+        <v>3.18</v>
       </c>
       <c r="AK17">
         <v>1.01</v>
@@ -3436,13 +3436,13 @@
         <v>1.03</v>
       </c>
       <c r="X19">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="Y19">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="Z19">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="AA19">
         <v>3.3</v>
@@ -3451,7 +3451,7 @@
         <v>1.31</v>
       </c>
       <c r="AC19">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="AD19">
         <v>1.08</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="AK19">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -4873,58 +4873,58 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="O28">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="P28">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="Q28">
         <v>2</v>
       </c>
       <c r="R28">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="S28">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T28">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="U28">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="V28">
         <v>1.44</v>
       </c>
       <c r="W28">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X28">
         <v>1.04</v>
       </c>
       <c r="Y28">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z28">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AA28">
         <v>1.73</v>
       </c>
       <c r="AB28">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AC28">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AD28">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AE28">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF28">
         <v>1.8</v>
@@ -6020,7 +6020,7 @@
         <v>3.2</v>
       </c>
       <c r="P35">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="Q35">
         <v>2.63</v>
@@ -6056,7 +6056,7 @@
         <v>1.95</v>
       </c>
       <c r="AB35">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC35">
         <v>3.34</v>
@@ -6192,7 +6192,7 @@
         <v>2.04</v>
       </c>
       <c r="S36">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T36">
         <v>2.75</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="O41">
         <v>3.4</v>
       </c>
       <c r="P41">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="Q41">
         <v>2.6</v>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK41">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL41">
         <v>0</v>

--- a/jogos_2026-08-17.xlsx
+++ b/jogos_2026-08-17.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="O2">
         <v>3.4</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="O3">
-        <v>3.75</v>
+        <v>4.05</v>
       </c>
       <c r="P3">
-        <v>4.85</v>
+        <v>5.45</v>
       </c>
       <c r="Q3">
         <v>1.91</v>
@@ -819,10 +819,10 @@
         <v>3.2</v>
       </c>
       <c r="U3">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="V3">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W3">
         <v>1.14</v>
@@ -831,31 +831,31 @@
         <v>1.03</v>
       </c>
       <c r="Y3">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z3">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="AA3">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AB3">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AC3">
         <v>2.3</v>
       </c>
       <c r="AD3">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AE3">
         <v>1.2</v>
       </c>
       <c r="AF3">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AG3">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AK3">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,55 +961,55 @@
         </is>
       </c>
       <c r="N4">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="O4">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="P4">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="Q4">
-        <v>5.1</v>
+        <v>6.08</v>
       </c>
       <c r="R4">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="S4">
         <v>1.25</v>
       </c>
       <c r="T4">
-        <v>2.96</v>
+        <v>3.02</v>
       </c>
       <c r="U4">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="V4">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W4">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X4">
         <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z4">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="AA4">
         <v>1.57</v>
       </c>
       <c r="AB4">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC4">
         <v>2.6</v>
       </c>
       <c r="AD4">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AE4">
         <v>1.2</v>
@@ -1018,7 +1018,7 @@
         <v>1.74</v>
       </c>
       <c r="AG4">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AK4">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1127,10 +1127,10 @@
         <v>2.01</v>
       </c>
       <c r="O5">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="P5">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1287,19 +1287,19 @@
         </is>
       </c>
       <c r="N6">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="O6">
         <v>3.2</v>
       </c>
       <c r="P6">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="Q6">
         <v>4.16</v>
       </c>
       <c r="R6">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S6">
         <v>1.45</v>
@@ -1311,7 +1311,7 @@
         <v>2.97</v>
       </c>
       <c r="V6">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W6">
         <v>1.06</v>
@@ -1320,7 +1320,7 @@
         <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="Z6">
         <v>2.88</v>
@@ -1329,7 +1329,7 @@
         <v>2.12</v>
       </c>
       <c r="AB6">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AC6">
         <v>3.74</v>
@@ -1341,7 +1341,7 @@
         <v>1.03</v>
       </c>
       <c r="AF6">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AG6">
         <v>1.82</v>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AK6">
         <v>1.25</v>
@@ -1492,10 +1492,10 @@
         <v>1.93</v>
       </c>
       <c r="AB7">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC7">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="AD7">
         <v>1.24</v>
@@ -1616,7 +1616,7 @@
         <v>3.12</v>
       </c>
       <c r="O8">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="P8">
         <v>1.95</v>
@@ -1649,7 +1649,7 @@
         <v>1.2</v>
       </c>
       <c r="Z8">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="AA8">
         <v>1.67</v>
@@ -1806,31 +1806,31 @@
         <v>1.03</v>
       </c>
       <c r="X9">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z9">
-        <v>2.88</v>
+        <v>3.06</v>
       </c>
       <c r="AA9">
-        <v>1.94</v>
+        <v>2.07</v>
       </c>
       <c r="AB9">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AC9">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="AD9">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AE9">
         <v>1.1</v>
       </c>
       <c r="AF9">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AG9">
         <v>1.85</v>
@@ -1849,7 +1849,7 @@
         <v>1.33</v>
       </c>
       <c r="AK9">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="O10">
-        <v>3.55</v>
+        <v>3.38</v>
       </c>
       <c r="P10">
         <v>5.35</v>
@@ -1960,7 +1960,7 @@
         <v>2.5</v>
       </c>
       <c r="U10">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="V10">
         <v>1.3</v>
@@ -1975,16 +1975,16 @@
         <v>1.41</v>
       </c>
       <c r="Z10">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="AA10">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="AB10">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AC10">
-        <v>4.13</v>
+        <v>4.17</v>
       </c>
       <c r="AD10">
         <v>1.18</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK10">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>2.2</v>
       </c>
       <c r="R12">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="S12">
         <v>1.3</v>
@@ -2295,7 +2295,7 @@
         <v>1.11</v>
       </c>
       <c r="X12">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y12">
         <v>1.25</v>
@@ -2319,7 +2319,7 @@
         <v>1.1</v>
       </c>
       <c r="AF12">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG12">
         <v>2</v>
@@ -2428,19 +2428,19 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="O13">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P13">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="Q13">
-        <v>2.99</v>
+        <v>2.75</v>
       </c>
       <c r="R13">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S13">
         <v>1.38</v>
@@ -2452,10 +2452,10 @@
         <v>3</v>
       </c>
       <c r="V13">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W13">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X13">
         <v>1.06</v>
@@ -2464,13 +2464,13 @@
         <v>1.36</v>
       </c>
       <c r="Z13">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AA13">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AB13">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AC13">
         <v>3.7</v>
@@ -2479,7 +2479,7 @@
         <v>1.22</v>
       </c>
       <c r="AE13">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF13">
         <v>1.8</v>
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="O14">
         <v>3.25</v>
@@ -2603,19 +2603,19 @@
         <v>2.38</v>
       </c>
       <c r="R14">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="S14">
         <v>1.42</v>
       </c>
       <c r="T14">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="U14">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="V14">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W14">
         <v>1.05</v>
@@ -2754,28 +2754,28 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="O15">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="P15">
-        <v>7.4</v>
+        <v>6.9</v>
       </c>
       <c r="Q15">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="R15">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="S15">
         <v>1.19</v>
       </c>
       <c r="T15">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="U15">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="V15">
         <v>1.73</v>
@@ -2793,19 +2793,19 @@
         <v>5.75</v>
       </c>
       <c r="AA15">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AB15">
         <v>2.8</v>
       </c>
       <c r="AC15">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AD15">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AE15">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AF15">
         <v>1.67</v>
@@ -2827,7 +2827,7 @@
         <v>1.15</v>
       </c>
       <c r="AK15">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2920,46 +2920,46 @@
         <v>1.44</v>
       </c>
       <c r="O16">
-        <v>4.65</v>
+        <v>4.5</v>
       </c>
       <c r="P16">
-        <v>6.7</v>
+        <v>7.3</v>
       </c>
       <c r="Q16">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="R16">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="S16">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T16">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U16">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="V16">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W16">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
         <v>1.16</v>
       </c>
       <c r="Z16">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AA16">
         <v>1.57</v>
       </c>
       <c r="AB16">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AC16">
         <v>2.45</v>
@@ -2971,10 +2971,10 @@
         <v>1.16</v>
       </c>
       <c r="AF16">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AG16">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>1.17</v>
       </c>
       <c r="AK16">
-        <v>2.73</v>
+        <v>2.89</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3089,40 +3089,40 @@
         <v>1.21</v>
       </c>
       <c r="Q17">
-        <v>5.75</v>
+        <v>8</v>
       </c>
       <c r="R17">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="S17">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T17">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="U17">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="V17">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="W17">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y17">
         <v>1.15</v>
       </c>
       <c r="Z17">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="AA17">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AB17">
-        <v>2.55</v>
+        <v>2.24</v>
       </c>
       <c r="AC17">
         <v>2.02</v>
@@ -3134,7 +3134,7 @@
         <v>1.22</v>
       </c>
       <c r="AF17">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AG17">
         <v>1.85</v>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>3.18</v>
+        <v>2.94</v>
       </c>
       <c r="AK17">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,28 +3243,28 @@
         </is>
       </c>
       <c r="N18">
+        <v>3.2</v>
+      </c>
+      <c r="O18">
         <v>3.5</v>
       </c>
-      <c r="O18">
-        <v>3.45</v>
-      </c>
       <c r="P18">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="Q18">
         <v>3.9</v>
       </c>
       <c r="R18">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S18">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T18">
         <v>3</v>
       </c>
       <c r="U18">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="V18">
         <v>1.44</v>
@@ -3276,16 +3276,16 @@
         <v>1</v>
       </c>
       <c r="Y18">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z18">
         <v>3.9</v>
       </c>
       <c r="AA18">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AB18">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AC18">
         <v>2.52</v>
@@ -3294,7 +3294,7 @@
         <v>1.41</v>
       </c>
       <c r="AE18">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF18">
         <v>1.62</v>
@@ -3412,7 +3412,7 @@
         <v>2.71</v>
       </c>
       <c r="P19">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="Q19">
         <v>3.08</v>
@@ -3424,13 +3424,13 @@
         <v>1.69</v>
       </c>
       <c r="T19">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="U19">
         <v>4.45</v>
       </c>
       <c r="V19">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="W19">
         <v>1.03</v>
@@ -3442,10 +3442,10 @@
         <v>1.58</v>
       </c>
       <c r="Z19">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="AA19">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="AB19">
         <v>1.31</v>
@@ -3457,13 +3457,13 @@
         <v>1.08</v>
       </c>
       <c r="AE19">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF19">
         <v>2.51</v>
       </c>
       <c r="AG19">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AK19">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3572,25 +3572,25 @@
         <v>2.06</v>
       </c>
       <c r="O20">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P20">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="Q20">
         <v>2.4</v>
       </c>
       <c r="R20">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="S20">
         <v>1.17</v>
       </c>
       <c r="T20">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="U20">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="V20">
         <v>1.89</v>
@@ -3608,7 +3608,7 @@
         <v>6.24</v>
       </c>
       <c r="AA20">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AB20">
         <v>3.42</v>
@@ -3617,7 +3617,7 @@
         <v>1.76</v>
       </c>
       <c r="AD20">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AE20">
         <v>1.36</v>
@@ -3626,7 +3626,7 @@
         <v>1.2</v>
       </c>
       <c r="AG20">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>3.4</v>
       </c>
       <c r="P21">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="Q21">
         <v>2.55</v>
@@ -3750,7 +3750,7 @@
         <v>1.3</v>
       </c>
       <c r="T21">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U21">
         <v>2.44</v>
@@ -3762,25 +3762,25 @@
         <v>1.08</v>
       </c>
       <c r="X21">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="Z21">
         <v>3.8</v>
       </c>
       <c r="AA21">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AB21">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC21">
         <v>2.75</v>
       </c>
       <c r="AD21">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE21">
         <v>1.13</v>
@@ -3789,7 +3789,7 @@
         <v>1.57</v>
       </c>
       <c r="AG21">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AK21">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3913,7 +3913,7 @@
         <v>1.44</v>
       </c>
       <c r="T22">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="U22">
         <v>3.2</v>
@@ -3928,28 +3928,28 @@
         <v>1.05</v>
       </c>
       <c r="Y22">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="Z22">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="AA22">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="AB22">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AC22">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="AD22">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AE22">
         <v>1.01</v>
       </c>
       <c r="AF22">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="AG22">
         <v>1.4</v>
@@ -3968,7 +3968,7 @@
         <v>1.02</v>
       </c>
       <c r="AK22">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,31 +4058,31 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="O23">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P23">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="Q23">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="R23">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S23">
         <v>1.24</v>
       </c>
       <c r="T23">
-        <v>3.7</v>
+        <v>3.44</v>
       </c>
       <c r="U23">
         <v>2.2</v>
       </c>
       <c r="V23">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="W23">
         <v>1.17</v>
@@ -4091,16 +4091,16 @@
         <v>1.03</v>
       </c>
       <c r="Y23">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z23">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AA23">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AB23">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AC23">
         <v>2.31</v>
@@ -4131,7 +4131,7 @@
         <v>1.24</v>
       </c>
       <c r="AK23">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,19 +4221,19 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="O24">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P24">
-        <v>3.18</v>
+        <v>3.6</v>
       </c>
       <c r="Q24">
         <v>2.11</v>
       </c>
       <c r="R24">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="S24">
         <v>1.13</v>
@@ -4254,10 +4254,10 @@
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z24">
-        <v>6.4</v>
+        <v>7.5</v>
       </c>
       <c r="AA24">
         <v>1.25</v>
@@ -4269,16 +4269,16 @@
         <v>1.77</v>
       </c>
       <c r="AD24">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AE24">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AF24">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AG24">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>1.14</v>
       </c>
       <c r="AK24">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4387,7 +4387,7 @@
         <v>2.89</v>
       </c>
       <c r="O25">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="P25">
         <v>2.2</v>
@@ -4405,10 +4405,10 @@
         <v>3.9</v>
       </c>
       <c r="U25">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="V25">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="W25">
         <v>1.13</v>
@@ -4429,16 +4429,16 @@
         <v>2.55</v>
       </c>
       <c r="AC25">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD25">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AE25">
         <v>1.25</v>
       </c>
       <c r="AF25">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AG25">
         <v>2.65</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="O26">
-        <v>3.72</v>
+        <v>3.4</v>
       </c>
       <c r="P26">
-        <v>4.15</v>
+        <v>4.19</v>
       </c>
       <c r="Q26">
         <v>2.21</v>
@@ -4577,25 +4577,25 @@
         <v>1.05</v>
       </c>
       <c r="X26">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y26">
         <v>1.3</v>
       </c>
       <c r="Z26">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AA26">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AB26">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AC26">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AD26">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE26">
         <v>1.1</v>
@@ -4710,19 +4710,19 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="O27">
         <v>3.3</v>
       </c>
       <c r="P27">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q27">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="R27">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="S27">
         <v>1.4</v>
@@ -4731,10 +4731,10 @@
         <v>2.73</v>
       </c>
       <c r="U27">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="V27">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W27">
         <v>1.04</v>
@@ -4746,22 +4746,22 @@
         <v>1.3</v>
       </c>
       <c r="Z27">
-        <v>3.15</v>
+        <v>3.51</v>
       </c>
       <c r="AA27">
         <v>1.95</v>
       </c>
       <c r="AB27">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AC27">
-        <v>3.4</v>
+        <v>3.41</v>
       </c>
       <c r="AD27">
         <v>1.3</v>
       </c>
       <c r="AE27">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF27">
         <v>1.7</v>
@@ -5039,28 +5039,28 @@
         <v>1.5</v>
       </c>
       <c r="O29">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="P29">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Q29">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="R29">
         <v>2.4</v>
       </c>
       <c r="S29">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T29">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U29">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="V29">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W29">
         <v>1.11</v>
@@ -5072,7 +5072,7 @@
         <v>1.2</v>
       </c>
       <c r="Z29">
-        <v>4.45</v>
+        <v>4.51</v>
       </c>
       <c r="AA29">
         <v>1.65</v>
@@ -5084,13 +5084,13 @@
         <v>2.5</v>
       </c>
       <c r="AD29">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE29">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF29">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AG29">
         <v>2.1</v>
@@ -5202,16 +5202,16 @@
         <v>2.22</v>
       </c>
       <c r="O30">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="P30">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="Q30">
         <v>3.04</v>
       </c>
       <c r="R30">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="S30">
         <v>1.55</v>
@@ -5229,7 +5229,7 @@
         <v>1.03</v>
       </c>
       <c r="X30">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y30">
         <v>1.42</v>
@@ -5241,22 +5241,22 @@
         <v>2.38</v>
       </c>
       <c r="AB30">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AC30">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="AD30">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE30">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF30">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AG30">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK30">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="O31">
-        <v>3.41</v>
+        <v>3.5</v>
       </c>
       <c r="P31">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q31">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="R31">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="S31">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T31">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="U31">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="V31">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W31">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X31">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z31">
-        <v>4.1</v>
+        <v>4.06</v>
       </c>
       <c r="AA31">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AB31">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="AC31">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="AD31">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE31">
         <v>1.13</v>
       </c>
       <c r="AF31">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG31">
-        <v>2.11</v>
+        <v>2.21</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>1.4</v>
       </c>
       <c r="AK31">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,16 +5525,16 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="O32">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="P32">
-        <v>3.25</v>
+        <v>2.93</v>
       </c>
       <c r="Q32">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="R32">
         <v>2.88</v>
@@ -5546,10 +5546,10 @@
         <v>5</v>
       </c>
       <c r="U32">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="V32">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="W32">
         <v>1.3</v>
@@ -5558,31 +5558,31 @@
         <v>1</v>
       </c>
       <c r="Y32">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z32">
-        <v>7.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA32">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AB32">
-        <v>3.86</v>
+        <v>4.14</v>
       </c>
       <c r="AC32">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AD32">
         <v>2.28</v>
       </c>
       <c r="AE32">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="AF32">
         <v>1.25</v>
       </c>
       <c r="AG32">
-        <v>3.56</v>
+        <v>3.74</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>1.3</v>
       </c>
       <c r="AK32">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,25 +5688,25 @@
         </is>
       </c>
       <c r="N33">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="O33">
-        <v>6.25</v>
+        <v>6.4</v>
       </c>
       <c r="P33">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Q33">
         <v>11</v>
       </c>
       <c r="R33">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="S33">
         <v>1.28</v>
       </c>
       <c r="T33">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U33">
         <v>2.34</v>
@@ -5721,31 +5721,31 @@
         <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z33">
         <v>4.4</v>
       </c>
       <c r="AA33">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB33">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AC33">
         <v>2.38</v>
       </c>
       <c r="AD33">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AE33">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AF33">
         <v>2.22</v>
       </c>
       <c r="AG33">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>4.6</v>
+        <v>1.13</v>
       </c>
       <c r="AK33">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="O34">
         <v>4.8</v>
       </c>
       <c r="P34">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="Q34">
         <v>1.73</v>
@@ -5878,22 +5878,22 @@
         <v>1.55</v>
       </c>
       <c r="W34">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X34">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y34">
         <v>1.13</v>
       </c>
       <c r="Z34">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AA34">
         <v>1.6</v>
       </c>
       <c r="AB34">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="AC34">
         <v>2.34</v>
@@ -5902,7 +5902,7 @@
         <v>1.48</v>
       </c>
       <c r="AE34">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF34">
         <v>1.9</v>
@@ -6020,7 +6020,7 @@
         <v>3.2</v>
       </c>
       <c r="P35">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="Q35">
         <v>2.63</v>
@@ -6035,10 +6035,10 @@
         <v>2.85</v>
       </c>
       <c r="U35">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="V35">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W35">
         <v>1.07</v>
@@ -6053,10 +6053,10 @@
         <v>3.22</v>
       </c>
       <c r="AA35">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AB35">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC35">
         <v>3.34</v>
@@ -6180,16 +6180,16 @@
         <v>1.91</v>
       </c>
       <c r="O36">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P36">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
       </c>
       <c r="R36">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="S36">
         <v>1.36</v>
@@ -6213,25 +6213,25 @@
         <v>1.3</v>
       </c>
       <c r="Z36">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AA36">
         <v>2.01</v>
       </c>
       <c r="AB36">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AC36">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AD36">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE36">
         <v>1.08</v>
       </c>
       <c r="AF36">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AG36">
         <v>1.91</v>
@@ -6545,7 +6545,7 @@
         <v>2.07</v>
       </c>
       <c r="AB38">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AC38">
         <v>3.5</v>
@@ -6576,7 +6576,7 @@
         <v>1.28</v>
       </c>
       <c r="AK38">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="O39">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="P39">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="Q39">
-        <v>2.29</v>
+        <v>2.18</v>
       </c>
       <c r="R39">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="S39">
         <v>1.33</v>
       </c>
       <c r="T39">
-        <v>2.84</v>
+        <v>2.93</v>
       </c>
       <c r="U39">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="V39">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W39">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X39">
         <v>1.03</v>
       </c>
       <c r="Y39">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z39">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="AA39">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AB39">
         <v>1.7</v>
       </c>
       <c r="AC39">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AD39">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE39">
         <v>1.07</v>
       </c>
       <c r="AF39">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AG39">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AK39">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6835,7 +6835,7 @@
         <v>3.2</v>
       </c>
       <c r="P40">
-        <v>2.15</v>
+        <v>2.27</v>
       </c>
       <c r="Q40">
         <v>3.4</v>
@@ -6862,16 +6862,16 @@
         <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="Z40">
-        <v>2.95</v>
+        <v>3.11</v>
       </c>
       <c r="AA40">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="AB40">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AC40">
         <v>3.5</v>
@@ -6998,7 +6998,7 @@
         <v>3.4</v>
       </c>
       <c r="P41">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Q41">
         <v>2.6</v>
@@ -7034,7 +7034,7 @@
         <v>1.75</v>
       </c>
       <c r="AB41">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC41">
         <v>2.95</v>
@@ -7155,7 +7155,7 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="O42">
         <v>3.55</v>
@@ -7197,7 +7197,7 @@
         <v>1.75</v>
       </c>
       <c r="AB42">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="AC42">
         <v>2.66</v>

--- a/jogos_2026-08-17.xlsx
+++ b/jogos_2026-08-17.xlsx
@@ -801,10 +801,10 @@
         <v>1.45</v>
       </c>
       <c r="O3">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="P3">
-        <v>5.45</v>
+        <v>5.25</v>
       </c>
       <c r="Q3">
         <v>1.91</v>
@@ -813,7 +813,7 @@
         <v>2.5</v>
       </c>
       <c r="S3">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T3">
         <v>3.2</v>
@@ -825,7 +825,7 @@
         <v>1.6</v>
       </c>
       <c r="W3">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X3">
         <v>1.03</v>
@@ -834,7 +834,7 @@
         <v>1.15</v>
       </c>
       <c r="Z3">
-        <v>4.55</v>
+        <v>4.8</v>
       </c>
       <c r="AA3">
         <v>1.49</v>
@@ -843,7 +843,7 @@
         <v>2.3</v>
       </c>
       <c r="AC3">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AD3">
         <v>1.56</v>
@@ -852,7 +852,7 @@
         <v>1.2</v>
       </c>
       <c r="AF3">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG3">
         <v>2.1</v>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK3">
         <v>2.5</v>
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="N4">
-        <v>5.3</v>
+        <v>6.39</v>
       </c>
       <c r="O4">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P4">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="Q4">
-        <v>6.08</v>
+        <v>6.17</v>
       </c>
       <c r="R4">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="S4">
         <v>1.25</v>
@@ -982,10 +982,10 @@
         <v>3.02</v>
       </c>
       <c r="U4">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V4">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W4">
         <v>1.11</v>
@@ -997,7 +997,7 @@
         <v>1.17</v>
       </c>
       <c r="Z4">
-        <v>4.33</v>
+        <v>4.35</v>
       </c>
       <c r="AA4">
         <v>1.57</v>
@@ -1009,7 +1009,7 @@
         <v>2.6</v>
       </c>
       <c r="AD4">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AE4">
         <v>1.2</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="AK4">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="O8">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P8">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q8">
         <v>3.64</v>
@@ -1948,10 +1948,10 @@
         <v>5.35</v>
       </c>
       <c r="Q10">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="R10">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="S10">
         <v>1.46</v>
@@ -1960,7 +1960,7 @@
         <v>2.5</v>
       </c>
       <c r="U10">
-        <v>3.36</v>
+        <v>3.16</v>
       </c>
       <c r="V10">
         <v>1.3</v>
@@ -1972,19 +1972,19 @@
         <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="Z10">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="AA10">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="AB10">
         <v>1.64</v>
       </c>
       <c r="AC10">
-        <v>4.17</v>
+        <v>4.24</v>
       </c>
       <c r="AD10">
         <v>1.18</v>
@@ -1993,10 +1993,10 @@
         <v>1.03</v>
       </c>
       <c r="AF10">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="AG10">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>1.3</v>
       </c>
       <c r="AK10">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="O35">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P35">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="Q35">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="R35">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="S35">
+        <v>1.36</v>
+      </c>
+      <c r="T35">
+        <v>2.75</v>
+      </c>
+      <c r="U35">
+        <v>2.82</v>
+      </c>
+      <c r="V35">
         <v>1.35</v>
       </c>
-      <c r="T35">
-        <v>2.85</v>
-      </c>
-      <c r="U35">
-        <v>2.8</v>
-      </c>
-      <c r="V35">
-        <v>1.36</v>
-      </c>
       <c r="W35">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X35">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y35">
         <v>1.3</v>
       </c>
       <c r="Z35">
-        <v>3.22</v>
+        <v>3.08</v>
       </c>
       <c r="AA35">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AB35">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC35">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="AD35">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE35">
         <v>1.08</v>
       </c>
       <c r="AF35">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AG35">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AK35">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="O36">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P36">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="Q36">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="R36">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="S36">
+        <v>1.35</v>
+      </c>
+      <c r="T36">
+        <v>2.85</v>
+      </c>
+      <c r="U36">
+        <v>2.8</v>
+      </c>
+      <c r="V36">
         <v>1.36</v>
       </c>
-      <c r="T36">
-        <v>2.75</v>
-      </c>
-      <c r="U36">
-        <v>2.82</v>
-      </c>
-      <c r="V36">
-        <v>1.35</v>
-      </c>
       <c r="W36">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X36">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
         <v>1.3</v>
       </c>
       <c r="Z36">
-        <v>3.08</v>
+        <v>3.22</v>
       </c>
       <c r="AA36">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AB36">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AC36">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="AD36">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE36">
         <v>1.08</v>
       </c>
       <c r="AF36">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AG36">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AK36">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6349,16 +6349,16 @@
         <v>5.61</v>
       </c>
       <c r="Q37">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="R37">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="S37">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T37">
-        <v>2.99</v>
+        <v>2.82</v>
       </c>
       <c r="U37">
         <v>2.75</v>
@@ -6370,19 +6370,19 @@
         <v>1.07</v>
       </c>
       <c r="X37">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z37">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AA37">
         <v>1.83</v>
       </c>
       <c r="AB37">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC37">
         <v>3</v>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK37">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AL37">
         <v>0</v>

--- a/jogos_2026-08-17.xlsx
+++ b/jogos_2026-08-17.xlsx
@@ -2431,61 +2431,61 @@
         <v>2.25</v>
       </c>
       <c r="O13">
+        <v>3</v>
+      </c>
+      <c r="P13">
+        <v>2.8</v>
+      </c>
+      <c r="Q13">
         <v>3.1</v>
       </c>
-      <c r="P13">
-        <v>2.9</v>
-      </c>
-      <c r="Q13">
-        <v>2.75</v>
-      </c>
       <c r="R13">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="S13">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="T13">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="U13">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="V13">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W13">
+        <v>1.01</v>
+      </c>
+      <c r="X13">
         <v>1.02</v>
       </c>
-      <c r="X13">
-        <v>1.06</v>
-      </c>
       <c r="Y13">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z13">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AA13">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="AB13">
-        <v>1.76</v>
+        <v>1.61</v>
       </c>
       <c r="AC13">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="AD13">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE13">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AF13">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG13">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2917,40 +2917,40 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="O16">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="P16">
-        <v>7.3</v>
+        <v>6.2</v>
       </c>
       <c r="Q16">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="R16">
-        <v>2.3</v>
+        <v>2.49</v>
       </c>
       <c r="S16">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T16">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="U16">
-        <v>2.23</v>
+        <v>2.33</v>
       </c>
       <c r="V16">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W16">
         <v>1.1</v>
       </c>
       <c r="X16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y16">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z16">
         <v>4.8</v>
@@ -2965,16 +2965,16 @@
         <v>2.45</v>
       </c>
       <c r="AD16">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AE16">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AF16">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AG16">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AK16">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,61 +3080,61 @@
         </is>
       </c>
       <c r="N17">
-        <v>9</v>
+        <v>6.5</v>
       </c>
       <c r="O17">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="P17">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="Q17">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="R17">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="S17">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T17">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U17">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V17">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="W17">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X17">
         <v>1.03</v>
       </c>
       <c r="Y17">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z17">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA17">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AB17">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="AC17">
-        <v>2.02</v>
+        <v>2.5</v>
       </c>
       <c r="AD17">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="AE17">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AF17">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="AG17">
         <v>1.85</v>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>2.94</v>
+        <v>1.18</v>
       </c>
       <c r="AK17">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AL17">
         <v>0</v>

--- a/jogos_2026-08-17.xlsx
+++ b/jogos_2026-08-17.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="O2">
-        <v>3.4</v>
+        <v>3.44</v>
       </c>
       <c r="P2">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA2">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AB2">
         <v>2.25</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,31 +798,31 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="O3">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="P3">
-        <v>5.25</v>
+        <v>6.75</v>
       </c>
       <c r="Q3">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="R3">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="S3">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T3">
         <v>3.2</v>
       </c>
       <c r="U3">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="V3">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="W3">
         <v>1.13</v>
@@ -831,31 +831,31 @@
         <v>1.03</v>
       </c>
       <c r="Y3">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z3">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AA3">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AB3">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AC3">
-        <v>2.45</v>
+        <v>2.16</v>
       </c>
       <c r="AD3">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="AE3">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AF3">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG3">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.17</v>
+        <v>1.02</v>
       </c>
       <c r="AK3">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="N4">
-        <v>6.39</v>
+        <v>5.25</v>
       </c>
       <c r="O4">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P4">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="Q4">
-        <v>6.17</v>
+        <v>5</v>
       </c>
       <c r="R4">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="S4">
         <v>1.25</v>
@@ -982,59 +982,59 @@
         <v>3.02</v>
       </c>
       <c r="U4">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="V4">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W4">
         <v>1.11</v>
       </c>
       <c r="X4">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y4">
+        <v>1.18</v>
+      </c>
+      <c r="Z4">
+        <v>4.5</v>
+      </c>
+      <c r="AA4">
+        <v>1.6</v>
+      </c>
+      <c r="AB4">
+        <v>2.36</v>
+      </c>
+      <c r="AC4">
+        <v>2.26</v>
+      </c>
+      <c r="AD4">
+        <v>1.56</v>
+      </c>
+      <c r="AE4">
+        <v>1.21</v>
+      </c>
+      <c r="AF4">
+        <v>1.6</v>
+      </c>
+      <c r="AG4">
+        <v>2.1</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4">
         <v>1.17</v>
       </c>
-      <c r="Z4">
-        <v>4.35</v>
-      </c>
-      <c r="AA4">
-        <v>1.57</v>
-      </c>
-      <c r="AB4">
-        <v>2.3</v>
-      </c>
-      <c r="AC4">
-        <v>2.6</v>
-      </c>
-      <c r="AD4">
-        <v>1.58</v>
-      </c>
-      <c r="AE4">
-        <v>1.2</v>
-      </c>
-      <c r="AF4">
-        <v>1.74</v>
-      </c>
-      <c r="AG4">
-        <v>1.94</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4">
-        <v>1.2</v>
-      </c>
       <c r="AK4">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,80 +1124,80 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="O5">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P5">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA5">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AB5">
+        <v>1.74</v>
+      </c>
+      <c r="AC5">
+        <v>3.45</v>
+      </c>
+      <c r="AD5">
+        <v>1.25</v>
+      </c>
+      <c r="AE5">
+        <v>1.06</v>
+      </c>
+      <c r="AF5">
+        <v>1.79</v>
+      </c>
+      <c r="AG5">
+        <v>1.92</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5">
+        <v>1.25</v>
+      </c>
+      <c r="AK5">
         <v>1.8</v>
-      </c>
-      <c r="AC5">
-        <v>0</v>
-      </c>
-      <c r="AD5">
-        <v>0</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>0</v>
-      </c>
-      <c r="AG5">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5">
-        <v>0</v>
-      </c>
-      <c r="AK5">
-        <v>0</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O6">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P6">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="Q6">
         <v>4.16</v>
       </c>
       <c r="R6">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="S6">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="T6">
-        <v>2.59</v>
+        <v>2.2</v>
       </c>
       <c r="U6">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="V6">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W6">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X6">
         <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="Z6">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="AA6">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AB6">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AC6">
-        <v>3.74</v>
+        <v>3.15</v>
       </c>
       <c r="AD6">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AE6">
         <v>1.03</v>
       </c>
       <c r="AF6">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AG6">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="AK6">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.53</v>
+        <v>2.2</v>
       </c>
       <c r="O7">
         <v>3.2</v>
       </c>
       <c r="P7">
-        <v>2.37</v>
+        <v>2.75</v>
       </c>
       <c r="Q7">
-        <v>3.18</v>
+        <v>2.82</v>
       </c>
       <c r="R7">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="S7">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="T7">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="U7">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="V7">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="W7">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X7">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z7">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="AA7">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AB7">
-        <v>1.76</v>
+        <v>1.99</v>
       </c>
       <c r="AC7">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AD7">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AE7">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF7">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AG7">
-        <v>1.96</v>
+        <v>2.15</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK7">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="O8">
+        <v>3.85</v>
+      </c>
+      <c r="P8">
+        <v>1.89</v>
+      </c>
+      <c r="Q8">
         <v>3.6</v>
       </c>
-      <c r="P8">
-        <v>1.96</v>
-      </c>
-      <c r="Q8">
-        <v>3.64</v>
-      </c>
       <c r="R8">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S8">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T8">
-        <v>3.14</v>
+        <v>3.42</v>
       </c>
       <c r="U8">
-        <v>2.45</v>
+        <v>2.27</v>
       </c>
       <c r="V8">
+        <v>1.54</v>
+      </c>
+      <c r="W8">
+        <v>1.1</v>
+      </c>
+      <c r="X8">
+        <v>1.01</v>
+      </c>
+      <c r="Y8">
+        <v>1.14</v>
+      </c>
+      <c r="Z8">
+        <v>4.4</v>
+      </c>
+      <c r="AA8">
+        <v>1.57</v>
+      </c>
+      <c r="AB8">
+        <v>2.25</v>
+      </c>
+      <c r="AC8">
+        <v>2.35</v>
+      </c>
+      <c r="AD8">
+        <v>1.47</v>
+      </c>
+      <c r="AE8">
+        <v>1.16</v>
+      </c>
+      <c r="AF8">
         <v>1.5</v>
       </c>
-      <c r="W8">
-        <v>1.08</v>
-      </c>
-      <c r="X8">
-        <v>1.02</v>
-      </c>
-      <c r="Y8">
-        <v>1.2</v>
-      </c>
-      <c r="Z8">
-        <v>4</v>
-      </c>
-      <c r="AA8">
-        <v>1.67</v>
-      </c>
-      <c r="AB8">
-        <v>2.1</v>
-      </c>
-      <c r="AC8">
-        <v>2.7</v>
-      </c>
-      <c r="AD8">
-        <v>1.38</v>
-      </c>
-      <c r="AE8">
-        <v>1.13</v>
-      </c>
-      <c r="AF8">
-        <v>1.57</v>
-      </c>
       <c r="AG8">
-        <v>2.15</v>
+        <v>2.36</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.2</v>
+        <v>1.75</v>
       </c>
       <c r="AK8">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,28 +1776,28 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="O9">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P9">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="Q9">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="R9">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="S9">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T9">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="U9">
-        <v>2.75</v>
+        <v>3.21</v>
       </c>
       <c r="V9">
         <v>1.33</v>
@@ -1806,22 +1806,22 @@
         <v>1.03</v>
       </c>
       <c r="X9">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="Z9">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="AA9">
-        <v>2.07</v>
+        <v>2.16</v>
       </c>
       <c r="AB9">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AC9">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="AD9">
         <v>1.21</v>
@@ -1830,7 +1830,7 @@
         <v>1.1</v>
       </c>
       <c r="AF9">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AG9">
         <v>1.85</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK9">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,16 +1939,16 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="O10">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="P10">
-        <v>5.35</v>
+        <v>5.45</v>
       </c>
       <c r="Q10">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="R10">
         <v>2.04</v>
@@ -1960,7 +1960,7 @@
         <v>2.5</v>
       </c>
       <c r="U10">
-        <v>3.16</v>
+        <v>3.4</v>
       </c>
       <c r="V10">
         <v>1.3</v>
@@ -1969,34 +1969,34 @@
         <v>1.02</v>
       </c>
       <c r="X10">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y10">
         <v>1.42</v>
       </c>
       <c r="Z10">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="AA10">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="AB10">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AC10">
-        <v>4.24</v>
+        <v>4.25</v>
       </c>
       <c r="AD10">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE10">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF10">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AG10">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.72</v>
+        <v>1.88</v>
       </c>
       <c r="O12">
+        <v>3.3</v>
+      </c>
+      <c r="P12">
         <v>3.7</v>
       </c>
-      <c r="P12">
-        <v>4.2</v>
-      </c>
       <c r="Q12">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="R12">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="S12">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="T12">
-        <v>3.2</v>
+        <v>2.74</v>
       </c>
       <c r="U12">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="V12">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W12">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X12">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z12">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="AA12">
-        <v>1.84</v>
+        <v>1.99</v>
       </c>
       <c r="AB12">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="AC12">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="AD12">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AE12">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF12">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG12">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK12">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="O13">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="P13">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="Q13">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="R13">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="S13">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="T13">
-        <v>2.47</v>
+        <v>2.36</v>
       </c>
       <c r="U13">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="V13">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="W13">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X13">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y13">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="Z13">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="AA13">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="AB13">
         <v>1.61</v>
       </c>
       <c r="AC13">
-        <v>4.1</v>
+        <v>4.36</v>
       </c>
       <c r="AD13">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE13">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF13">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AG13">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK13">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2594,55 +2594,55 @@
         <v>1.77</v>
       </c>
       <c r="O14">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P14">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="Q14">
         <v>2.38</v>
       </c>
       <c r="R14">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="S14">
         <v>1.42</v>
       </c>
       <c r="T14">
-        <v>2.75</v>
+        <v>2.47</v>
       </c>
       <c r="U14">
-        <v>2.94</v>
+        <v>3.02</v>
       </c>
       <c r="V14">
         <v>1.33</v>
       </c>
       <c r="W14">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X14">
         <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z14">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="AA14">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB14">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="AC14">
-        <v>4.1</v>
+        <v>3.54</v>
       </c>
       <c r="AD14">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AE14">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF14">
         <v>1.95</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK14">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="O15">
         <v>5.2</v>
       </c>
       <c r="P15">
-        <v>6.9</v>
+        <v>8.4</v>
       </c>
       <c r="Q15">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R15">
-        <v>2.97</v>
+        <v>2.79</v>
       </c>
       <c r="S15">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="T15">
-        <v>3.92</v>
+        <v>4.15</v>
       </c>
       <c r="U15">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="V15">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="W15">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="X15">
         <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z15">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="AA15">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AB15">
-        <v>2.8</v>
+        <v>3.02</v>
       </c>
       <c r="AC15">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AD15">
         <v>1.73</v>
       </c>
       <c r="AE15">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AF15">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG15">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>1.15</v>
       </c>
       <c r="AK15">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="O16">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="P16">
         <v>6.2</v>
@@ -2929,52 +2929,52 @@
         <v>1.89</v>
       </c>
       <c r="R16">
-        <v>2.49</v>
+        <v>2.55</v>
       </c>
       <c r="S16">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T16">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="U16">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="V16">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W16">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X16">
         <v>1.04</v>
       </c>
       <c r="Y16">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z16">
         <v>4.8</v>
       </c>
       <c r="AA16">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB16">
-        <v>2.21</v>
+        <v>2.46</v>
       </c>
       <c r="AC16">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AD16">
         <v>1.53</v>
       </c>
       <c r="AE16">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF16">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AG16">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK16">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3086,25 +3086,25 @@
         <v>4.6</v>
       </c>
       <c r="P17">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="Q17">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="R17">
         <v>2.45</v>
       </c>
       <c r="S17">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T17">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U17">
         <v>2.25</v>
       </c>
       <c r="V17">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W17">
         <v>1.1</v>
@@ -3113,7 +3113,7 @@
         <v>1.03</v>
       </c>
       <c r="Y17">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z17">
         <v>4.5</v>
@@ -3128,10 +3128,10 @@
         <v>2.5</v>
       </c>
       <c r="AD17">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AE17">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AF17">
         <v>1.84</v>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="AK17">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="O18">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P18">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="Q18">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="R18">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="S18">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T18">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U18">
-        <v>2.06</v>
+        <v>2.45</v>
       </c>
       <c r="V18">
         <v>1.44</v>
       </c>
       <c r="W18">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X18">
         <v>1</v>
       </c>
       <c r="Y18">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z18">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AA18">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AB18">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC18">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="AD18">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE18">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF18">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AG18">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK18">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="O21">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P21">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="Q21">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="R21">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="S21">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T21">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U21">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="V21">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="W21">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X21">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y21">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z21">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AA21">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AB21">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AC21">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="AD21">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AE21">
         <v>1.13</v>
       </c>
       <c r="AF21">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AG21">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK21">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4547,65 +4547,65 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="O26">
         <v>3.4</v>
       </c>
       <c r="P26">
-        <v>4.19</v>
+        <v>4.6</v>
       </c>
       <c r="Q26">
-        <v>2.21</v>
+        <v>2.43</v>
       </c>
       <c r="R26">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S26">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T26">
-        <v>2.94</v>
+        <v>2.87</v>
       </c>
       <c r="U26">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="V26">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W26">
         <v>1.05</v>
       </c>
       <c r="X26">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y26">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z26">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="AA26">
+        <v>1.96</v>
+      </c>
+      <c r="AB26">
+        <v>1.75</v>
+      </c>
+      <c r="AC26">
+        <v>3.4</v>
+      </c>
+      <c r="AD26">
+        <v>1.29</v>
+      </c>
+      <c r="AE26">
+        <v>1.06</v>
+      </c>
+      <c r="AF26">
+        <v>1.73</v>
+      </c>
+      <c r="AG26">
         <v>1.83</v>
       </c>
-      <c r="AB26">
-        <v>1.85</v>
-      </c>
-      <c r="AC26">
-        <v>3.2</v>
-      </c>
-      <c r="AD26">
-        <v>1.3</v>
-      </c>
-      <c r="AE26">
-        <v>1.1</v>
-      </c>
-      <c r="AF26">
-        <v>1.72</v>
-      </c>
-      <c r="AG26">
-        <v>1.87</v>
-      </c>
       <c r="AH26" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK26">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="O29">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="P29">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="Q29">
         <v>1.91</v>
       </c>
       <c r="R29">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S29">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T29">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="U29">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="V29">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W29">
         <v>1.11</v>
       </c>
       <c r="X29">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y29">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z29">
-        <v>4.51</v>
+        <v>4.35</v>
       </c>
       <c r="AA29">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AB29">
-        <v>2.17</v>
+        <v>2.31</v>
       </c>
       <c r="AC29">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AD29">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="AE29">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF29">
         <v>1.65</v>
       </c>
       <c r="AG29">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AK29">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,31 +5199,31 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="O30">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="P30">
-        <v>3.6</v>
+        <v>3.89</v>
       </c>
       <c r="Q30">
-        <v>3.04</v>
+        <v>2.93</v>
       </c>
       <c r="R30">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="S30">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="T30">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="U30">
         <v>3.3</v>
       </c>
       <c r="V30">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W30">
         <v>1.03</v>
@@ -5232,31 +5232,31 @@
         <v>1.07</v>
       </c>
       <c r="Y30">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="Z30">
         <v>2.88</v>
       </c>
       <c r="AA30">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="AB30">
         <v>1.6</v>
       </c>
       <c r="AC30">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="AD30">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE30">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF30">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AG30">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK30">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,31 +5362,31 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="O31">
-        <v>3.5</v>
+        <v>3.41</v>
       </c>
       <c r="P31">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="Q31">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="R31">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="S31">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T31">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="U31">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="V31">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W31">
         <v>1.08</v>
@@ -5395,31 +5395,31 @@
         <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z31">
-        <v>4.06</v>
+        <v>3.75</v>
       </c>
       <c r="AA31">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="AB31">
-        <v>2.04</v>
+        <v>2.11</v>
       </c>
       <c r="AC31">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="AD31">
         <v>1.4</v>
       </c>
       <c r="AE31">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF31">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG31">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AK31">
         <v>1.5</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="O33">
-        <v>6.4</v>
+        <v>5.3</v>
       </c>
       <c r="P33">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="Q33">
         <v>11</v>
@@ -5703,49 +5703,49 @@
         <v>2.63</v>
       </c>
       <c r="S33">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T33">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="U33">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="V33">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W33">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X33">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y33">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="Z33">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AA33">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB33">
+        <v>2.45</v>
+      </c>
+      <c r="AC33">
         <v>2.29</v>
-      </c>
-      <c r="AC33">
-        <v>2.38</v>
       </c>
       <c r="AD33">
         <v>1.5</v>
       </c>
       <c r="AE33">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AF33">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="AG33">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.13</v>
+        <v>4.2</v>
       </c>
       <c r="AK33">
         <v>1.04</v>
@@ -5851,31 +5851,31 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="O34">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="P34">
-        <v>8.5</v>
+        <v>7.6</v>
       </c>
       <c r="Q34">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="R34">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="S34">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T34">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="U34">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="V34">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W34">
         <v>1.11</v>
@@ -5887,29 +5887,29 @@
         <v>1.13</v>
       </c>
       <c r="Z34">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AA34">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AB34">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="AC34">
-        <v>2.34</v>
+        <v>2.39</v>
       </c>
       <c r="AD34">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AE34">
         <v>1.17</v>
       </c>
       <c r="AF34">
+        <v>1.8</v>
+      </c>
+      <c r="AG34">
         <v>1.9</v>
       </c>
-      <c r="AG34">
-        <v>1.75</v>
-      </c>
       <c r="AH34" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AK34">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="O35">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P35">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="Q35">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="R35">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="S35">
+        <v>1.35</v>
+      </c>
+      <c r="T35">
+        <v>2.85</v>
+      </c>
+      <c r="U35">
+        <v>2.8</v>
+      </c>
+      <c r="V35">
         <v>1.36</v>
       </c>
-      <c r="T35">
-        <v>2.75</v>
-      </c>
-      <c r="U35">
-        <v>2.82</v>
-      </c>
-      <c r="V35">
-        <v>1.35</v>
-      </c>
       <c r="W35">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X35">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
         <v>1.3</v>
       </c>
       <c r="Z35">
-        <v>3.08</v>
+        <v>3.22</v>
       </c>
       <c r="AA35">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AB35">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AC35">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="AD35">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE35">
         <v>1.08</v>
       </c>
       <c r="AF35">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AG35">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AK35">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="O36">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P36">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="Q36">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="R36">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="S36">
+        <v>1.36</v>
+      </c>
+      <c r="T36">
+        <v>2.75</v>
+      </c>
+      <c r="U36">
+        <v>2.82</v>
+      </c>
+      <c r="V36">
         <v>1.35</v>
       </c>
-      <c r="T36">
-        <v>2.85</v>
-      </c>
-      <c r="U36">
-        <v>2.8</v>
-      </c>
-      <c r="V36">
-        <v>1.36</v>
-      </c>
       <c r="W36">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X36">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y36">
         <v>1.3</v>
       </c>
       <c r="Z36">
-        <v>3.22</v>
+        <v>3.08</v>
       </c>
       <c r="AA36">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AB36">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC36">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="AD36">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE36">
         <v>1.08</v>
       </c>
       <c r="AF36">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AG36">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AK36">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.64</v>
+        <v>1.49</v>
       </c>
       <c r="O37">
-        <v>3.96</v>
+        <v>4.3</v>
       </c>
       <c r="P37">
-        <v>5.61</v>
+        <v>6.65</v>
       </c>
       <c r="Q37">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="R37">
-        <v>2.24</v>
+        <v>2.5</v>
       </c>
       <c r="S37">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T37">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="U37">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="V37">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W37">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X37">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y37">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="Z37">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="AA37">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AB37">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AC37">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AD37">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE37">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF37">
         <v>1.85</v>
       </c>
       <c r="AG37">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AK37">
-        <v>2.35</v>
+        <v>2.47</v>
       </c>
       <c r="AL37">
         <v>0</v>

--- a/jogos_2026-08-17.xlsx
+++ b/jogos_2026-08-17.xlsx
@@ -612,13 +612,13 @@
         </is>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -631,7 +631,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
@@ -696,7 +696,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["9"]</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -714,28 +714,28 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -775,26 +775,26 @@
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
@@ -859,12 +859,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["28", "59", "85"]</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["43"]</t>
         </is>
       </c>
       <c r="AJ3">
@@ -877,28 +877,28 @@
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -941,13 +941,13 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4">
         <v>0</v>
@@ -957,7 +957,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["38"]</t>
         </is>
       </c>
       <c r="AJ4">
@@ -1040,28 +1040,28 @@
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1101,26 +1101,26 @@
         </is>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+1", "74"]</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["85"]</t>
         </is>
       </c>
       <c r="AJ5">
@@ -1203,28 +1203,28 @@
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1279,11 +1279,11 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["60", "81"]</t>
         </is>
       </c>
       <c r="AJ6">
@@ -1366,28 +1366,28 @@
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1439,14 +1439,14 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
@@ -1511,12 +1511,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["78"]</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["83"]</t>
         </is>
       </c>
       <c r="AJ7">
@@ -1529,28 +1529,28 @@
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
@@ -1692,28 +1692,28 @@
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP8">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -1768,11 +1768,11 @@
         <v>0</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["61"]</t>
         </is>
       </c>
       <c r="AJ9">
@@ -1855,28 +1855,28 @@
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN9">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP9">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>0.76</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
@@ -1916,10 +1916,10 @@
         </is>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -1928,14 +1928,14 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["50"]</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+1"]</t>
         </is>
       </c>
       <c r="AJ10">
@@ -2018,28 +2018,28 @@
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN10">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO10">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP10">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
@@ -2242,13 +2242,13 @@
         </is>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H12">
         <v>0</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["6", "17", "30"]</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
@@ -2344,28 +2344,28 @@
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN12">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP12">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
@@ -2405,10 +2405,10 @@
         </is>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -2417,14 +2417,14 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["87"]</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["54"]</t>
         </is>
       </c>
       <c r="AJ13">
@@ -2507,28 +2507,28 @@
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN13">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO13">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14">
@@ -2670,28 +2670,28 @@
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN14">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP14">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
@@ -2731,13 +2731,13 @@
         </is>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15">
         <v>0</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["36"]</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
@@ -2833,28 +2833,28 @@
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN15">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO15">
-        <v>-1</v>
+        <v>25</v>
       </c>
       <c r="AP15">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
@@ -2894,13 +2894,13 @@
         </is>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2909,11 +2909,11 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16">
@@ -2978,12 +2978,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["18", "30", "45+1"]</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["58", "64"]</t>
         </is>
       </c>
       <c r="AJ16">
@@ -2996,28 +2996,28 @@
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO16">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
@@ -3057,26 +3057,26 @@
         </is>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["38", "65", "76"]</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["17", "22", "82", "90+3"]</t>
         </is>
       </c>
       <c r="AJ17">
@@ -3159,28 +3159,28 @@
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO17">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP17">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
@@ -3220,26 +3220,26 @@
         </is>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H18">
         <v>0</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18">
         <v>0</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N18">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["18", "80"]</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
@@ -3322,28 +3322,28 @@
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO18">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP18">
-        <v>-1</v>
+        <v>25</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
@@ -3383,13 +3383,13 @@
         </is>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19">
         <v>0</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -3402,59 +3402,59 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N19">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O19">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="P19">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="Q19">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="R19">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="S19">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="T19">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="U19">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="V19">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W19">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X19">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Y19">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="Z19">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="AA19">
-        <v>3.14</v>
+        <v>2.8</v>
       </c>
       <c r="AB19">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AC19">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="AD19">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AE19">
         <v>1.02</v>
@@ -3463,50 +3463,50 @@
         <v>2.51</v>
       </c>
       <c r="AG19">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
+          <t>["12"]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ19">
+        <v>1.35</v>
+      </c>
+      <c r="AK19">
+        <v>1.58</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>3</v>
+      </c>
+      <c r="AN19">
+        <v>0</v>
+      </c>
+      <c r="AO19">
+        <v>11</v>
+      </c>
+      <c r="AP19">
+        <v>7</v>
+      </c>
+      <c r="AQ19">
         <v>1.4</v>
       </c>
-      <c r="AK19">
-        <v>1.55</v>
-      </c>
-      <c r="AL19">
-        <v>0</v>
-      </c>
-      <c r="AM19">
-        <v>-1</v>
-      </c>
-      <c r="AN19">
-        <v>-1</v>
-      </c>
-      <c r="AO19">
-        <v>-1</v>
-      </c>
-      <c r="AP19">
-        <v>-1</v>
-      </c>
-      <c r="AQ19">
-        <v>0</v>
-      </c>
       <c r="AR19">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
@@ -3546,130 +3546,130 @@
         </is>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N20">
         <v>2.06</v>
       </c>
       <c r="O20">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="P20">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="Q20">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R20">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="S20">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T20">
         <v>4.5</v>
       </c>
       <c r="U20">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="V20">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="W20">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="Z20">
-        <v>6.24</v>
+        <v>8.5</v>
       </c>
       <c r="AA20">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AB20">
-        <v>3.42</v>
+        <v>3.8</v>
       </c>
       <c r="AC20">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AD20">
-        <v>2.02</v>
+        <v>2.11</v>
       </c>
       <c r="AE20">
         <v>1.36</v>
       </c>
       <c r="AF20">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AG20">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["21", "61", "67", "83"]</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["5", "16", "39", "78"]</t>
         </is>
       </c>
       <c r="AJ20">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AK20">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AL20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AN20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO20">
-        <v>-1</v>
+        <v>28</v>
       </c>
       <c r="AP20">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
@@ -3709,10 +3709,10 @@
         </is>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -3721,14 +3721,14 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N21">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["64"]</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["47", "90+7"]</t>
         </is>
       </c>
       <c r="AJ21">
@@ -3811,28 +3811,28 @@
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO21">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP21">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22">
         <v>0</v>
@@ -3884,118 +3884,118 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22">
         <v>0</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N22">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="O22">
-        <v>3.85</v>
+        <v>3.72</v>
       </c>
       <c r="P22">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="Q22">
         <v>2</v>
       </c>
       <c r="R22">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="S22">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T22">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="U22">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="V22">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="W22">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X22">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="Y22">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="Z22">
-        <v>2.55</v>
+        <v>2.31</v>
       </c>
       <c r="AA22">
-        <v>2.38</v>
+        <v>2.49</v>
       </c>
       <c r="AB22">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AC22">
-        <v>4.45</v>
+        <v>4.75</v>
       </c>
       <c r="AD22">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AE22">
         <v>1.01</v>
       </c>
       <c r="AF22">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="AG22">
         <v>1.4</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
+          <t>["50"]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ22">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK22">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="AL22">
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN22">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO22">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>0.54</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
@@ -4035,130 +4035,130 @@
         </is>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23">
         <v>0</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N23">
-        <v>2.94</v>
+        <v>3.32</v>
       </c>
       <c r="O23">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P23">
         <v>1.92</v>
       </c>
       <c r="Q23">
-        <v>3.7</v>
+        <v>3.89</v>
       </c>
       <c r="R23">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S23">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="T23">
-        <v>3.44</v>
+        <v>3.25</v>
       </c>
       <c r="U23">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="V23">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="W23">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X23">
         <v>1.03</v>
       </c>
       <c r="Y23">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z23">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AA23">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AB23">
+        <v>2.15</v>
+      </c>
+      <c r="AC23">
+        <v>2.6</v>
+      </c>
+      <c r="AD23">
+        <v>1.48</v>
+      </c>
+      <c r="AE23">
+        <v>1.13</v>
+      </c>
+      <c r="AF23">
+        <v>1.53</v>
+      </c>
+      <c r="AG23">
         <v>2.3</v>
       </c>
-      <c r="AC23">
-        <v>2.31</v>
-      </c>
-      <c r="AD23">
-        <v>1.57</v>
-      </c>
-      <c r="AE23">
-        <v>1.18</v>
-      </c>
-      <c r="AF23">
-        <v>1.46</v>
-      </c>
-      <c r="AG23">
-        <v>2.5</v>
-      </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45"]</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["30", "52", "73"]</t>
         </is>
       </c>
       <c r="AJ23">
-        <v>1.24</v>
+        <v>1.8</v>
       </c>
       <c r="AK23">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AL23">
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO23">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP23">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AQ23">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AR23">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AT23">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
@@ -4189,139 +4189,139 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N24">
-        <v>1.73</v>
+        <v>2.65</v>
       </c>
       <c r="O24">
+        <v>3.55</v>
+      </c>
+      <c r="P24">
+        <v>2.2</v>
+      </c>
+      <c r="Q24">
+        <v>3.1</v>
+      </c>
+      <c r="R24">
+        <v>2.4</v>
+      </c>
+      <c r="S24">
+        <v>1.22</v>
+      </c>
+      <c r="T24">
         <v>4</v>
       </c>
-      <c r="P24">
-        <v>3.6</v>
-      </c>
-      <c r="Q24">
-        <v>2.11</v>
-      </c>
-      <c r="R24">
-        <v>2.82</v>
-      </c>
-      <c r="S24">
-        <v>1.13</v>
-      </c>
-      <c r="T24">
-        <v>4.5</v>
-      </c>
       <c r="U24">
-        <v>1.82</v>
+        <v>2.03</v>
       </c>
       <c r="V24">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="W24">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="X24">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z24">
-        <v>7.5</v>
+        <v>5.75</v>
       </c>
       <c r="AA24">
+        <v>1.38</v>
+      </c>
+      <c r="AB24">
+        <v>2.62</v>
+      </c>
+      <c r="AC24">
+        <v>2.04</v>
+      </c>
+      <c r="AD24">
+        <v>1.7</v>
+      </c>
+      <c r="AE24">
+        <v>1.24</v>
+      </c>
+      <c r="AF24">
+        <v>1.4</v>
+      </c>
+      <c r="AG24">
+        <v>2.88</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>["1", "19", "22", "70"]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>["3", "35", "45+3", "51", "61", "83"]</t>
+        </is>
+      </c>
+      <c r="AJ24">
         <v>1.25</v>
       </c>
-      <c r="AB24">
-        <v>3.4</v>
-      </c>
-      <c r="AC24">
-        <v>1.77</v>
-      </c>
-      <c r="AD24">
-        <v>2.03</v>
-      </c>
-      <c r="AE24">
-        <v>1.38</v>
-      </c>
-      <c r="AF24">
-        <v>1.31</v>
-      </c>
-      <c r="AG24">
-        <v>3.08</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ24">
-        <v>1.14</v>
-      </c>
       <c r="AK24">
-        <v>2</v>
+        <v>1.37</v>
       </c>
       <c r="AL24">
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN24">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AO24">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP24">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="AQ24">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR24">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AS24">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AT24">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
@@ -4352,139 +4352,139 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N25">
-        <v>2.89</v>
+        <v>1.7</v>
       </c>
       <c r="O25">
-        <v>3.65</v>
+        <v>4.8</v>
       </c>
       <c r="P25">
-        <v>2.2</v>
+        <v>3.55</v>
       </c>
       <c r="Q25">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="R25">
-        <v>2.29</v>
+        <v>2.71</v>
       </c>
       <c r="S25">
+        <v>1.12</v>
+      </c>
+      <c r="T25">
+        <v>4.95</v>
+      </c>
+      <c r="U25">
+        <v>1.88</v>
+      </c>
+      <c r="V25">
+        <v>1.85</v>
+      </c>
+      <c r="W25">
         <v>1.22</v>
       </c>
-      <c r="T25">
-        <v>3.9</v>
-      </c>
-      <c r="U25">
-        <v>2.08</v>
-      </c>
-      <c r="V25">
-        <v>1.7</v>
-      </c>
-      <c r="W25">
-        <v>1.13</v>
-      </c>
       <c r="X25">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Z25">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AA25">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="AB25">
-        <v>2.55</v>
+        <v>3.4</v>
       </c>
       <c r="AC25">
-        <v>2.1</v>
+        <v>1.74</v>
       </c>
       <c r="AD25">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AE25">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AF25">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AG25">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["30", "84"]</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["11", "52", "75", "87", "90+2"]</t>
         </is>
       </c>
       <c r="AJ25">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AK25">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="AL25">
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AO25">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AP25">
-        <v>-1</v>
+        <v>24</v>
       </c>
       <c r="AQ25">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AR25">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AS25">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AT25">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
@@ -4524,26 +4524,26 @@
         </is>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J26">
         <v>0</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N26">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["31", "35", "88"]</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["75"]</t>
         </is>
       </c>
       <c r="AJ26">
@@ -4626,28 +4626,28 @@
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN26">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ26">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AR26">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AS26">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT26">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
@@ -4687,48 +4687,48 @@
         </is>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N27">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="O27">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="P27">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="Q27">
-        <v>2.78</v>
+        <v>2.85</v>
       </c>
       <c r="R27">
-        <v>2.14</v>
+        <v>2.03</v>
       </c>
       <c r="S27">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T27">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="U27">
         <v>2.81</v>
@@ -4737,80 +4737,80 @@
         <v>1.36</v>
       </c>
       <c r="W27">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z27">
-        <v>3.51</v>
+        <v>3.4</v>
       </c>
       <c r="AA27">
         <v>1.95</v>
       </c>
       <c r="AB27">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AC27">
-        <v>3.41</v>
+        <v>3.49</v>
       </c>
       <c r="AD27">
         <v>1.3</v>
       </c>
       <c r="AE27">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF27">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG27">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["30", "43", "90"]</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["3", "46", "65"]</t>
         </is>
       </c>
       <c r="AJ27">
         <v>1.33</v>
       </c>
       <c r="AK27">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AL27">
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO27">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AP27">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AQ27">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AR27">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AS27">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AT27">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
@@ -4850,42 +4850,42 @@
         </is>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H28">
         <v>0</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28">
         <v>0</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28">
         <v>0</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N28">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="O28">
-        <v>3.9</v>
+        <v>4.15</v>
       </c>
       <c r="P28">
-        <v>4.75</v>
+        <v>4.9</v>
       </c>
       <c r="Q28">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="R28">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="S28">
         <v>1.3</v>
@@ -4894,10 +4894,10 @@
         <v>3.08</v>
       </c>
       <c r="U28">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="V28">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W28">
         <v>1.06</v>
@@ -4906,74 +4906,74 @@
         <v>1.04</v>
       </c>
       <c r="Y28">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z28">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AA28">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AB28">
+        <v>2.05</v>
+      </c>
+      <c r="AC28">
+        <v>2.81</v>
+      </c>
+      <c r="AD28">
+        <v>1.36</v>
+      </c>
+      <c r="AE28">
+        <v>1.13</v>
+      </c>
+      <c r="AF28">
+        <v>1.77</v>
+      </c>
+      <c r="AG28">
         <v>2</v>
       </c>
-      <c r="AC28">
-        <v>2.74</v>
-      </c>
-      <c r="AD28">
-        <v>1.35</v>
-      </c>
-      <c r="AE28">
-        <v>1.1</v>
-      </c>
-      <c r="AF28">
-        <v>1.8</v>
-      </c>
-      <c r="AG28">
-        <v>1.86</v>
-      </c>
       <c r="AH28" t="inlineStr">
         <is>
+          <t>["34", "90+3"]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ28">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK28">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AL28">
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN28">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO28">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP28">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ28">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AR28">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AS28">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AT28">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
@@ -5013,26 +5013,26 @@
         </is>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N29">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["10", "63", "90+6"]</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["36", "62"]</t>
         </is>
       </c>
       <c r="AJ29">
@@ -5115,28 +5115,28 @@
         <v>0</v>
       </c>
       <c r="AM29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN29">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO29">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AP29">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ29">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AR29">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AS29">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AT29">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
@@ -5176,13 +5176,13 @@
         </is>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -5191,11 +5191,11 @@
         <v>0</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N30">
@@ -5260,12 +5260,12 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["21"]</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["76"]</t>
         </is>
       </c>
       <c r="AJ30">
@@ -5278,28 +5278,28 @@
         <v>0</v>
       </c>
       <c r="AM30">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP30">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ30">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="AR30">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AS30">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AT30">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
@@ -5339,26 +5339,26 @@
         </is>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31">
         <v>0</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31">
         <v>0</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N31">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+8"]</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["3"]</t>
         </is>
       </c>
       <c r="AJ31">
@@ -5441,28 +5441,28 @@
         <v>0</v>
       </c>
       <c r="AM31">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO31">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP31">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ31">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS31">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AT31">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="O32">
-        <v>4.25</v>
+        <v>4.1</v>
       </c>
       <c r="P32">
-        <v>2.93</v>
+        <v>3.17</v>
       </c>
       <c r="Q32">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="R32">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="S32">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="T32">
         <v>5</v>
       </c>
       <c r="U32">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="V32">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="W32">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="X32">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z32">
-        <v>8.300000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="AA32">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AB32">
-        <v>4.14</v>
+        <v>3.45</v>
       </c>
       <c r="AC32">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AD32">
-        <v>2.28</v>
+        <v>2.12</v>
       </c>
       <c r="AE32">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="AF32">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AG32">
-        <v>3.74</v>
+        <v>3.34</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK32">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5691,31 +5691,31 @@
         <v>9.4</v>
       </c>
       <c r="O33">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="P33">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Q33">
         <v>11</v>
       </c>
       <c r="R33">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="S33">
         <v>1.25</v>
       </c>
       <c r="T33">
-        <v>3.42</v>
+        <v>4</v>
       </c>
       <c r="U33">
-        <v>2.31</v>
+        <v>2.23</v>
       </c>
       <c r="V33">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="W33">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X33">
         <v>1.04</v>
@@ -5724,22 +5724,22 @@
         <v>1.13</v>
       </c>
       <c r="Z33">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AA33">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AB33">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="AC33">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AD33">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AE33">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AF33">
         <v>2.15</v>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>4.2</v>
+        <v>1.11</v>
       </c>
       <c r="AK33">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,16 +5851,16 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="O34">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="P34">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="Q34">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="R34">
         <v>2.45</v>
@@ -5872,10 +5872,10 @@
         <v>3.42</v>
       </c>
       <c r="U34">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="V34">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W34">
         <v>1.11</v>
@@ -5890,25 +5890,25 @@
         <v>4.5</v>
       </c>
       <c r="AA34">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AB34">
         <v>2.26</v>
       </c>
       <c r="AC34">
-        <v>2.39</v>
+        <v>2.35</v>
       </c>
       <c r="AD34">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AE34">
         <v>1.17</v>
       </c>
       <c r="AF34">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG34">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK34">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O35">
+        <v>3</v>
+      </c>
+      <c r="P35">
         <v>3.2</v>
       </c>
-      <c r="P35">
-        <v>3.1</v>
-      </c>
       <c r="Q35">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="R35">
         <v>2</v>
       </c>
       <c r="S35">
+        <v>1.47</v>
+      </c>
+      <c r="T35">
+        <v>2.41</v>
+      </c>
+      <c r="U35">
+        <v>3</v>
+      </c>
+      <c r="V35">
         <v>1.35</v>
-      </c>
-      <c r="T35">
-        <v>2.85</v>
-      </c>
-      <c r="U35">
-        <v>2.8</v>
-      </c>
-      <c r="V35">
-        <v>1.36</v>
       </c>
       <c r="W35">
         <v>1.07</v>
       </c>
       <c r="X35">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y35">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="Z35">
-        <v>3.22</v>
+        <v>2.8</v>
       </c>
       <c r="AA35">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AB35">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AC35">
-        <v>3.34</v>
+        <v>4.4</v>
       </c>
       <c r="AD35">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AE35">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AF35">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AG35">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>1.27</v>
       </c>
       <c r="AK35">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="O36">
-        <v>3.25</v>
+        <v>3.16</v>
       </c>
       <c r="P36">
-        <v>3.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q36">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="R36">
-        <v>2.16</v>
+        <v>2.03</v>
       </c>
       <c r="S36">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T36">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="U36">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="V36">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W36">
         <v>1.05</v>
       </c>
       <c r="X36">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y36">
         <v>1.3</v>
       </c>
       <c r="Z36">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="AA36">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AB36">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AC36">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AD36">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE36">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF36">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AG36">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="AK36">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,31 +6340,31 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="O37">
-        <v>4.3</v>
+        <v>4.26</v>
       </c>
       <c r="P37">
-        <v>6.65</v>
+        <v>6.6</v>
       </c>
       <c r="Q37">
         <v>2</v>
       </c>
       <c r="R37">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="S37">
         <v>1.3</v>
       </c>
       <c r="T37">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="U37">
         <v>2.6</v>
       </c>
       <c r="V37">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W37">
         <v>1.11</v>
@@ -6379,10 +6379,10 @@
         <v>3.9</v>
       </c>
       <c r="AA37">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AB37">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AC37">
         <v>2.8</v>
@@ -6391,13 +6391,13 @@
         <v>1.34</v>
       </c>
       <c r="AE37">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF37">
         <v>1.85</v>
       </c>
       <c r="AG37">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK37">
-        <v>2.47</v>
+        <v>2.56</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="O38">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P38">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="Q38">
         <v>2.95</v>
       </c>
       <c r="R38">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="S38">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="T38">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="U38">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="V38">
         <v>1.32</v>
       </c>
       <c r="W38">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X38">
         <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z38">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="AA38">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="AB38">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AC38">
-        <v>3.5</v>
+        <v>3.78</v>
       </c>
       <c r="AD38">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE38">
         <v>1.07</v>
       </c>
       <c r="AF38">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AG38">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>1.28</v>
       </c>
       <c r="AK38">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,55 +6666,55 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="O39">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="P39">
-        <v>4.5</v>
+        <v>4.05</v>
       </c>
       <c r="Q39">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="R39">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="S39">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="T39">
-        <v>2.93</v>
+        <v>2.7</v>
       </c>
       <c r="U39">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="V39">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="W39">
         <v>1.07</v>
       </c>
       <c r="X39">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y39">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z39">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="AA39">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AB39">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AC39">
         <v>3.25</v>
       </c>
       <c r="AD39">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE39">
         <v>1.07</v>
@@ -6723,7 +6723,7 @@
         <v>1.82</v>
       </c>
       <c r="AG39">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="AK39">
         <v>2.2</v>
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="O40">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P40">
-        <v>2.27</v>
+        <v>1.95</v>
       </c>
       <c r="Q40">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="R40">
-        <v>1.9</v>
+        <v>2.14</v>
       </c>
       <c r="S40">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="T40">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="U40">
         <v>2.8</v>
       </c>
       <c r="V40">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W40">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X40">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z40">
-        <v>3.11</v>
+        <v>2.9</v>
       </c>
       <c r="AA40">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="AB40">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AC40">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="AD40">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE40">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF40">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AG40">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK40">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6995,61 +6995,61 @@
         <v>1.9</v>
       </c>
       <c r="O41">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P41">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="Q41">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="R41">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S41">
         <v>1.33</v>
       </c>
       <c r="T41">
-        <v>3.03</v>
+        <v>2.82</v>
       </c>
       <c r="U41">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="V41">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W41">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X41">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y41">
         <v>1.22</v>
       </c>
       <c r="Z41">
-        <v>3.75</v>
+        <v>3.82</v>
       </c>
       <c r="AA41">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB41">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC41">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="AD41">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AE41">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF41">
         <v>1.62</v>
       </c>
       <c r="AG41">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK41">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="O42">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="P42">
-        <v>4.22</v>
+        <v>4.47</v>
       </c>
       <c r="Q42">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="R42">
         <v>2.3</v>
       </c>
       <c r="S42">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T42">
         <v>3.2</v>
       </c>
       <c r="U42">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="V42">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W42">
         <v>1.11</v>
       </c>
       <c r="X42">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y42">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="Z42">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="AA42">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AB42">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AC42">
-        <v>2.66</v>
+        <v>2.49</v>
       </c>
       <c r="AD42">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AE42">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF42">
         <v>1.65</v>
       </c>
       <c r="AG42">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AK42">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="AL42">
         <v>0</v>
